--- a/kobo/comunidade_diagnostico_completo.xlsx
+++ b/kobo/comunidade_diagnostico_completo.xlsx
@@ -13474,7 +13474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C669"/>
+  <dimension ref="A1:C670"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17016,17 +17016,17 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>intensidade</t>
+          <t>confianca</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>baixa</t>
+          <t>nao_se_aplica</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Baixa</t>
+          <t>Não se aplica</t>
         </is>
       </c>
     </row>
@@ -17038,12 +17038,12 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>baixa</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Baixa</t>
         </is>
       </c>
     </row>
@@ -17055,12 +17055,12 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>alta</t>
+          <t>media</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
@@ -17072,29 +17072,29 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>nao_se_aplica</t>
+          <t>alta</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Não se aplica</t>
+          <t>Alta</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>acesso_mat</t>
+          <t>intensidade</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>facil</t>
+          <t>nao_se_aplica</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Fácil</t>
+          <t>Não se aplica</t>
         </is>
       </c>
     </row>
@@ -17106,12 +17106,12 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>moderado</t>
+          <t>facil</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Moderado</t>
+          <t>Fácil</t>
         </is>
       </c>
     </row>
@@ -17123,12 +17123,12 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>dificil</t>
+          <t>moderado</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Difícil</t>
+          <t>Moderado</t>
         </is>
       </c>
     </row>
@@ -17140,12 +17140,12 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>inexistente</t>
+          <t>dificil</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Inexistente</t>
+          <t>Difícil</t>
         </is>
       </c>
     </row>
@@ -17157,29 +17157,29 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>nao_sabe</t>
+          <t>inexistente</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Não sabe</t>
+          <t>Inexistente</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>part_estud</t>
+          <t>acesso_mat</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>espectadores</t>
+          <t>nao_sabe</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Espectadores</t>
+          <t>Não sabe</t>
         </is>
       </c>
     </row>
@@ -17191,12 +17191,12 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>colaboradores_pontuais</t>
+          <t>espectadores</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Colaboradores pontuais</t>
+          <t>Espectadores</t>
         </is>
       </c>
     </row>
@@ -17208,12 +17208,12 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>protagonistas_em_alguns_momentos</t>
+          <t>colaboradores_pontuais</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Protagonistas em alguns momentos</t>
+          <t>Colaboradores pontuais</t>
         </is>
       </c>
     </row>
@@ -17225,12 +17225,12 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>protagonistas_continuos</t>
+          <t>protagonistas_em_alguns_momentos</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Protagonistas contínuos</t>
+          <t>Protagonistas em alguns momentos</t>
         </is>
       </c>
     </row>
@@ -17242,29 +17242,29 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>nao_sabe</t>
+          <t>protagonistas_continuos</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Não sabe</t>
+          <t>Protagonistas contínuos</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>continuidade_proj</t>
+          <t>part_estud</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>garantida_institucionalmente</t>
+          <t>nao_sabe</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Garantida institucionalmente</t>
+          <t>Não sabe</t>
         </is>
       </c>
     </row>
@@ -17276,12 +17276,12 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>dependente_de_pessoas_especifica</t>
+          <t>garantida_institucionalmente</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Dependente de pessoas específicas</t>
+          <t>Garantida institucionalmente</t>
         </is>
       </c>
     </row>
@@ -17293,12 +17293,12 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>incerta</t>
+          <t>dependente_de_pessoas_especifica</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Incerta</t>
+          <t>Dependente de pessoas específicas</t>
         </is>
       </c>
     </row>
@@ -17310,29 +17310,29 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>nao_sabe</t>
+          <t>incerta</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Não sabe</t>
+          <t>Incerta</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>nivel_part</t>
+          <t>continuidade_proj</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>informativa</t>
+          <t>nao_sabe</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Informativa (recebem informação)</t>
+          <t>Não sabe</t>
         </is>
       </c>
     </row>
@@ -17344,12 +17344,12 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>consultiva</t>
+          <t>informativa</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Consultiva (são ouvidos)</t>
+          <t>Informativa (recebem informação)</t>
         </is>
       </c>
     </row>
@@ -17361,12 +17361,12 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>colaborativa</t>
+          <t>consultiva</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Colaborativa (constroem junto)</t>
+          <t>Consultiva (são ouvidos)</t>
         </is>
       </c>
     </row>
@@ -17378,12 +17378,12 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>protagonista</t>
+          <t>colaborativa</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Protagonista (decidem e conduzem)</t>
+          <t>Colaborativa (constroem junto)</t>
         </is>
       </c>
     </row>
@@ -17395,29 +17395,29 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>nao_sabe</t>
+          <t>protagonista</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Não sabe</t>
+          <t>Protagonista (decidem e conduzem)</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>env_fam</t>
+          <t>nivel_part</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>ausente</t>
+          <t>nao_sabe</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Ausente</t>
+          <t>Não sabe</t>
         </is>
       </c>
     </row>
@@ -17429,12 +17429,12 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>esporadico</t>
+          <t>ausente</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Esporádico</t>
+          <t>Ausente</t>
         </is>
       </c>
     </row>
@@ -17446,12 +17446,12 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>regular</t>
+          <t>esporadico</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Regular</t>
+          <t>Esporádico</t>
         </is>
       </c>
     </row>
@@ -17463,12 +17463,12 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>ativo_protagonista</t>
+          <t>regular</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Ativo/protagonista</t>
+          <t>Regular</t>
         </is>
       </c>
     </row>
@@ -17480,29 +17480,29 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>nao_sabe</t>
+          <t>ativo_protagonista</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Não sabe</t>
+          <t>Ativo/protagonista</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>barr_fam</t>
+          <t>env_fam</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>horario_de_trabalho</t>
+          <t>nao_sabe</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Horário de trabalho</t>
+          <t>Não sabe</t>
         </is>
       </c>
     </row>
@@ -17514,12 +17514,12 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>distancia</t>
+          <t>horario_de_trabalho</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Distância</t>
+          <t>Horário de trabalho</t>
         </is>
       </c>
     </row>
@@ -17531,12 +17531,12 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>comunicacao_inadequada</t>
+          <t>distancia</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Comunicação inadequada</t>
+          <t>Distância</t>
         </is>
       </c>
     </row>
@@ -17548,12 +17548,12 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>falta_de_convite_convocacao</t>
+          <t>comunicacao_inadequada</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Falta de convite/convocação</t>
+          <t>Comunicação inadequada</t>
         </is>
       </c>
     </row>
@@ -17565,29 +17565,29 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>falta_de_convite_convocacao</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Outra</t>
+          <t>Falta de convite/convocação</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>cat_ator</t>
+          <t>barr_fam</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>sec_educacao</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Secretaria de Educação</t>
+          <t>Outra</t>
         </is>
       </c>
     </row>
@@ -17599,12 +17599,12 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>sec_meio_amb</t>
+          <t>sec_educacao</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Secretaria de Meio Ambiente</t>
+          <t>Secretaria de Educação</t>
         </is>
       </c>
     </row>
@@ -17616,12 +17616,12 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>defesa_civil</t>
+          <t>sec_meio_amb</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Defesa Civil</t>
+          <t>Secretaria de Meio Ambiente</t>
         </is>
       </c>
     </row>
@@ -17633,12 +17633,12 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>sec_saude</t>
+          <t>defesa_civil</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Secretaria de Saúde</t>
+          <t>Defesa Civil</t>
         </is>
       </c>
     </row>
@@ -17650,12 +17650,12 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>assist_social</t>
+          <t>sec_saude</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Assistência Social</t>
+          <t>Secretaria de Saúde</t>
         </is>
       </c>
     </row>
@@ -17667,12 +17667,12 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>obras</t>
+          <t>assist_social</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Obras</t>
+          <t>Assistência Social</t>
         </is>
       </c>
     </row>
@@ -17684,12 +17684,12 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>bombeiros</t>
+          <t>obras</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Bombeiros</t>
+          <t>Obras</t>
         </is>
       </c>
     </row>
@@ -17701,12 +17701,12 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>ubs</t>
+          <t>bombeiros</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>UBS</t>
+          <t>Bombeiros</t>
         </is>
       </c>
     </row>
@@ -17718,12 +17718,12 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>vigilancia</t>
+          <t>ubs</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Vigilância</t>
+          <t>UBS</t>
         </is>
       </c>
     </row>
@@ -17735,12 +17735,12 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>outro_publico</t>
+          <t>vigilancia</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Outro (poder público)</t>
+          <t>Vigilância</t>
         </is>
       </c>
     </row>
@@ -17752,12 +17752,12 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>universidade</t>
+          <t>outro_publico</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Universidade</t>
+          <t>Outro (poder público)</t>
         </is>
       </c>
     </row>
@@ -17769,12 +17769,12 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>inst_federal</t>
+          <t>universidade</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Instituto Federal</t>
+          <t>Universidade</t>
         </is>
       </c>
     </row>
@@ -17786,12 +17786,12 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>escola_tecnica</t>
+          <t>inst_federal</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Escola técnica</t>
+          <t>Instituto Federal</t>
         </is>
       </c>
     </row>
@@ -17803,12 +17803,12 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>centro_pesquisa</t>
+          <t>escola_tecnica</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Centro de pesquisa</t>
+          <t>Escola técnica</t>
         </is>
       </c>
     </row>
@@ -17820,12 +17820,12 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>museu</t>
+          <t>centro_pesquisa</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Museu</t>
+          <t>Centro de pesquisa</t>
         </is>
       </c>
     </row>
@@ -17837,12 +17837,12 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>jardim_botanico</t>
+          <t>museu</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Jardim botânico</t>
+          <t>Museu</t>
         </is>
       </c>
     </row>
@@ -17854,12 +17854,12 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>outro_educ_ciencia</t>
+          <t>jardim_botanico</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Outro (educação/ciência)</t>
+          <t>Jardim botânico</t>
         </is>
       </c>
     </row>
@@ -17871,12 +17871,12 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>assoc_moradores</t>
+          <t>outro_educ_ciencia</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Associação de moradores</t>
+          <t>Outro (educação/ciência)</t>
         </is>
       </c>
     </row>
@@ -17888,12 +17888,12 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>ong</t>
+          <t>assoc_moradores</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>ONG</t>
+          <t>Associação de moradores</t>
         </is>
       </c>
     </row>
@@ -17905,12 +17905,12 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>cooperativa</t>
+          <t>ong</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Cooperativa</t>
+          <t>ONG</t>
         </is>
       </c>
     </row>
@@ -17922,12 +17922,12 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>catadores</t>
+          <t>cooperativa</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Catadores</t>
+          <t>Cooperativa</t>
         </is>
       </c>
     </row>
@@ -17939,12 +17939,12 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>mov_sociais</t>
+          <t>catadores</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Movimentos sociais</t>
+          <t>Catadores</t>
         </is>
       </c>
     </row>
@@ -17956,12 +17956,12 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>coletivos</t>
+          <t>mov_sociais</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Coletivos</t>
+          <t>Movimentos sociais</t>
         </is>
       </c>
     </row>
@@ -17973,12 +17973,12 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>grupos_culturais</t>
+          <t>coletivos</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Grupos culturais</t>
+          <t>Coletivos</t>
         </is>
       </c>
     </row>
@@ -17990,12 +17990,12 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>org_comunit_relig</t>
+          <t>grupos_culturais</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Organizações comunitárias/religiosas</t>
+          <t>Grupos culturais</t>
         </is>
       </c>
     </row>
@@ -18007,12 +18007,12 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>outro_soc_civil</t>
+          <t>org_comunit_relig</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Outro (sociedade civil)</t>
+          <t>Organizações comunitárias/religiosas</t>
         </is>
       </c>
     </row>
@@ -18024,12 +18024,12 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>povos_indigenas</t>
+          <t>outro_soc_civil</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Povos indígenas</t>
+          <t>Outro (sociedade civil)</t>
         </is>
       </c>
     </row>
@@ -18041,12 +18041,12 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>quilombolas</t>
+          <t>povos_indigenas</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Quilombolas</t>
+          <t>Povos indígenas</t>
         </is>
       </c>
     </row>
@@ -18058,12 +18058,12 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>agric_familiares</t>
+          <t>quilombolas</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Agricultores familiares</t>
+          <t>Quilombolas</t>
         </is>
       </c>
     </row>
@@ -18075,12 +18075,12 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>pescadores</t>
+          <t>agric_familiares</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Pescadores</t>
+          <t>Agricultores familiares</t>
         </is>
       </c>
     </row>
@@ -18092,12 +18092,12 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>com_tradicionais</t>
+          <t>pescadores</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Comunidades tradicionais</t>
+          <t>Pescadores</t>
         </is>
       </c>
     </row>
@@ -18109,12 +18109,12 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>liderancas</t>
+          <t>com_tradicionais</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Lideranças</t>
+          <t>Comunidades tradicionais</t>
         </is>
       </c>
     </row>
@@ -18126,12 +18126,12 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>detentores_saberes</t>
+          <t>liderancas</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Detentores de conhecimentos locais</t>
+          <t>Lideranças</t>
         </is>
       </c>
     </row>
@@ -18143,29 +18143,29 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>outro_comunidades</t>
+          <t>detentores_saberes</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Outro (comunidades e conhecimentos)</t>
+          <t>Detentores de conhecimentos locais</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>nivel_rel_grade</t>
+          <t>cat_ator</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>nao_existe</t>
+          <t>outro_comunidades</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Não existe no território</t>
+          <t>Outro (comunidades e conhecimentos)</t>
         </is>
       </c>
     </row>
@@ -18177,12 +18177,12 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>nao_sei</t>
+          <t>nao_existe</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Não sei se existe</t>
+          <t>Não existe no território</t>
         </is>
       </c>
     </row>
@@ -18194,12 +18194,12 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>sem_contato</t>
+          <t>nao_sei</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Existe, mas nunca houve contato</t>
+          <t>Não sei se existe</t>
         </is>
       </c>
     </row>
@@ -18211,12 +18211,12 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>contato_pontual</t>
+          <t>sem_contato</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Contato pontual, sem combinação formal (ainda não é parceiro(a))</t>
+          <t>Existe, mas nunca houve contato</t>
         </is>
       </c>
     </row>
@@ -18228,12 +18228,12 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>parceria</t>
+          <t>contato_pontual</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Parceria — já colaboram em ações combinadas</t>
+          <t>Contato pontual, sem combinação formal (ainda não é parceiro(a))</t>
         </is>
       </c>
     </row>
@@ -18245,29 +18245,29 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>articulacao</t>
+          <t>parceria</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Articulação permanente — parceria contínua e estruturada</t>
+          <t>Parceria — já colaboram em ações combinadas</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>canais</t>
+          <t>nivel_rel_grade</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>whatsapp</t>
+          <t>articulacao</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>WhatsApp</t>
+          <t>Articulação permanente — parceria contínua e estruturada</t>
         </is>
       </c>
     </row>
@@ -18279,12 +18279,12 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>comunicados_impressos</t>
+          <t>whatsapp</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Comunicados impressos</t>
+          <t>WhatsApp</t>
         </is>
       </c>
     </row>
@@ -18296,12 +18296,12 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>reunioes</t>
+          <t>comunicados_impressos</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Reuniões</t>
+          <t>Comunicados impressos</t>
         </is>
       </c>
     </row>
@@ -18313,12 +18313,12 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>redes_sociais</t>
+          <t>reunioes</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Redes sociais</t>
+          <t>Reuniões</t>
         </is>
       </c>
     </row>
@@ -18330,12 +18330,12 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>alto_falante_radio_local</t>
+          <t>redes_sociais</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Alto-falante/rádio local</t>
+          <t>Redes sociais</t>
         </is>
       </c>
     </row>
@@ -18347,29 +18347,29 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>alto_falante_radio_local</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>Alto-falante/rádio local</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>suficiente</t>
+          <t>canais</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>sim</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Outro</t>
         </is>
       </c>
     </row>
@@ -18381,12 +18381,12 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>parcialmente</t>
+          <t>sim</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Parcialmente</t>
+          <t>Sim</t>
         </is>
       </c>
     </row>
@@ -18398,12 +18398,12 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>nao</t>
+          <t>parcialmente</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Parcialmente</t>
         </is>
       </c>
     </row>
@@ -18415,29 +18415,29 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>nao_sabe</t>
+          <t>nao</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Não sabe</t>
+          <t>Não</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>barr_artic</t>
+          <t>suficiente</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>falta_de_contato</t>
+          <t>nao_sabe</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Falta de contato</t>
+          <t>Não sabe</t>
         </is>
       </c>
     </row>
@@ -18449,12 +18449,12 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>burocracia</t>
+          <t>falta_de_contato</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Burocracia</t>
+          <t>Falta de contato</t>
         </is>
       </c>
     </row>
@@ -18466,12 +18466,12 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>desconfianca_historico_de_relaca</t>
+          <t>burocracia</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Desconfiança/histórico de relação</t>
+          <t>Burocracia</t>
         </is>
       </c>
     </row>
@@ -18483,12 +18483,12 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>falta_de_tempo</t>
+          <t>desconfianca_historico_de_relaca</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Falta de tempo</t>
+          <t>Desconfiança/histórico de relação</t>
         </is>
       </c>
     </row>
@@ -18500,29 +18500,29 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>falta_de_tempo</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Outra</t>
+          <t>Falta de tempo</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>ameacas</t>
+          <t>barr_artic</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>enchente</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Enchente</t>
+          <t>Outra</t>
         </is>
       </c>
     </row>
@@ -18534,12 +18534,12 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>inundacao</t>
+          <t>enchente</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Inundação</t>
+          <t>Enchente</t>
         </is>
       </c>
     </row>
@@ -18551,12 +18551,12 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>alagamento</t>
+          <t>inundacao</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Alagamento</t>
+          <t>Inundação</t>
         </is>
       </c>
     </row>
@@ -18568,12 +18568,12 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>enxurrada</t>
+          <t>alagamento</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Enxurrada</t>
+          <t>Alagamento</t>
         </is>
       </c>
     </row>
@@ -18585,12 +18585,12 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>deslizamento</t>
+          <t>enxurrada</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Deslizamento</t>
+          <t>Enxurrada</t>
         </is>
       </c>
     </row>
@@ -18602,12 +18602,12 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>erosao</t>
+          <t>deslizamento</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Erosão</t>
+          <t>Deslizamento</t>
         </is>
       </c>
     </row>
@@ -18619,12 +18619,12 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>estiagem_seca</t>
+          <t>erosao</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Estiagem/seca</t>
+          <t>Erosão</t>
         </is>
       </c>
     </row>
@@ -18636,12 +18636,12 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>falta_de_agua</t>
+          <t>estiagem_seca</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Falta de água</t>
+          <t>Estiagem/seca</t>
         </is>
       </c>
     </row>
@@ -18653,12 +18653,12 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>onda_de_calor</t>
+          <t>falta_de_agua</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Onda de calor</t>
+          <t>Falta de água</t>
         </is>
       </c>
     </row>
@@ -18670,12 +18670,12 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>frio_intenso</t>
+          <t>onda_de_calor</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Frio intenso</t>
+          <t>Onda de calor</t>
         </is>
       </c>
     </row>
@@ -18687,12 +18687,12 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>tempestades</t>
+          <t>frio_intenso</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Tempestades</t>
+          <t>Frio intenso</t>
         </is>
       </c>
     </row>
@@ -18704,12 +18704,12 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>vendavais</t>
+          <t>tempestades</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Vendavais</t>
+          <t>Tempestades</t>
         </is>
       </c>
     </row>
@@ -18721,12 +18721,12 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>granizo</t>
+          <t>vendavais</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Granizo</t>
+          <t>Vendavais</t>
         </is>
       </c>
     </row>
@@ -18738,12 +18738,12 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>ciclones</t>
+          <t>granizo</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Ciclones</t>
+          <t>Granizo</t>
         </is>
       </c>
     </row>
@@ -18755,12 +18755,12 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>queimadas</t>
+          <t>ciclones</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Queimadas</t>
+          <t>Ciclones</t>
         </is>
       </c>
     </row>
@@ -18772,12 +18772,12 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>incendios</t>
+          <t>queimadas</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Incêndios</t>
+          <t>Queimadas</t>
         </is>
       </c>
     </row>
@@ -18789,12 +18789,12 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>fumaca_poluicao_atmosferica</t>
+          <t>incendios</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Fumaça/poluição atmosférica</t>
+          <t>Incêndios</t>
         </is>
       </c>
     </row>
@@ -18806,12 +18806,12 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>contaminacao_da_agua</t>
+          <t>fumaca_poluicao_atmosferica</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Contaminação da água</t>
+          <t>Fumaça/poluição atmosférica</t>
         </is>
       </c>
     </row>
@@ -18823,12 +18823,12 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>problemas_relacionados_a_residuo</t>
+          <t>contaminacao_da_agua</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Problemas relacionados a resíduos</t>
+          <t>Contaminação da água</t>
         </is>
       </c>
     </row>
@@ -18840,29 +18840,29 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>problemas_relacionados_a_residuo</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Outros</t>
+          <t>Problemas relacionados a resíduos</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>base_percepcao</t>
+          <t>ameacas</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>observacao_ao_longo_dos_anos</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>Observação ao longo dos anos</t>
+          <t>Outros</t>
         </is>
       </c>
     </row>
@@ -18874,12 +18874,12 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>relatos_de_moradores_antigos</t>
+          <t>observacao_ao_longo_dos_anos</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Relatos de moradores antigos</t>
+          <t>Observação ao longo dos anos</t>
         </is>
       </c>
     </row>
@@ -18891,12 +18891,12 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>comparacao_com_registros</t>
+          <t>relatos_de_moradores_antigos</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>Comparação com registros</t>
+          <t>Relatos de moradores antigos</t>
         </is>
       </c>
     </row>
@@ -18908,12 +18908,12 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>noticias</t>
+          <t>comparacao_com_registros</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>Notícias</t>
+          <t>Comparação com registros</t>
         </is>
       </c>
     </row>
@@ -18925,29 +18925,29 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>nao_sabe</t>
+          <t>noticias</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>Não sabe</t>
+          <t>Notícias</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>fontes_risco</t>
+          <t>base_percepcao</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>defesa_civil</t>
+          <t>nao_sabe</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Defesa Civil</t>
+          <t>Não sabe</t>
         </is>
       </c>
     </row>
@@ -18959,12 +18959,12 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>dados_meteorologicos</t>
+          <t>defesa_civil</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Dados meteorológicos (ex.: INMET)</t>
+          <t>Defesa Civil</t>
         </is>
       </c>
     </row>
@@ -18976,12 +18976,12 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>universidade</t>
+          <t>dados_meteorologicos</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Universidade</t>
+          <t>Dados meteorológicos (ex.: INMET)</t>
         </is>
       </c>
     </row>
@@ -18993,12 +18993,12 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>ong</t>
+          <t>universidade</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>ONG</t>
+          <t>Universidade</t>
         </is>
       </c>
     </row>
@@ -19010,12 +19010,12 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>conhecimento_tradicional</t>
+          <t>ong</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>Conhecimento tradicional</t>
+          <t>ONG</t>
         </is>
       </c>
     </row>
@@ -19027,12 +19027,12 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>nao_ha_fonte_consultada</t>
+          <t>conhecimento_tradicional</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>Não há fonte consultada</t>
+          <t>Conhecimento tradicional</t>
         </is>
       </c>
     </row>
@@ -19044,29 +19044,29 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>nao_ha_fonte_consultada</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>Outra</t>
+          <t>Não há fonte consultada</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>freq_risco</t>
+          <t>fontes_risco</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>raro</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>Raro (já ocorreu uma vez)</t>
+          <t>Outra</t>
         </is>
       </c>
     </row>
@@ -19078,12 +19078,12 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>ocasional</t>
+          <t>raro</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>Ocasional</t>
+          <t>Raro (já ocorreu uma vez)</t>
         </is>
       </c>
     </row>
@@ -19095,12 +19095,12 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>frequente</t>
+          <t>ocasional</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>Frequente</t>
+          <t>Ocasional</t>
         </is>
       </c>
     </row>
@@ -19112,12 +19112,12 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>muito_frequente_recorrente</t>
+          <t>frequente</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>Muito frequente/recorrente</t>
+          <t>Frequente</t>
         </is>
       </c>
     </row>
@@ -19129,29 +19129,29 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>nao_sabe</t>
+          <t>muito_frequente_recorrente</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>Não sabe</t>
+          <t>Muito frequente/recorrente</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>cond_amplia</t>
+          <t>freq_risco</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>acessibilidade_limitada_nas_rota</t>
+          <t>nao_sabe</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>Acessibilidade limitada nas rotas de saída</t>
+          <t>Não sabe</t>
         </is>
       </c>
     </row>
@@ -19163,12 +19163,12 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>ausencia_de_sinalizacao_de_emerg</t>
+          <t>acessibilidade_limitada_nas_rota</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>Ausência de sinalização de emergência</t>
+          <t>Acessibilidade limitada nas rotas de saída</t>
         </is>
       </c>
     </row>
@@ -19180,12 +19180,12 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>estrutura_fisica_fragilizada</t>
+          <t>ausencia_de_sinalizacao_de_emerg</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>Estrutura física fragilizada</t>
+          <t>Ausência de sinalização de emergência</t>
         </is>
       </c>
     </row>
@@ -19197,12 +19197,12 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>ausencia_de_comunicacao_acessive</t>
+          <t>estrutura_fisica_fragilizada</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>Ausência de comunicação acessível (Libras/Braile/linguagem simples)</t>
+          <t>Estrutura física fragilizada</t>
         </is>
       </c>
     </row>
@@ -19214,12 +19214,12 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>ausencia_de_plano_de_evacuacao_a</t>
+          <t>ausencia_de_comunicacao_acessive</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>Ausência de plano de evacuação adaptado</t>
+          <t>Ausência de comunicação acessível (Libras/Braile/linguagem simples)</t>
         </is>
       </c>
     </row>
@@ -19231,12 +19231,12 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>distancia_de_pontos_de_apoio_soc</t>
+          <t>ausencia_de_plano_de_evacuacao_a</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>Distância de pontos de apoio/socorro</t>
+          <t>Ausência de plano de evacuação adaptado</t>
         </is>
       </c>
     </row>
@@ -19248,29 +19248,29 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>distancia_de_pontos_de_apoio_soc</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>Outra condição</t>
+          <t>Distância de pontos de apoio/socorro</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>cap_resp</t>
+          <t>cond_amplia</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>brigada_equipe_treinada</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>Brigada/equipe treinada</t>
+          <t>Outra condição</t>
         </is>
       </c>
     </row>
@@ -19282,12 +19282,12 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>plano_de_evacuacao</t>
+          <t>brigada_equipe_treinada</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>Plano de evacuação</t>
+          <t>Brigada/equipe treinada</t>
         </is>
       </c>
     </row>
@@ -19299,12 +19299,12 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>comunicacao_de_alerta</t>
+          <t>plano_de_evacuacao</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>Comunicação de alerta</t>
+          <t>Plano de evacuação</t>
         </is>
       </c>
     </row>
@@ -19316,12 +19316,12 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>apoio_de_rede_externa</t>
+          <t>comunicacao_de_alerta</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>Apoio de rede externa</t>
+          <t>Comunicação de alerta</t>
         </is>
       </c>
     </row>
@@ -19333,12 +19333,12 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>kit_de_emergencia</t>
+          <t>apoio_de_rede_externa</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>Kit de emergência</t>
+          <t>Apoio de rede externa</t>
         </is>
       </c>
     </row>
@@ -19350,12 +19350,12 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>nenhuma_identificada</t>
+          <t>kit_de_emergencia</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>Nenhuma identificada</t>
+          <t>Kit de emergência</t>
         </is>
       </c>
     </row>
@@ -19367,29 +19367,29 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>nenhuma_identificada</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>Outra</t>
+          <t>Nenhuma identificada</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>aval_cap</t>
+          <t>cap_resp</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>boa</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Outra</t>
         </is>
       </c>
     </row>
@@ -19401,12 +19401,12 @@
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>regular</t>
+          <t>boa</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>Regular</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
@@ -19418,12 +19418,12 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>fraca</t>
+          <t>regular</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>Fraca</t>
+          <t>Regular</t>
         </is>
       </c>
     </row>
@@ -19435,12 +19435,12 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>inexistente</t>
+          <t>fraca</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>Inexistente</t>
+          <t>Fraca</t>
         </is>
       </c>
     </row>
@@ -19452,29 +19452,29 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>nao_sabe</t>
+          <t>inexistente</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>Não sabe</t>
+          <t>Inexistente</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>bma_ns</t>
+          <t>aval_cap</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>baixa</t>
+          <t>nao_sabe</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>Baixa</t>
+          <t>Não sabe</t>
         </is>
       </c>
     </row>
@@ -19486,12 +19486,12 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>baixa</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Baixa</t>
         </is>
       </c>
     </row>
@@ -19503,12 +19503,12 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>alta</t>
+          <t>media</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
@@ -19520,29 +19520,29 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>nao_sabe</t>
+          <t>alta</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>Não sabe</t>
+          <t>Alta</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>bma</t>
+          <t>bma_ns</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>baixa</t>
+          <t>nao_sabe</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>Baixa</t>
+          <t>Não sabe</t>
         </is>
       </c>
     </row>
@@ -19554,12 +19554,12 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>baixa</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Baixa</t>
         </is>
       </c>
     </row>
@@ -19571,29 +19571,29 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>alta</t>
+          <t>media</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>prio_1a5</t>
+          <t>bma</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>alta</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>1 — Muito baixa</t>
+          <t>Alta</t>
         </is>
       </c>
     </row>
@@ -19605,12 +19605,12 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1 — Muito baixa</t>
         </is>
       </c>
     </row>
@@ -19622,12 +19622,12 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>3 — Média</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -19639,12 +19639,12 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3 — Média</t>
         </is>
       </c>
     </row>
@@ -19656,29 +19656,29 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>5 — Muito alta</t>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>marc_risco</t>
+          <t>prio_1a5</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>lacuna</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>Não sabemos avaliar isso com segurança (gera lacuna de conhecimento)</t>
+          <t>5 — Muito alta</t>
         </is>
       </c>
     </row>
@@ -19690,12 +19690,12 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>aval_externa</t>
+          <t>lacuna</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>Requer avaliação técnica externa</t>
+          <t>Não sabemos avaliar isso com segurança (gera lacuna de conhecimento)</t>
         </is>
       </c>
     </row>
@@ -19707,29 +19707,29 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>selecionado</t>
+          <t>aval_externa</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>Selecionar este risco para a Leitura Integrada e planejamento</t>
+          <t>Requer avaliação técnica externa</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>acionavel</t>
+          <t>marc_risco</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>a_escola_pode_agir_sozinha</t>
+          <t>selecionado</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>A comunidade pode agir sozinha</t>
+          <t>Selecionar este risco para a Leitura Integrada e planejamento</t>
         </is>
       </c>
     </row>
@@ -19741,12 +19741,12 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>precisa_de_parceria</t>
+          <t>a_escola_pode_agir_sozinha</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>Precisa de parceria</t>
+          <t>A comunidade pode agir sozinha</t>
         </is>
       </c>
     </row>
@@ -19758,12 +19758,12 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>esta_fora_do_alcance_da_escola</t>
+          <t>precisa_de_parceria</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>Está fora do alcance da comunidade</t>
+          <t>Precisa de parceria</t>
         </is>
       </c>
     </row>
@@ -19775,29 +19775,29 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>nao_sabe</t>
+          <t>esta_fora_do_alcance_da_escola</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>Não sabe</t>
+          <t>Está fora do alcance da comunidade</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>resp_tipo</t>
+          <t>acionavel</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>acao_estrutural</t>
+          <t>nao_sabe</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>Ação estrutural</t>
+          <t>Não sabe</t>
         </is>
       </c>
     </row>
@@ -19809,12 +19809,12 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>acao_pedagogica</t>
+          <t>acao_estrutural</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>Ação pedagógica</t>
+          <t>Ação estrutural</t>
         </is>
       </c>
     </row>
@@ -19826,12 +19826,12 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>articulacao_institucional</t>
+          <t>acao_pedagogica</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>Articulação institucional</t>
+          <t>Ação pedagógica</t>
         </is>
       </c>
     </row>
@@ -19843,12 +19843,12 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>comunicacao</t>
+          <t>articulacao_institucional</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>Comunicação</t>
+          <t>Articulação institucional</t>
         </is>
       </c>
     </row>
@@ -19860,12 +19860,12 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>mobilizacao_comunitaria</t>
+          <t>comunicacao</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>Mobilização comunitária</t>
+          <t>Comunicação</t>
         </is>
       </c>
     </row>
@@ -19877,12 +19877,12 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>monitoramento</t>
+          <t>mobilizacao_comunitaria</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>Monitoramento</t>
+          <t>Mobilização comunitária</t>
         </is>
       </c>
     </row>
@@ -19894,29 +19894,29 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>monitoramento</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>Monitoramento</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>status_ativ</t>
+          <t>resp_tipo</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>planejada</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>Planejada</t>
+          <t>Outro</t>
         </is>
       </c>
     </row>
@@ -19928,12 +19928,12 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>em_andamento</t>
+          <t>planejada</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>Em andamento</t>
+          <t>Planejada</t>
         </is>
       </c>
     </row>
@@ -19945,12 +19945,12 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>concluida</t>
+          <t>em_andamento</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>Concluída</t>
+          <t>Em andamento</t>
         </is>
       </c>
     </row>
@@ -19962,29 +19962,29 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>nao_realizada</t>
+          <t>concluida</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>Não realizada</t>
+          <t>Concluída</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>papel_estud2</t>
+          <t>status_ativ</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>espectador</t>
+          <t>nao_realizada</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>Espectador</t>
+          <t>Não realizada</t>
         </is>
       </c>
     </row>
@@ -19996,12 +19996,12 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>participante</t>
+          <t>espectador</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>Participante</t>
+          <t>Espectador</t>
         </is>
       </c>
     </row>
@@ -20013,12 +20013,12 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>protagonista</t>
+          <t>participante</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>Protagonista</t>
+          <t>Participante</t>
         </is>
       </c>
     </row>
@@ -20030,29 +20030,29 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>coprodutor</t>
+          <t>protagonista</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>Coprodutor</t>
+          <t>Protagonista</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>viabilidade</t>
+          <t>papel_estud2</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>alta</t>
+          <t>coprodutor</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Coprodutor</t>
         </is>
       </c>
     </row>
@@ -20064,12 +20064,12 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>alta</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Alta</t>
         </is>
       </c>
     </row>
@@ -20081,12 +20081,12 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>baixa</t>
+          <t>media</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>Baixa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
@@ -20098,29 +20098,29 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>incerta</t>
+          <t>baixa</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>Incerta</t>
+          <t>Baixa</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>barr_impl</t>
+          <t>viabilidade</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>tempo</t>
+          <t>incerta</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>Tempo</t>
+          <t>Incerta</t>
         </is>
       </c>
     </row>
@@ -20132,12 +20132,12 @@
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>recursos</t>
+          <t>tempo</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>Recursos</t>
+          <t>Tempo</t>
         </is>
       </c>
     </row>
@@ -20149,12 +20149,12 @@
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>articulacao</t>
+          <t>recursos</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>Articulação</t>
+          <t>Recursos</t>
         </is>
       </c>
     </row>
@@ -20166,12 +20166,12 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>clima</t>
+          <t>articulacao</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>Clima</t>
+          <t>Articulação</t>
         </is>
       </c>
     </row>
@@ -20183,12 +20183,12 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>adesao</t>
+          <t>clima</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>Adesão</t>
+          <t>Clima</t>
         </is>
       </c>
     </row>
@@ -20200,29 +20200,29 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>adesao</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>Outra</t>
+          <t>Adesão</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>coerencia</t>
+          <t>barr_impl</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>coerente</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>Coerente</t>
+          <t>Outra</t>
         </is>
       </c>
     </row>
@@ -20234,12 +20234,12 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>parcialmente_coerente</t>
+          <t>coerente</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>Parcialmente coerente</t>
+          <t>Coerente</t>
         </is>
       </c>
     </row>
@@ -20251,29 +20251,29 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>nao_tenho_certeza</t>
+          <t>parcialmente_coerente</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>Não tenho certeza</t>
+          <t>Parcialmente coerente</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>com_final</t>
+          <t>coerencia</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>informar</t>
+          <t>nao_tenho_certeza</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>Informar</t>
+          <t>Não tenho certeza</t>
         </is>
       </c>
     </row>
@@ -20285,12 +20285,12 @@
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>sensibilizar</t>
+          <t>informar</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>Sensibilizar</t>
+          <t>Informar</t>
         </is>
       </c>
     </row>
@@ -20302,12 +20302,12 @@
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>mobilizar</t>
+          <t>sensibilizar</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>Mobilizar</t>
+          <t>Sensibilizar</t>
         </is>
       </c>
     </row>
@@ -20319,12 +20319,12 @@
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>prestar_contas</t>
+          <t>mobilizar</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>Prestar contas</t>
+          <t>Mobilizar</t>
         </is>
       </c>
     </row>
@@ -20336,12 +20336,12 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>dar_voz_a_comunidade</t>
+          <t>prestar_contas</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>Dar voz à comunidade</t>
+          <t>Prestar contas</t>
         </is>
       </c>
     </row>
@@ -20353,29 +20353,29 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>dar_voz_a_comunidade</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>Dar voz à comunidade</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>com_publico</t>
+          <t>com_final</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>estudantes</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>Estudantes</t>
+          <t>Outro</t>
         </is>
       </c>
     </row>
@@ -20387,12 +20387,12 @@
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>professores</t>
+          <t>estudantes</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>Professores(as)</t>
+          <t>Estudantes</t>
         </is>
       </c>
     </row>
@@ -20404,12 +20404,12 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>familias</t>
+          <t>professores</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>Famílias</t>
+          <t>Professores(as)</t>
         </is>
       </c>
     </row>
@@ -20421,12 +20421,12 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>comunidade</t>
+          <t>familias</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>Comunidade</t>
+          <t>Famílias</t>
         </is>
       </c>
     </row>
@@ -20438,12 +20438,12 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>poder_publico</t>
+          <t>comunidade</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>Poder público</t>
+          <t>Comunidade</t>
         </is>
       </c>
     </row>
@@ -20455,29 +20455,29 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>poder_publico</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>Poder público</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>com_escuta</t>
+          <t>com_publico</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>caixa_de_sugestoes</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>Caixa de sugestões</t>
+          <t>Outro</t>
         </is>
       </c>
     </row>
@@ -20489,12 +20489,12 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>roda_de_conversa</t>
+          <t>caixa_de_sugestoes</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>Roda de conversa</t>
+          <t>Caixa de sugestões</t>
         </is>
       </c>
     </row>
@@ -20506,12 +20506,12 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>formulario</t>
+          <t>roda_de_conversa</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>Formulário</t>
+          <t>Roda de conversa</t>
         </is>
       </c>
     </row>
@@ -20523,12 +20523,12 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>redes_sociais</t>
+          <t>formulario</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>Redes sociais</t>
+          <t>Formulário</t>
         </is>
       </c>
     </row>
@@ -20540,12 +20540,12 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>reuniao</t>
+          <t>redes_sociais</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>Reunião</t>
+          <t>Redes sociais</t>
         </is>
       </c>
     </row>
@@ -20557,29 +20557,29 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>reuniao</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>Reunião</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>com_midia</t>
+          <t>com_escuta</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>cartaz</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>Cartaz</t>
+          <t>Outro</t>
         </is>
       </c>
     </row>
@@ -20591,12 +20591,12 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>radio_escolar</t>
+          <t>cartaz</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>Rádio escolar</t>
+          <t>Cartaz</t>
         </is>
       </c>
     </row>
@@ -20608,12 +20608,12 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>video</t>
+          <t>radio_escolar</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>Vídeo</t>
+          <t>Rádio escolar</t>
         </is>
       </c>
     </row>
@@ -20625,12 +20625,12 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>redes_sociais</t>
+          <t>video</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>Redes sociais</t>
+          <t>Vídeo</t>
         </is>
       </c>
     </row>
@@ -20642,12 +20642,12 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>jornal_mural</t>
+          <t>redes_sociais</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>Jornal mural</t>
+          <t>Redes sociais</t>
         </is>
       </c>
     </row>
@@ -20659,12 +20659,12 @@
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>teatro</t>
+          <t>jornal_mural</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>Teatro</t>
+          <t>Jornal mural</t>
         </is>
       </c>
     </row>
@@ -20676,12 +20676,12 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>podcast</t>
+          <t>teatro</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>Podcast</t>
+          <t>Teatro</t>
         </is>
       </c>
     </row>
@@ -20693,29 +20693,29 @@
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>podcast</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>Podcast</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>com_barr</t>
+          <t>com_midia</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>idioma_linguagem_tecnica</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>Idioma/linguagem técnica</t>
+          <t>Outro</t>
         </is>
       </c>
     </row>
@@ -20727,12 +20727,12 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>acessibilidade_para_pessoas_com_</t>
+          <t>idioma_linguagem_tecnica</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>Acessibilidade para pessoas com deficiência</t>
+          <t>Idioma/linguagem técnica</t>
         </is>
       </c>
     </row>
@@ -20744,12 +20744,12 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>falta_de_conectividade</t>
+          <t>acessibilidade_para_pessoas_com_</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>Falta de conectividade</t>
+          <t>Acessibilidade para pessoas com deficiência</t>
         </is>
       </c>
     </row>
@@ -20761,12 +20761,12 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>alfabetizacao</t>
+          <t>falta_de_conectividade</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>Alfabetização</t>
+          <t>Falta de conectividade</t>
         </is>
       </c>
     </row>
@@ -20778,29 +20778,29 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>alfabetizacao</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>Outra</t>
+          <t>Alfabetização</t>
         </is>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>com_decisao</t>
+          <t>com_barr</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>nenhuma</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>Nenhuma</t>
+          <t>Outra</t>
         </is>
       </c>
     </row>
@@ -20812,12 +20812,12 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>sao_consultados</t>
+          <t>nenhuma</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>São consultados</t>
+          <t>Nenhuma</t>
         </is>
       </c>
     </row>
@@ -20829,12 +20829,12 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>colaboram_na_producao</t>
+          <t>sao_consultados</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>Colaboram na produção</t>
+          <t>São consultados</t>
         </is>
       </c>
     </row>
@@ -20846,29 +20846,29 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>decidem_conteudo_formato</t>
+          <t>colaboram_na_producao</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>Decidem conteúdo/formato</t>
+          <t>Colaboram na produção</t>
         </is>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>ind_tipo</t>
+          <t>com_decisao</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>processo</t>
+          <t>decidem_conteudo_formato</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>Processo</t>
+          <t>Decidem conteúdo/formato</t>
         </is>
       </c>
     </row>
@@ -20880,12 +20880,12 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>participacao</t>
+          <t>processo</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>Participação</t>
+          <t>Processo</t>
         </is>
       </c>
     </row>
@@ -20897,29 +20897,29 @@
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>resultado</t>
+          <t>participacao</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>Resultado</t>
+          <t>Participação</t>
         </is>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>periodicidade</t>
+          <t>ind_tipo</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>mensal</t>
+          <t>resultado</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>Mensal</t>
+          <t>Resultado</t>
         </is>
       </c>
     </row>
@@ -20931,12 +20931,12 @@
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>bimestral</t>
+          <t>mensal</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>Bimestral</t>
+          <t>Mensal</t>
         </is>
       </c>
     </row>
@@ -20948,12 +20948,12 @@
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>trimestral</t>
+          <t>bimestral</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>Trimestral</t>
+          <t>Bimestral</t>
         </is>
       </c>
     </row>
@@ -20965,12 +20965,12 @@
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>semestral</t>
+          <t>trimestral</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>Semestral</t>
+          <t>Trimestral</t>
         </is>
       </c>
     </row>
@@ -20982,12 +20982,12 @@
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>anual</t>
+          <t>semestral</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>Anual</t>
+          <t>Semestral</t>
         </is>
       </c>
     </row>
@@ -20999,29 +20999,29 @@
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>por_evento</t>
+          <t>anual</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>Por evento</t>
+          <t>Anual</t>
         </is>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>perfil_com</t>
+          <t>periodicidade</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>estudante</t>
+          <t>por_evento</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>Estudante</t>
+          <t>Por evento</t>
         </is>
       </c>
     </row>
@@ -21033,12 +21033,12 @@
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>ex_escola</t>
+          <t>estudante</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>Pessoa que já trabalhou em escola, mas atualmente não trabalha</t>
+          <t>Estudante</t>
         </is>
       </c>
     </row>
@@ -21050,12 +21050,12 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>ong</t>
+          <t>ex_escola</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>Pessoa de ONG ou outra organização da sociedade civil</t>
+          <t>Pessoa que já trabalhou em escola, mas atualmente não trabalha</t>
         </is>
       </c>
     </row>
@@ -21067,29 +21067,29 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>ong</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>Pessoa de ONG ou outra organização da sociedade civil</t>
         </is>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>nivel_estudo</t>
+          <t>perfil_com</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>ensino_fundamental</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>Ensino Fundamental</t>
+          <t>Outro</t>
         </is>
       </c>
     </row>
@@ -21101,12 +21101,12 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>ensino_medio</t>
+          <t>ensino_fundamental</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>Ensino Médio</t>
+          <t>Ensino Fundamental</t>
         </is>
       </c>
     </row>
@@ -21118,12 +21118,12 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>eja</t>
+          <t>ensino_medio</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>EJA</t>
+          <t>Ensino Médio</t>
         </is>
       </c>
     </row>
@@ -21135,12 +21135,12 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>ensino_tecnico_profissional</t>
+          <t>eja</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>Ensino técnico/profissional</t>
+          <t>EJA</t>
         </is>
       </c>
     </row>
@@ -21152,12 +21152,12 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>graduacao</t>
+          <t>ensino_tecnico_profissional</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>Graduação</t>
+          <t>Ensino técnico/profissional</t>
         </is>
       </c>
     </row>
@@ -21169,12 +21169,12 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>pos_graduacao</t>
+          <t>graduacao</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>Pós-graduação</t>
+          <t>Graduação</t>
         </is>
       </c>
     </row>
@@ -21186,29 +21186,29 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>pos_graduacao</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>Pós-graduação</t>
         </is>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>funcao_ex</t>
+          <t>nivel_estudo</t>
         </is>
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>professor</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>Professor(a)</t>
+          <t>Outro</t>
         </is>
       </c>
     </row>
@@ -21220,12 +21220,12 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>gestor_direcao</t>
+          <t>professor</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>Gestor(a) / Direção</t>
+          <t>Professor(a)</t>
         </is>
       </c>
     </row>
@@ -21237,12 +21237,12 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>coordenacao_supervisao_pedagogic</t>
+          <t>gestor_direcao</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>Coordenação / supervisão pedagógica</t>
+          <t>Gestor(a) / Direção</t>
         </is>
       </c>
     </row>
@@ -21254,12 +21254,12 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>apoio_escolar_funcionario</t>
+          <t>coordenacao_supervisao_pedagogic</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>Apoio escolar / funcionário(a)</t>
+          <t>Coordenação / supervisão pedagógica</t>
         </is>
       </c>
     </row>
@@ -21271,29 +21271,29 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>apoio_escolar_funcionario</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>Apoio escolar / funcionário(a)</t>
         </is>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>ong_area</t>
+          <t>funcao_ex</t>
         </is>
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>educacao</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>Educação</t>
+          <t>Outro</t>
         </is>
       </c>
     </row>
@@ -21305,12 +21305,12 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>meio_ambiente</t>
+          <t>educacao</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>Meio ambiente</t>
+          <t>Educação</t>
         </is>
       </c>
     </row>
@@ -21322,12 +21322,12 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>direitos_humanos</t>
+          <t>meio_ambiente</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>Direitos humanos</t>
+          <t>Meio ambiente</t>
         </is>
       </c>
     </row>
@@ -21339,12 +21339,12 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>saude</t>
+          <t>direitos_humanos</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>Saúde</t>
+          <t>Direitos humanos</t>
         </is>
       </c>
     </row>
@@ -21356,12 +21356,12 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>cultura</t>
+          <t>saude</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>Cultura</t>
+          <t>Saúde</t>
         </is>
       </c>
     </row>
@@ -21373,12 +21373,12 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>assistencia_social</t>
+          <t>cultura</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>Assistência social</t>
+          <t>Cultura</t>
         </is>
       </c>
     </row>
@@ -21390,12 +21390,12 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>povos_e_comunidades_tradicionais</t>
+          <t>assistencia_social</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>Povos e comunidades tradicionais</t>
+          <t>Assistência social</t>
         </is>
       </c>
     </row>
@@ -21407,29 +21407,29 @@
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>povos_e_comunidades_tradicionais</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>Povos e comunidades tradicionais</t>
         </is>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>vinculo_escola</t>
+          <t>ong_area</t>
         </is>
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>nenhum</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>Nenhum vínculo atual com escola</t>
+          <t>Outro</t>
         </is>
       </c>
     </row>
@@ -21441,12 +21441,12 @@
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>familiar_de_estudante</t>
+          <t>nenhum</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>Familiar de estudante</t>
+          <t>Nenhum vínculo atual com escola</t>
         </is>
       </c>
     </row>
@@ -21458,12 +21458,12 @@
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>ex_aluno</t>
+          <t>familiar_de_estudante</t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>Ex-aluno(a)</t>
+          <t>Familiar de estudante</t>
         </is>
       </c>
     </row>
@@ -21475,12 +21475,12 @@
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>voluntario_ou_parceiro_de_escola</t>
+          <t>ex_aluno</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>Voluntário(a) ou parceiro(a) de escola</t>
+          <t>Ex-aluno(a)</t>
         </is>
       </c>
     </row>
@@ -21492,12 +21492,12 @@
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>atuo_em_projetos_em_escolas_por_</t>
+          <t>voluntario_ou_parceiro_de_escola</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>Atuo em projetos em escolas por meio de organização</t>
+          <t>Voluntário(a) ou parceiro(a) de escola</t>
         </is>
       </c>
     </row>
@@ -21509,29 +21509,29 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>atuo_em_projetos_em_escolas_por_</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>Atuo em projetos em escolas por meio de organização</t>
         </is>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>onde_ea_com</t>
+          <t>vinculo_escola</t>
         </is>
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>escolas_do_territorio</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>Escolas do território</t>
+          <t>Outro</t>
         </is>
       </c>
     </row>
@@ -21543,12 +21543,12 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>associacoes_ongs</t>
+          <t>escolas_do_territorio</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>Associações / ONGs</t>
+          <t>Escolas do território</t>
         </is>
       </c>
     </row>
@@ -21560,12 +21560,12 @@
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>mutiroes_e_acoes_comunitarias</t>
+          <t>associacoes_ongs</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>Mutirões e ações comunitárias</t>
+          <t>Associações / ONGs</t>
         </is>
       </c>
     </row>
@@ -21577,12 +21577,12 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>igrejas_grupos_religiosos</t>
+          <t>mutiroes_e_acoes_comunitarias</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>Igrejas / grupos religiosos</t>
+          <t>Mutirões e ações comunitárias</t>
         </is>
       </c>
     </row>
@@ -21594,12 +21594,12 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>coletivos_e_grupos_de_jovens</t>
+          <t>igrejas_grupos_religiosos</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>Coletivos e grupos de jovens</t>
+          <t>Igrejas / grupos religiosos</t>
         </is>
       </c>
     </row>
@@ -21611,12 +21611,12 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>universidades_institutos</t>
+          <t>coletivos_e_grupos_de_jovens</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>Universidades / institutos</t>
+          <t>Coletivos e grupos de jovens</t>
         </is>
       </c>
     </row>
@@ -21628,12 +21628,12 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>rodas_de_conversa_e_oficinas</t>
+          <t>universidades_institutos</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>Rodas de conversa e oficinas</t>
+          <t>Universidades / institutos</t>
         </is>
       </c>
     </row>
@@ -21645,12 +21645,12 @@
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>redes_sociais_comunicacao</t>
+          <t>rodas_de_conversa_e_oficinas</t>
         </is>
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>Redes sociais / comunicação</t>
+          <t>Rodas de conversa e oficinas</t>
         </is>
       </c>
     </row>
@@ -21662,12 +21662,12 @@
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>nao_acontece</t>
+          <t>redes_sociais_comunicacao</t>
         </is>
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>Não acontece</t>
+          <t>Redes sociais / comunicação</t>
         </is>
       </c>
     </row>
@@ -21679,29 +21679,29 @@
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>nao_acontece</t>
         </is>
       </c>
       <c r="C483" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>Não acontece</t>
         </is>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>instit_com</t>
+          <t>onde_ea_com</t>
         </is>
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>inexistente</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>Inexistente</t>
+          <t>Outro</t>
         </is>
       </c>
     </row>
@@ -21713,12 +21713,12 @@
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>isolada_ocasional</t>
+          <t>inexistente</t>
         </is>
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>Isolada/ocasional</t>
+          <t>Inexistente</t>
         </is>
       </c>
     </row>
@@ -21730,12 +21730,12 @@
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>recorrente_dependente_de_poucas_</t>
+          <t>isolada_ocasional</t>
         </is>
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>Recorrente, dependente de poucas pessoas</t>
+          <t>Isolada/ocasional</t>
         </is>
       </c>
     </row>
@@ -21747,12 +21747,12 @@
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>presente_em_diferentes_grupos_or</t>
+          <t>recorrente_dependente_de_poucas_</t>
         </is>
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>Presente em diferentes grupos/organizações</t>
+          <t>Recorrente, dependente de poucas pessoas</t>
         </is>
       </c>
     </row>
@@ -21764,12 +21764,12 @@
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>integrada_as_acoes_da_comunidade</t>
+          <t>presente_em_diferentes_grupos_or</t>
         </is>
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>Integrada às ações da comunidade</t>
+          <t>Presente em diferentes grupos/organizações</t>
         </is>
       </c>
     </row>
@@ -21781,12 +21781,12 @@
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>continua_e_reconhecida_pela_comu</t>
+          <t>integrada_as_acoes_da_comunidade</t>
         </is>
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>Contínua e reconhecida pela comunidade</t>
+          <t>Integrada às ações da comunidade</t>
         </is>
       </c>
     </row>
@@ -21798,29 +21798,29 @@
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>nao_sabe</t>
+          <t>continua_e_reconhecida_pela_comu</t>
         </is>
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>Não sabe</t>
+          <t>Contínua e reconhecida pela comunidade</t>
         </is>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>esc_territorio</t>
+          <t>instit_com</t>
         </is>
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>sim_com_frequencia</t>
+          <t>nao_sabe</t>
         </is>
       </c>
       <c r="C491" t="inlineStr">
         <is>
-          <t>Sim, com frequência</t>
+          <t>Não sabe</t>
         </is>
       </c>
     </row>
@@ -21832,12 +21832,12 @@
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>as_vezes</t>
+          <t>sim_com_frequencia</t>
         </is>
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>Às vezes</t>
+          <t>Sim, com frequência</t>
         </is>
       </c>
     </row>
@@ -21849,12 +21849,12 @@
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>raramente</t>
+          <t>as_vezes</t>
         </is>
       </c>
       <c r="C493" t="inlineStr">
         <is>
-          <t>Raramente</t>
+          <t>Às vezes</t>
         </is>
       </c>
     </row>
@@ -21866,12 +21866,12 @@
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>nao</t>
+          <t>raramente</t>
         </is>
       </c>
       <c r="C494" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Raramente</t>
         </is>
       </c>
     </row>
@@ -21883,12 +21883,12 @@
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>nao_existe_escola_no_territorio</t>
+          <t>nao</t>
         </is>
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>Não existe escola no território</t>
+          <t>Não</t>
         </is>
       </c>
     </row>
@@ -21900,29 +21900,29 @@
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>nao_sei</t>
+          <t>nao_existe_escola_no_territorio</t>
         </is>
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>Não sei</t>
+          <t>Não existe escola no território</t>
         </is>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>contexto_ea_com</t>
+          <t>esc_territorio</t>
         </is>
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>escola</t>
+          <t>nao_sei</t>
         </is>
       </c>
       <c r="C497" t="inlineStr">
         <is>
-          <t>Escola</t>
+          <t>Não sei</t>
         </is>
       </c>
     </row>
@@ -21934,12 +21934,12 @@
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>espaco_comunitario_associacao</t>
+          <t>escola</t>
         </is>
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>Espaço comunitário / associação</t>
+          <t>Escola</t>
         </is>
       </c>
     </row>
@@ -21951,12 +21951,12 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>rua_praca_ou_area_externa</t>
+          <t>espaco_comunitario_associacao</t>
         </is>
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>Rua, praça ou área externa</t>
+          <t>Espaço comunitário / associação</t>
         </is>
       </c>
     </row>
@@ -21968,12 +21968,12 @@
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>visita_de_campo_trilha</t>
+          <t>rua_praca_ou_area_externa</t>
         </is>
       </c>
       <c r="C500" t="inlineStr">
         <is>
-          <t>Visita de campo / trilha</t>
+          <t>Rua, praça ou área externa</t>
         </is>
       </c>
     </row>
@@ -21985,12 +21985,12 @@
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>evento_feira</t>
+          <t>visita_de_campo_trilha</t>
         </is>
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>Evento / feira</t>
+          <t>Visita de campo / trilha</t>
         </is>
       </c>
     </row>
@@ -22002,12 +22002,12 @@
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>online_redes_sociais</t>
+          <t>evento_feira</t>
         </is>
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>Online / redes sociais</t>
+          <t>Evento / feira</t>
         </is>
       </c>
     </row>
@@ -22019,29 +22019,29 @@
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>online_redes_sociais</t>
         </is>
       </c>
       <c r="C503" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>Online / redes sociais</t>
         </is>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>quem_planejou_com</t>
+          <t>contexto_ea_com</t>
         </is>
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>estudantes</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C504" t="inlineStr">
         <is>
-          <t>Estudantes</t>
+          <t>Outro</t>
         </is>
       </c>
     </row>
@@ -22053,12 +22053,12 @@
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>professores</t>
+          <t>estudantes</t>
         </is>
       </c>
       <c r="C505" t="inlineStr">
         <is>
-          <t>Professores(as)</t>
+          <t>Estudantes</t>
         </is>
       </c>
     </row>
@@ -22070,12 +22070,12 @@
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>associacao_ong</t>
+          <t>professores</t>
         </is>
       </c>
       <c r="C506" t="inlineStr">
         <is>
-          <t>Associação / ONG</t>
+          <t>Professores(as)</t>
         </is>
       </c>
     </row>
@@ -22087,12 +22087,12 @@
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>liderancas_comunitarias</t>
+          <t>associacao_ong</t>
         </is>
       </c>
       <c r="C507" t="inlineStr">
         <is>
-          <t>Lideranças comunitárias</t>
+          <t>Associação / ONG</t>
         </is>
       </c>
     </row>
@@ -22104,12 +22104,12 @@
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>poder_publico</t>
+          <t>liderancas_comunitarias</t>
         </is>
       </c>
       <c r="C508" t="inlineStr">
         <is>
-          <t>Poder público</t>
+          <t>Lideranças comunitárias</t>
         </is>
       </c>
     </row>
@@ -22121,12 +22121,12 @@
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>universidade_instituto</t>
+          <t>poder_publico</t>
         </is>
       </c>
       <c r="C509" t="inlineStr">
         <is>
-          <t>Universidade / instituto</t>
+          <t>Poder público</t>
         </is>
       </c>
     </row>
@@ -22138,12 +22138,12 @@
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>moradores_em_geral</t>
+          <t>universidade_instituto</t>
         </is>
       </c>
       <c r="C510" t="inlineStr">
         <is>
-          <t>Moradores em geral</t>
+          <t>Universidade / instituto</t>
         </is>
       </c>
     </row>
@@ -22155,29 +22155,29 @@
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>moradores_em_geral</t>
         </is>
       </c>
       <c r="C511" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>Moradores em geral</t>
         </is>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>continuidade_com</t>
+          <t>quem_planejou_com</t>
         </is>
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>depende_de_pessoas_especificas</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C512" t="inlineStr">
         <is>
-          <t>Depende de pessoas específicas</t>
+          <t>Outro</t>
         </is>
       </c>
     </row>
@@ -22189,12 +22189,12 @@
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>garantida</t>
+          <t>depende_de_pessoas_especificas</t>
         </is>
       </c>
       <c r="C513" t="inlineStr">
         <is>
-          <t>Tem continuidade garantida (organização ou parceria)</t>
+          <t>Depende de pessoas específicas</t>
         </is>
       </c>
     </row>
@@ -22206,12 +22206,12 @@
       </c>
       <c r="B514" t="inlineStr">
         <is>
-          <t>incerta</t>
+          <t>garantida</t>
         </is>
       </c>
       <c r="C514" t="inlineStr">
         <is>
-          <t>Incerta</t>
+          <t>Tem continuidade garantida (organização ou parceria)</t>
         </is>
       </c>
     </row>
@@ -22223,29 +22223,29 @@
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>nao_sabe</t>
+          <t>incerta</t>
         </is>
       </c>
       <c r="C515" t="inlineStr">
         <is>
-          <t>Não sabe</t>
+          <t>Incerta</t>
         </is>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>causa_dif_com</t>
+          <t>continuidade_com</t>
         </is>
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>falta_de_formacao</t>
+          <t>nao_sabe</t>
         </is>
       </c>
       <c r="C516" t="inlineStr">
         <is>
-          <t>Falta de formação</t>
+          <t>Não sabe</t>
         </is>
       </c>
     </row>
@@ -22257,12 +22257,12 @@
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>falta_de_material</t>
+          <t>falta_de_formacao</t>
         </is>
       </c>
       <c r="C517" t="inlineStr">
         <is>
-          <t>Falta de material</t>
+          <t>Falta de formação</t>
         </is>
       </c>
     </row>
@@ -22274,12 +22274,12 @@
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>tema_sensivel_delicado</t>
+          <t>falta_de_material</t>
         </is>
       </c>
       <c r="C518" t="inlineStr">
         <is>
-          <t>Tema sensível/delicado</t>
+          <t>Falta de material</t>
         </is>
       </c>
     </row>
@@ -22291,12 +22291,12 @@
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>falta_de_tempo</t>
+          <t>tema_sensivel_delicado</t>
         </is>
       </c>
       <c r="C519" t="inlineStr">
         <is>
-          <t>Falta de tempo</t>
+          <t>Tema sensível/delicado</t>
         </is>
       </c>
     </row>
@@ -22308,12 +22308,12 @@
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>falta_de_apoio_ou_recursos</t>
+          <t>falta_de_tempo</t>
         </is>
       </c>
       <c r="C520" t="inlineStr">
         <is>
-          <t>Falta de apoio ou recursos</t>
+          <t>Falta de tempo</t>
         </is>
       </c>
     </row>
@@ -22325,29 +22325,29 @@
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>falta_de_apoio_ou_recursos</t>
         </is>
       </c>
       <c r="C521" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>Falta de apoio ou recursos</t>
         </is>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>apoio_com</t>
+          <t>causa_dif_com</t>
         </is>
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>formacao</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C522" t="inlineStr">
         <is>
-          <t>Formação</t>
+          <t>Outro</t>
         </is>
       </c>
     </row>
@@ -22359,12 +22359,12 @@
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>material_educativo</t>
+          <t>formacao</t>
         </is>
       </c>
       <c r="C523" t="inlineStr">
         <is>
-          <t>Material educativo</t>
+          <t>Formação</t>
         </is>
       </c>
     </row>
@@ -22376,12 +22376,12 @@
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>tempo_para_se_organizar</t>
+          <t>material_educativo</t>
         </is>
       </c>
       <c r="C524" t="inlineStr">
         <is>
-          <t>Tempo para se organizar</t>
+          <t>Material educativo</t>
         </is>
       </c>
     </row>
@@ -22393,12 +22393,12 @@
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>apoio_de_liderancas_poder_public</t>
+          <t>tempo_para_se_organizar</t>
         </is>
       </c>
       <c r="C525" t="inlineStr">
         <is>
-          <t>Apoio de lideranças / poder público</t>
+          <t>Tempo para se organizar</t>
         </is>
       </c>
     </row>
@@ -22410,12 +22410,12 @@
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>parcerias</t>
+          <t>apoio_de_liderancas_poder_public</t>
         </is>
       </c>
       <c r="C526" t="inlineStr">
         <is>
-          <t>Parcerias</t>
+          <t>Apoio de lideranças / poder público</t>
         </is>
       </c>
     </row>
@@ -22427,12 +22427,12 @@
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>recursos_financeiros</t>
+          <t>parcerias</t>
         </is>
       </c>
       <c r="C527" t="inlineStr">
         <is>
-          <t>Recursos financeiros</t>
+          <t>Parcerias</t>
         </is>
       </c>
     </row>
@@ -22444,29 +22444,29 @@
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>recursos_financeiros</t>
         </is>
       </c>
       <c r="C528" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>Recursos financeiros</t>
         </is>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>barreiras_com</t>
+          <t>apoio_com</t>
         </is>
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>tempo</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C529" t="inlineStr">
         <is>
-          <t>Tempo</t>
+          <t>Outro</t>
         </is>
       </c>
     </row>
@@ -22478,12 +22478,12 @@
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>formacao</t>
+          <t>tempo</t>
         </is>
       </c>
       <c r="C530" t="inlineStr">
         <is>
-          <t>Formação</t>
+          <t>Tempo</t>
         </is>
       </c>
     </row>
@@ -22495,12 +22495,12 @@
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>materiais</t>
+          <t>formacao</t>
         </is>
       </c>
       <c r="C531" t="inlineStr">
         <is>
-          <t>Materiais</t>
+          <t>Formação</t>
         </is>
       </c>
     </row>
@@ -22512,12 +22512,12 @@
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>recursos_financeiros</t>
+          <t>materiais</t>
         </is>
       </c>
       <c r="C532" t="inlineStr">
         <is>
-          <t>Recursos financeiros</t>
+          <t>Materiais</t>
         </is>
       </c>
     </row>
@@ -22529,12 +22529,12 @@
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>apoio_do_poder_publico</t>
+          <t>recursos_financeiros</t>
         </is>
       </c>
       <c r="C533" t="inlineStr">
         <is>
-          <t>Apoio do poder público</t>
+          <t>Recursos financeiros</t>
         </is>
       </c>
     </row>
@@ -22546,12 +22546,12 @@
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>apoio_de_liderancas</t>
+          <t>apoio_do_poder_publico</t>
         </is>
       </c>
       <c r="C534" t="inlineStr">
         <is>
-          <t>Apoio de lideranças</t>
+          <t>Apoio do poder público</t>
         </is>
       </c>
     </row>
@@ -22563,12 +22563,12 @@
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>organizacao_coletiva_planejament</t>
+          <t>apoio_de_liderancas</t>
         </is>
       </c>
       <c r="C535" t="inlineStr">
         <is>
-          <t>Organização coletiva / planejamento conjunto</t>
+          <t>Apoio de lideranças</t>
         </is>
       </c>
     </row>
@@ -22580,12 +22580,12 @@
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>informacoes_sobre_o_territorio</t>
+          <t>organizacao_coletiva_planejament</t>
         </is>
       </c>
       <c r="C536" t="inlineStr">
         <is>
-          <t>Informações sobre o território</t>
+          <t>Organização coletiva / planejamento conjunto</t>
         </is>
       </c>
     </row>
@@ -22597,12 +22597,12 @@
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>descontinuidade_das_acoes</t>
+          <t>informacoes_sobre_o_territorio</t>
         </is>
       </c>
       <c r="C537" t="inlineStr">
         <is>
-          <t>Descontinuidade das ações</t>
+          <t>Informações sobre o território</t>
         </is>
       </c>
     </row>
@@ -22614,12 +22614,12 @@
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>rotatividade_de_pessoas</t>
+          <t>descontinuidade_das_acoes</t>
         </is>
       </c>
       <c r="C538" t="inlineStr">
         <is>
-          <t>Rotatividade de pessoas</t>
+          <t>Descontinuidade das ações</t>
         </is>
       </c>
     </row>
@@ -22631,29 +22631,29 @@
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>rotatividade_de_pessoas</t>
         </is>
       </c>
       <c r="C539" t="inlineStr">
         <is>
-          <t>Outras</t>
+          <t>Rotatividade de pessoas</t>
         </is>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
         <is>
-          <t>materiais_com</t>
+          <t>barreiras_com</t>
         </is>
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>livros_e_cartilhas</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C540" t="inlineStr">
         <is>
-          <t>Livros e cartilhas</t>
+          <t>Outras</t>
         </is>
       </c>
     </row>
@@ -22665,12 +22665,12 @@
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>videos</t>
+          <t>livros_e_cartilhas</t>
         </is>
       </c>
       <c r="C541" t="inlineStr">
         <is>
-          <t>Vídeos</t>
+          <t>Livros e cartilhas</t>
         </is>
       </c>
     </row>
@@ -22682,12 +22682,12 @@
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>jogos</t>
+          <t>videos</t>
         </is>
       </c>
       <c r="C542" t="inlineStr">
         <is>
-          <t>Jogos</t>
+          <t>Vídeos</t>
         </is>
       </c>
     </row>
@@ -22699,12 +22699,12 @@
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>materiais_produzidos_pela_comuni</t>
+          <t>jogos</t>
         </is>
       </c>
       <c r="C543" t="inlineStr">
         <is>
-          <t>Materiais produzidos pela comunidade/organização</t>
+          <t>Jogos</t>
         </is>
       </c>
     </row>
@@ -22716,12 +22716,12 @@
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>recursos_digitais</t>
+          <t>materiais_produzidos_pela_comuni</t>
         </is>
       </c>
       <c r="C544" t="inlineStr">
         <is>
-          <t>Recursos digitais</t>
+          <t>Materiais produzidos pela comunidade/organização</t>
         </is>
       </c>
     </row>
@@ -22733,12 +22733,12 @@
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>nenhum</t>
+          <t>recursos_digitais</t>
         </is>
       </c>
       <c r="C545" t="inlineStr">
         <is>
-          <t>Nenhum</t>
+          <t>Recursos digitais</t>
         </is>
       </c>
     </row>
@@ -22750,29 +22750,29 @@
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>nenhum</t>
         </is>
       </c>
       <c r="C546" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>Nenhum</t>
         </is>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="inlineStr">
         <is>
-          <t>quem_part_com</t>
+          <t>materiais_com</t>
         </is>
       </c>
       <c r="B547" t="inlineStr">
         <is>
-          <t>estudantes</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C547" t="inlineStr">
         <is>
-          <t>Estudantes</t>
+          <t>Outro</t>
         </is>
       </c>
     </row>
@@ -22784,12 +22784,12 @@
       </c>
       <c r="B548" t="inlineStr">
         <is>
-          <t>professores</t>
+          <t>estudantes</t>
         </is>
       </c>
       <c r="C548" t="inlineStr">
         <is>
-          <t>Professores(as)</t>
+          <t>Estudantes</t>
         </is>
       </c>
     </row>
@@ -22801,12 +22801,12 @@
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>familias</t>
+          <t>professores</t>
         </is>
       </c>
       <c r="C549" t="inlineStr">
         <is>
-          <t>Famílias</t>
+          <t>Professores(as)</t>
         </is>
       </c>
     </row>
@@ -22818,12 +22818,12 @@
       </c>
       <c r="B550" t="inlineStr">
         <is>
-          <t>moradores</t>
+          <t>familias</t>
         </is>
       </c>
       <c r="C550" t="inlineStr">
         <is>
-          <t>Moradores</t>
+          <t>Famílias</t>
         </is>
       </c>
     </row>
@@ -22835,12 +22835,12 @@
       </c>
       <c r="B551" t="inlineStr">
         <is>
-          <t>liderancas_comunitarias</t>
+          <t>moradores</t>
         </is>
       </c>
       <c r="C551" t="inlineStr">
         <is>
-          <t>Lideranças comunitárias</t>
+          <t>Moradores</t>
         </is>
       </c>
     </row>
@@ -22852,12 +22852,12 @@
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>associacoes_ongs</t>
+          <t>liderancas_comunitarias</t>
         </is>
       </c>
       <c r="C552" t="inlineStr">
         <is>
-          <t>Associações / ONGs</t>
+          <t>Lideranças comunitárias</t>
         </is>
       </c>
     </row>
@@ -22869,12 +22869,12 @@
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>poder_publico</t>
+          <t>associacoes_ongs</t>
         </is>
       </c>
       <c r="C553" t="inlineStr">
         <is>
-          <t>Poder público</t>
+          <t>Associações / ONGs</t>
         </is>
       </c>
     </row>
@@ -22886,29 +22886,29 @@
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>poder_publico</t>
         </is>
       </c>
       <c r="C554" t="inlineStr">
         <is>
-          <t>Outros</t>
+          <t>Poder público</t>
         </is>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
-          <t>esp_com</t>
+          <t>quem_part_com</t>
         </is>
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>associacao_de_moradores</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C555" t="inlineStr">
         <is>
-          <t>Associação de moradores</t>
+          <t>Outros</t>
         </is>
       </c>
     </row>
@@ -22920,12 +22920,12 @@
       </c>
       <c r="B556" t="inlineStr">
         <is>
-          <t>conselho_comunitario</t>
+          <t>associacao_de_moradores</t>
         </is>
       </c>
       <c r="C556" t="inlineStr">
         <is>
-          <t>Conselho comunitário</t>
+          <t>Associação de moradores</t>
         </is>
       </c>
     </row>
@@ -22937,12 +22937,12 @@
       </c>
       <c r="B557" t="inlineStr">
         <is>
-          <t>assembleias_reunioes_comunitaria</t>
+          <t>conselho_comunitario</t>
         </is>
       </c>
       <c r="C557" t="inlineStr">
         <is>
-          <t>Assembleias / reuniões comunitárias</t>
+          <t>Conselho comunitário</t>
         </is>
       </c>
     </row>
@@ -22954,12 +22954,12 @@
       </c>
       <c r="B558" t="inlineStr">
         <is>
-          <t>gremio_estudantil_coletivos_de_j</t>
+          <t>assembleias_reunioes_comunitaria</t>
         </is>
       </c>
       <c r="C558" t="inlineStr">
         <is>
-          <t>Grêmio estudantil / coletivos de jovens</t>
+          <t>Assembleias / reuniões comunitárias</t>
         </is>
       </c>
     </row>
@@ -22971,12 +22971,12 @@
       </c>
       <c r="B559" t="inlineStr">
         <is>
-          <t>conselhos_de_politicas_publicas</t>
+          <t>gremio_estudantil_coletivos_de_j</t>
         </is>
       </c>
       <c r="C559" t="inlineStr">
         <is>
-          <t>Conselhos de políticas públicas</t>
+          <t>Grêmio estudantil / coletivos de jovens</t>
         </is>
       </c>
     </row>
@@ -22988,12 +22988,12 @@
       </c>
       <c r="B560" t="inlineStr">
         <is>
-          <t>nenhum</t>
+          <t>conselhos_de_politicas_publicas</t>
         </is>
       </c>
       <c r="C560" t="inlineStr">
         <is>
-          <t>Nenhum</t>
+          <t>Conselhos de políticas públicas</t>
         </is>
       </c>
     </row>
@@ -23005,29 +23005,29 @@
       </c>
       <c r="B561" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>nenhum</t>
         </is>
       </c>
       <c r="C561" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>Nenhum</t>
         </is>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="inlineStr">
         <is>
-          <t>instancias_com</t>
+          <t>esp_com</t>
         </is>
       </c>
       <c r="B562" t="inlineStr">
         <is>
-          <t>associacao_de_moradores</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C562" t="inlineStr">
         <is>
-          <t>Associação de moradores</t>
+          <t>Outro</t>
         </is>
       </c>
     </row>
@@ -23039,12 +23039,12 @@
       </c>
       <c r="B563" t="inlineStr">
         <is>
-          <t>conselho_comunitario</t>
+          <t>associacao_de_moradores</t>
         </is>
       </c>
       <c r="C563" t="inlineStr">
         <is>
-          <t>Conselho comunitário</t>
+          <t>Associação de moradores</t>
         </is>
       </c>
     </row>
@@ -23056,12 +23056,12 @@
       </c>
       <c r="B564" t="inlineStr">
         <is>
-          <t>conselho_escolar</t>
+          <t>conselho_comunitario</t>
         </is>
       </c>
       <c r="C564" t="inlineStr">
         <is>
-          <t>Conselho escolar</t>
+          <t>Conselho comunitário</t>
         </is>
       </c>
     </row>
@@ -23073,12 +23073,12 @@
       </c>
       <c r="B565" t="inlineStr">
         <is>
-          <t>conselhos_de_politicas_publicas</t>
+          <t>conselho_escolar</t>
         </is>
       </c>
       <c r="C565" t="inlineStr">
         <is>
-          <t>Conselhos de políticas públicas</t>
+          <t>Conselho escolar</t>
         </is>
       </c>
     </row>
@@ -23090,12 +23090,12 @@
       </c>
       <c r="B566" t="inlineStr">
         <is>
-          <t>gremio_coletivos</t>
+          <t>conselhos_de_politicas_publicas</t>
         </is>
       </c>
       <c r="C566" t="inlineStr">
         <is>
-          <t>Grêmio / coletivos</t>
+          <t>Conselhos de políticas públicas</t>
         </is>
       </c>
     </row>
@@ -23107,12 +23107,12 @@
       </c>
       <c r="B567" t="inlineStr">
         <is>
-          <t>nenhuma</t>
+          <t>gremio_coletivos</t>
         </is>
       </c>
       <c r="C567" t="inlineStr">
         <is>
-          <t>Nenhuma</t>
+          <t>Grêmio / coletivos</t>
         </is>
       </c>
     </row>
@@ -23124,29 +23124,29 @@
       </c>
       <c r="B568" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>nenhuma</t>
         </is>
       </c>
       <c r="C568" t="inlineStr">
         <is>
-          <t>Outra</t>
+          <t>Nenhuma</t>
         </is>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="inlineStr">
         <is>
-          <t>impacto_alag_com</t>
+          <t>instancias_com</t>
         </is>
       </c>
       <c r="B569" t="inlineStr">
         <is>
-          <t>danos_as_moradias</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C569" t="inlineStr">
         <is>
-          <t>Danos às moradias</t>
+          <t>Outra</t>
         </is>
       </c>
     </row>
@@ -23158,12 +23158,12 @@
       </c>
       <c r="B570" t="inlineStr">
         <is>
-          <t>danos_a_ruas_estradas_ou_pontes</t>
+          <t>danos_as_moradias</t>
         </is>
       </c>
       <c r="C570" t="inlineStr">
         <is>
-          <t>Danos a ruas, estradas ou pontes</t>
+          <t>Danos às moradias</t>
         </is>
       </c>
     </row>
@@ -23175,12 +23175,12 @@
       </c>
       <c r="B571" t="inlineStr">
         <is>
-          <t>acesso_interrompido</t>
+          <t>danos_a_ruas_estradas_ou_pontes</t>
         </is>
       </c>
       <c r="C571" t="inlineStr">
         <is>
-          <t>Acesso interrompido (trabalho, escola, saúde)</t>
+          <t>Danos a ruas, estradas ou pontes</t>
         </is>
       </c>
     </row>
@@ -23192,12 +23192,12 @@
       </c>
       <c r="B572" t="inlineStr">
         <is>
-          <t>contaminacao_da_agua</t>
+          <t>acesso_interrompido</t>
         </is>
       </c>
       <c r="C572" t="inlineStr">
         <is>
-          <t>Contaminação da água</t>
+          <t>Acesso interrompido (trabalho, escola, saúde)</t>
         </is>
       </c>
     </row>
@@ -23209,12 +23209,12 @@
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>perda_de_bens_ou_plantacoes</t>
+          <t>contaminacao_da_agua</t>
         </is>
       </c>
       <c r="C573" t="inlineStr">
         <is>
-          <t>Perda de bens ou plantações</t>
+          <t>Contaminação da água</t>
         </is>
       </c>
     </row>
@@ -23226,12 +23226,12 @@
       </c>
       <c r="B574" t="inlineStr">
         <is>
-          <t>impacto_na_saude</t>
+          <t>perda_de_bens_ou_plantacoes</t>
         </is>
       </c>
       <c r="C574" t="inlineStr">
         <is>
-          <t>Impacto na saúde</t>
+          <t>Perda de bens ou plantações</t>
         </is>
       </c>
     </row>
@@ -23243,12 +23243,12 @@
       </c>
       <c r="B575" t="inlineStr">
         <is>
-          <t>interrupcao_de_aulas</t>
+          <t>impacto_na_saude</t>
         </is>
       </c>
       <c r="C575" t="inlineStr">
         <is>
-          <t>Interrupção de aulas</t>
+          <t>Impacto na saúde</t>
         </is>
       </c>
     </row>
@@ -23260,29 +23260,29 @@
       </c>
       <c r="B576" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>interrupcao_de_aulas</t>
         </is>
       </c>
       <c r="C576" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>Interrupção de aulas</t>
         </is>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="inlineStr">
         <is>
-          <t>impacto_clima_com</t>
+          <t>impacto_alag_com</t>
         </is>
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>danos_materiais</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C577" t="inlineStr">
         <is>
-          <t>Danos materiais</t>
+          <t>Outro</t>
         </is>
       </c>
     </row>
@@ -23294,12 +23294,12 @@
       </c>
       <c r="B578" t="inlineStr">
         <is>
-          <t>deslocamento_de_pessoas</t>
+          <t>danos_materiais</t>
         </is>
       </c>
       <c r="C578" t="inlineStr">
         <is>
-          <t>Deslocamento de pessoas (necessidade de migração)</t>
+          <t>Danos materiais</t>
         </is>
       </c>
     </row>
@@ -23311,12 +23311,12 @@
       </c>
       <c r="B579" t="inlineStr">
         <is>
-          <t>obitos</t>
+          <t>deslocamento_de_pessoas</t>
         </is>
       </c>
       <c r="C579" t="inlineStr">
         <is>
-          <t>Óbitos</t>
+          <t>Deslocamento de pessoas (necessidade de migração)</t>
         </is>
       </c>
     </row>
@@ -23328,12 +23328,12 @@
       </c>
       <c r="B580" t="inlineStr">
         <is>
-          <t>perda_de_renda_ou_plantacoes</t>
+          <t>obitos</t>
         </is>
       </c>
       <c r="C580" t="inlineStr">
         <is>
-          <t>Perda de renda ou plantações</t>
+          <t>Óbitos</t>
         </is>
       </c>
     </row>
@@ -23345,12 +23345,12 @@
       </c>
       <c r="B581" t="inlineStr">
         <is>
-          <t>impacto_na_saude</t>
+          <t>perda_de_renda_ou_plantacoes</t>
         </is>
       </c>
       <c r="C581" t="inlineStr">
         <is>
-          <t>Impacto na saúde</t>
+          <t>Perda de renda ou plantações</t>
         </is>
       </c>
     </row>
@@ -23362,12 +23362,12 @@
       </c>
       <c r="B582" t="inlineStr">
         <is>
-          <t>impacto_emocional</t>
+          <t>impacto_na_saude</t>
         </is>
       </c>
       <c r="C582" t="inlineStr">
         <is>
-          <t>Impacto emocional</t>
+          <t>Impacto na saúde</t>
         </is>
       </c>
     </row>
@@ -23379,12 +23379,12 @@
       </c>
       <c r="B583" t="inlineStr">
         <is>
-          <t>interrupcao_de_aulas_ou_do_traba</t>
+          <t>impacto_emocional</t>
         </is>
       </c>
       <c r="C583" t="inlineStr">
         <is>
-          <t>Interrupção de aulas ou do trabalho</t>
+          <t>Impacto emocional</t>
         </is>
       </c>
     </row>
@@ -23396,29 +23396,29 @@
       </c>
       <c r="B584" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>interrupcao_de_aulas_ou_do_traba</t>
         </is>
       </c>
       <c r="C584" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>Interrupção de aulas ou do trabalho</t>
         </is>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="inlineStr">
         <is>
-          <t>impacto_risco_com</t>
+          <t>impacto_clima_com</t>
         </is>
       </c>
       <c r="B585" t="inlineStr">
         <is>
-          <t>danos_as_moradias</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C585" t="inlineStr">
         <is>
-          <t>Danos às moradias</t>
+          <t>Outro</t>
         </is>
       </c>
     </row>
@@ -23430,12 +23430,12 @@
       </c>
       <c r="B586" t="inlineStr">
         <is>
-          <t>acesso_interrompido</t>
+          <t>danos_as_moradias</t>
         </is>
       </c>
       <c r="C586" t="inlineStr">
         <is>
-          <t>Acesso interrompido</t>
+          <t>Danos às moradias</t>
         </is>
       </c>
     </row>
@@ -23447,12 +23447,12 @@
       </c>
       <c r="B587" t="inlineStr">
         <is>
-          <t>perda_de_bens_materiais</t>
+          <t>acesso_interrompido</t>
         </is>
       </c>
       <c r="C587" t="inlineStr">
         <is>
-          <t>Perda de bens/materiais</t>
+          <t>Acesso interrompido</t>
         </is>
       </c>
     </row>
@@ -23464,12 +23464,12 @@
       </c>
       <c r="B588" t="inlineStr">
         <is>
-          <t>impacto_na_saude</t>
+          <t>perda_de_bens_materiais</t>
         </is>
       </c>
       <c r="C588" t="inlineStr">
         <is>
-          <t>Impacto na saúde</t>
+          <t>Perda de bens/materiais</t>
         </is>
       </c>
     </row>
@@ -23481,12 +23481,12 @@
       </c>
       <c r="B589" t="inlineStr">
         <is>
-          <t>impacto_emocional</t>
+          <t>impacto_na_saude</t>
         </is>
       </c>
       <c r="C589" t="inlineStr">
         <is>
-          <t>Impacto emocional</t>
+          <t>Impacto na saúde</t>
         </is>
       </c>
     </row>
@@ -23498,12 +23498,12 @@
       </c>
       <c r="B590" t="inlineStr">
         <is>
-          <t>perda_de_renda_ou_plantacoes</t>
+          <t>impacto_emocional</t>
         </is>
       </c>
       <c r="C590" t="inlineStr">
         <is>
-          <t>Perda de renda ou plantações</t>
+          <t>Impacto emocional</t>
         </is>
       </c>
     </row>
@@ -23515,12 +23515,12 @@
       </c>
       <c r="B591" t="inlineStr">
         <is>
-          <t>interrupcao_de_aulas_ou_do_traba</t>
+          <t>perda_de_renda_ou_plantacoes</t>
         </is>
       </c>
       <c r="C591" t="inlineStr">
         <is>
-          <t>Interrupção de aulas ou do trabalho</t>
+          <t>Perda de renda ou plantações</t>
         </is>
       </c>
     </row>
@@ -23532,29 +23532,29 @@
       </c>
       <c r="B592" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>interrupcao_de_aulas_ou_do_traba</t>
         </is>
       </c>
       <c r="C592" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>Interrupção de aulas ou do trabalho</t>
         </is>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="inlineStr">
         <is>
-          <t>afetou_com</t>
+          <t>impacto_risco_com</t>
         </is>
       </c>
       <c r="B593" t="inlineStr">
         <is>
-          <t>minha_familia_moradia</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C593" t="inlineStr">
         <is>
-          <t>Minha família / moradia</t>
+          <t>Outro</t>
         </is>
       </c>
     </row>
@@ -23566,12 +23566,12 @@
       </c>
       <c r="B594" t="inlineStr">
         <is>
-          <t>a_comunidade_como_um_todo</t>
+          <t>minha_familia_moradia</t>
         </is>
       </c>
       <c r="C594" t="inlineStr">
         <is>
-          <t>A comunidade como um todo</t>
+          <t>Minha família / moradia</t>
         </is>
       </c>
     </row>
@@ -23583,12 +23583,12 @@
       </c>
       <c r="B595" t="inlineStr">
         <is>
-          <t>ambos</t>
+          <t>a_comunidade_como_um_todo</t>
         </is>
       </c>
       <c r="C595" t="inlineStr">
         <is>
-          <t>Ambos</t>
+          <t>A comunidade como um todo</t>
         </is>
       </c>
     </row>
@@ -23600,12 +23600,12 @@
       </c>
       <c r="B596" t="inlineStr">
         <is>
-          <t>nenhum</t>
+          <t>ambos</t>
         </is>
       </c>
       <c r="C596" t="inlineStr">
         <is>
-          <t>Nenhum</t>
+          <t>Ambos</t>
         </is>
       </c>
     </row>
@@ -23617,29 +23617,29 @@
       </c>
       <c r="B597" t="inlineStr">
         <is>
-          <t>nao_sabe</t>
+          <t>nenhum</t>
         </is>
       </c>
       <c r="C597" t="inlineStr">
         <is>
-          <t>Não sabe</t>
+          <t>Nenhum</t>
         </is>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="inlineStr">
         <is>
-          <t>ativos_com</t>
+          <t>afetou_com</t>
         </is>
       </c>
       <c r="B598" t="inlineStr">
         <is>
-          <t>moradias</t>
+          <t>nao_sabe</t>
         </is>
       </c>
       <c r="C598" t="inlineStr">
         <is>
-          <t>Moradias</t>
+          <t>Não sabe</t>
         </is>
       </c>
     </row>
@@ -23651,12 +23651,12 @@
       </c>
       <c r="B599" t="inlineStr">
         <is>
-          <t>escola</t>
+          <t>moradias</t>
         </is>
       </c>
       <c r="C599" t="inlineStr">
         <is>
-          <t>Escola(s)</t>
+          <t>Moradias</t>
         </is>
       </c>
     </row>
@@ -23668,12 +23668,12 @@
       </c>
       <c r="B600" t="inlineStr">
         <is>
-          <t>posto_de_saude</t>
+          <t>escola</t>
         </is>
       </c>
       <c r="C600" t="inlineStr">
         <is>
-          <t>Posto de saúde</t>
+          <t>Escola(s)</t>
         </is>
       </c>
     </row>
@@ -23685,12 +23685,12 @@
       </c>
       <c r="B601" t="inlineStr">
         <is>
-          <t>ruas_estradas_e_pontes</t>
+          <t>posto_de_saude</t>
         </is>
       </c>
       <c r="C601" t="inlineStr">
         <is>
-          <t>Ruas, estradas e pontes</t>
+          <t>Posto de saúde</t>
         </is>
       </c>
     </row>
@@ -23702,12 +23702,12 @@
       </c>
       <c r="B602" t="inlineStr">
         <is>
-          <t>plantacoes_rocas_e_criacoes</t>
+          <t>ruas_estradas_e_pontes</t>
         </is>
       </c>
       <c r="C602" t="inlineStr">
         <is>
-          <t>Plantações, roças e criações</t>
+          <t>Ruas, estradas e pontes</t>
         </is>
       </c>
     </row>
@@ -23719,12 +23719,12 @@
       </c>
       <c r="B603" t="inlineStr">
         <is>
-          <t>fontes_de_agua</t>
+          <t>plantacoes_rocas_e_criacoes</t>
         </is>
       </c>
       <c r="C603" t="inlineStr">
         <is>
-          <t>Fontes de água</t>
+          <t>Plantações, roças e criações</t>
         </is>
       </c>
     </row>
@@ -23736,12 +23736,12 @@
       </c>
       <c r="B604" t="inlineStr">
         <is>
-          <t>comercios_locais_de_trabalho</t>
+          <t>fontes_de_agua</t>
         </is>
       </c>
       <c r="C604" t="inlineStr">
         <is>
-          <t>Comércios / locais de trabalho</t>
+          <t>Fontes de água</t>
         </is>
       </c>
     </row>
@@ -23753,12 +23753,12 @@
       </c>
       <c r="B605" t="inlineStr">
         <is>
-          <t>espacos_comunitarios</t>
+          <t>comercios_locais_de_trabalho</t>
         </is>
       </c>
       <c r="C605" t="inlineStr">
         <is>
-          <t>Espaços comunitários</t>
+          <t>Comércios / locais de trabalho</t>
         </is>
       </c>
     </row>
@@ -23770,29 +23770,29 @@
       </c>
       <c r="B606" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>espacos_comunitarios</t>
         </is>
       </c>
       <c r="C606" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>Espaços comunitários</t>
         </is>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="inlineStr">
         <is>
-          <t>grupos_exp_com</t>
+          <t>ativos_com</t>
         </is>
       </c>
       <c r="B607" t="inlineStr">
         <is>
-          <t>estudantes</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C607" t="inlineStr">
         <is>
-          <t>Estudantes</t>
+          <t>Outro</t>
         </is>
       </c>
     </row>
@@ -23804,12 +23804,12 @@
       </c>
       <c r="B608" t="inlineStr">
         <is>
-          <t>familias</t>
+          <t>estudantes</t>
         </is>
       </c>
       <c r="C608" t="inlineStr">
         <is>
-          <t>Famílias</t>
+          <t>Estudantes</t>
         </is>
       </c>
     </row>
@@ -23821,12 +23821,12 @@
       </c>
       <c r="B609" t="inlineStr">
         <is>
-          <t>pessoas_com_deficiencia</t>
+          <t>familias</t>
         </is>
       </c>
       <c r="C609" t="inlineStr">
         <is>
-          <t>Pessoas com deficiência</t>
+          <t>Famílias</t>
         </is>
       </c>
     </row>
@@ -23838,12 +23838,12 @@
       </c>
       <c r="B610" t="inlineStr">
         <is>
-          <t>criancas_pequenas</t>
+          <t>pessoas_com_deficiencia</t>
         </is>
       </c>
       <c r="C610" t="inlineStr">
         <is>
-          <t>Crianças pequenas</t>
+          <t>Pessoas com deficiência</t>
         </is>
       </c>
     </row>
@@ -23855,12 +23855,12 @@
       </c>
       <c r="B611" t="inlineStr">
         <is>
-          <t>idosos</t>
+          <t>criancas_pequenas</t>
         </is>
       </c>
       <c r="C611" t="inlineStr">
         <is>
-          <t>Idosos</t>
+          <t>Crianças pequenas</t>
         </is>
       </c>
     </row>
@@ -23872,12 +23872,12 @@
       </c>
       <c r="B612" t="inlineStr">
         <is>
-          <t>trabalhadores_rurais_pescadores</t>
+          <t>idosos</t>
         </is>
       </c>
       <c r="C612" t="inlineStr">
         <is>
-          <t>Trabalhadores rurais / pescadores</t>
+          <t>Idosos</t>
         </is>
       </c>
     </row>
@@ -23889,12 +23889,12 @@
       </c>
       <c r="B613" t="inlineStr">
         <is>
-          <t>povos_e_comunidades_tradicionais</t>
+          <t>trabalhadores_rurais_pescadores</t>
         </is>
       </c>
       <c r="C613" t="inlineStr">
         <is>
-          <t>Povos e comunidades tradicionais</t>
+          <t>Trabalhadores rurais / pescadores</t>
         </is>
       </c>
     </row>
@@ -23906,29 +23906,29 @@
       </c>
       <c r="B614" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>povos_e_comunidades_tradicionais</t>
         </is>
       </c>
       <c r="C614" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>Povos e comunidades tradicionais</t>
         </is>
       </c>
     </row>
     <row r="615">
       <c r="A615" t="inlineStr">
         <is>
-          <t>cartog_com</t>
+          <t>grupos_exp_com</t>
         </is>
       </c>
       <c r="B615" t="inlineStr">
         <is>
-          <t>estudantes</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C615" t="inlineStr">
         <is>
-          <t>Estudantes</t>
+          <t>Outro</t>
         </is>
       </c>
     </row>
@@ -23940,12 +23940,12 @@
       </c>
       <c r="B616" t="inlineStr">
         <is>
-          <t>moradores</t>
+          <t>estudantes</t>
         </is>
       </c>
       <c r="C616" t="inlineStr">
         <is>
-          <t>Moradores</t>
+          <t>Estudantes</t>
         </is>
       </c>
     </row>
@@ -23957,12 +23957,12 @@
       </c>
       <c r="B617" t="inlineStr">
         <is>
-          <t>liderancas</t>
+          <t>moradores</t>
         </is>
       </c>
       <c r="C617" t="inlineStr">
         <is>
-          <t>Lideranças</t>
+          <t>Moradores</t>
         </is>
       </c>
     </row>
@@ -23974,12 +23974,12 @@
       </c>
       <c r="B618" t="inlineStr">
         <is>
-          <t>pessoas_de_ongs</t>
+          <t>liderancas</t>
         </is>
       </c>
       <c r="C618" t="inlineStr">
         <is>
-          <t>Pessoas de ONGs</t>
+          <t>Lideranças</t>
         </is>
       </c>
     </row>
@@ -23991,29 +23991,29 @@
       </c>
       <c r="B619" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>pessoas_de_ongs</t>
         </is>
       </c>
       <c r="C619" t="inlineStr">
         <is>
-          <t>Outros</t>
+          <t>Pessoas de ONGs</t>
         </is>
       </c>
     </row>
     <row r="620">
       <c r="A620" t="inlineStr">
         <is>
-          <t>abrangencia_com</t>
+          <t>cartog_com</t>
         </is>
       </c>
       <c r="B620" t="inlineStr">
         <is>
-          <t>individual</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C620" t="inlineStr">
         <is>
-          <t>Individual</t>
+          <t>Outros</t>
         </is>
       </c>
     </row>
@@ -24025,12 +24025,12 @@
       </c>
       <c r="B621" t="inlineStr">
         <is>
-          <t>uma_familia</t>
+          <t>individual</t>
         </is>
       </c>
       <c r="C621" t="inlineStr">
         <is>
-          <t>Uma família</t>
+          <t>Individual</t>
         </is>
       </c>
     </row>
@@ -24042,12 +24042,12 @@
       </c>
       <c r="B622" t="inlineStr">
         <is>
-          <t>um_grupo_ou_organizacao</t>
+          <t>uma_familia</t>
         </is>
       </c>
       <c r="C622" t="inlineStr">
         <is>
-          <t>Um grupo ou organização</t>
+          <t>Uma família</t>
         </is>
       </c>
     </row>
@@ -24059,12 +24059,12 @@
       </c>
       <c r="B623" t="inlineStr">
         <is>
-          <t>toda_a_comunidade</t>
+          <t>um_grupo_ou_organizacao</t>
         </is>
       </c>
       <c r="C623" t="inlineStr">
         <is>
-          <t>Toda a comunidade</t>
+          <t>Um grupo ou organização</t>
         </is>
       </c>
     </row>
@@ -24076,29 +24076,29 @@
       </c>
       <c r="B624" t="inlineStr">
         <is>
-          <t>mais_de_uma_comunidade_territori</t>
+          <t>toda_a_comunidade</t>
         </is>
       </c>
       <c r="C624" t="inlineStr">
         <is>
-          <t>Mais de uma comunidade / território</t>
+          <t>Toda a comunidade</t>
         </is>
       </c>
     </row>
     <row r="625">
       <c r="A625" t="inlineStr">
         <is>
-          <t>afetados_com</t>
+          <t>abrangencia_com</t>
         </is>
       </c>
       <c r="B625" t="inlineStr">
         <is>
-          <t>estudantes</t>
+          <t>mais_de_uma_comunidade_territori</t>
         </is>
       </c>
       <c r="C625" t="inlineStr">
         <is>
-          <t>Estudantes</t>
+          <t>Mais de uma comunidade / território</t>
         </is>
       </c>
     </row>
@@ -24110,12 +24110,12 @@
       </c>
       <c r="B626" t="inlineStr">
         <is>
-          <t>familias</t>
+          <t>estudantes</t>
         </is>
       </c>
       <c r="C626" t="inlineStr">
         <is>
-          <t>Famílias</t>
+          <t>Estudantes</t>
         </is>
       </c>
     </row>
@@ -24127,12 +24127,12 @@
       </c>
       <c r="B627" t="inlineStr">
         <is>
-          <t>moradores</t>
+          <t>familias</t>
         </is>
       </c>
       <c r="C627" t="inlineStr">
         <is>
-          <t>Moradores</t>
+          <t>Famílias</t>
         </is>
       </c>
     </row>
@@ -24144,12 +24144,12 @@
       </c>
       <c r="B628" t="inlineStr">
         <is>
-          <t>trabalhadores</t>
+          <t>moradores</t>
         </is>
       </c>
       <c r="C628" t="inlineStr">
         <is>
-          <t>Trabalhadores</t>
+          <t>Moradores</t>
         </is>
       </c>
     </row>
@@ -24161,12 +24161,12 @@
       </c>
       <c r="B629" t="inlineStr">
         <is>
-          <t>criancas_e_idosos</t>
+          <t>trabalhadores</t>
         </is>
       </c>
       <c r="C629" t="inlineStr">
         <is>
-          <t>Crianças e idosos</t>
+          <t>Trabalhadores</t>
         </is>
       </c>
     </row>
@@ -24178,29 +24178,29 @@
       </c>
       <c r="B630" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>criancas_e_idosos</t>
         </is>
       </c>
       <c r="C630" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>Crianças e idosos</t>
         </is>
       </c>
     </row>
     <row r="631">
       <c r="A631" t="inlineStr">
         <is>
-          <t>decisao_part_com</t>
+          <t>afetados_com</t>
         </is>
       </c>
       <c r="B631" t="inlineStr">
         <is>
-          <t>estudantes</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C631" t="inlineStr">
         <is>
-          <t>Estudantes</t>
+          <t>Outro</t>
         </is>
       </c>
     </row>
@@ -24212,12 +24212,12 @@
       </c>
       <c r="B632" t="inlineStr">
         <is>
-          <t>familias</t>
+          <t>estudantes</t>
         </is>
       </c>
       <c r="C632" t="inlineStr">
         <is>
-          <t>Famílias</t>
+          <t>Estudantes</t>
         </is>
       </c>
     </row>
@@ -24229,12 +24229,12 @@
       </c>
       <c r="B633" t="inlineStr">
         <is>
-          <t>moradores</t>
+          <t>familias</t>
         </is>
       </c>
       <c r="C633" t="inlineStr">
         <is>
-          <t>Moradores</t>
+          <t>Famílias</t>
         </is>
       </c>
     </row>
@@ -24246,12 +24246,12 @@
       </c>
       <c r="B634" t="inlineStr">
         <is>
-          <t>liderancas_comunitarias</t>
+          <t>moradores</t>
         </is>
       </c>
       <c r="C634" t="inlineStr">
         <is>
-          <t>Lideranças comunitárias</t>
+          <t>Moradores</t>
         </is>
       </c>
     </row>
@@ -24263,12 +24263,12 @@
       </c>
       <c r="B635" t="inlineStr">
         <is>
-          <t>associacoes_ongs</t>
+          <t>liderancas_comunitarias</t>
         </is>
       </c>
       <c r="C635" t="inlineStr">
         <is>
-          <t>Associações / ONGs</t>
+          <t>Lideranças comunitárias</t>
         </is>
       </c>
     </row>
@@ -24280,12 +24280,12 @@
       </c>
       <c r="B636" t="inlineStr">
         <is>
-          <t>poder_publico</t>
+          <t>associacoes_ongs</t>
         </is>
       </c>
       <c r="C636" t="inlineStr">
         <is>
-          <t>Poder público</t>
+          <t>Associações / ONGs</t>
         </is>
       </c>
     </row>
@@ -24297,12 +24297,12 @@
       </c>
       <c r="B637" t="inlineStr">
         <is>
-          <t>escola_do_territorio</t>
+          <t>poder_publico</t>
         </is>
       </c>
       <c r="C637" t="inlineStr">
         <is>
-          <t>Escola(s) do território</t>
+          <t>Poder público</t>
         </is>
       </c>
     </row>
@@ -24314,29 +24314,29 @@
       </c>
       <c r="B638" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>escola_do_territorio</t>
         </is>
       </c>
       <c r="C638" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>Escola(s) do território</t>
         </is>
       </c>
     </row>
     <row r="639">
       <c r="A639" t="inlineStr">
         <is>
-          <t>publicos_com</t>
+          <t>decisao_part_com</t>
         </is>
       </c>
       <c r="B639" t="inlineStr">
         <is>
-          <t>estudantes</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C639" t="inlineStr">
         <is>
-          <t>Estudantes</t>
+          <t>Outro</t>
         </is>
       </c>
     </row>
@@ -24348,12 +24348,12 @@
       </c>
       <c r="B640" t="inlineStr">
         <is>
-          <t>professores</t>
+          <t>estudantes</t>
         </is>
       </c>
       <c r="C640" t="inlineStr">
         <is>
-          <t>Professores(as)</t>
+          <t>Estudantes</t>
         </is>
       </c>
     </row>
@@ -24365,12 +24365,12 @@
       </c>
       <c r="B641" t="inlineStr">
         <is>
-          <t>familias</t>
+          <t>professores</t>
         </is>
       </c>
       <c r="C641" t="inlineStr">
         <is>
-          <t>Famílias</t>
+          <t>Professores(as)</t>
         </is>
       </c>
     </row>
@@ -24382,12 +24382,12 @@
       </c>
       <c r="B642" t="inlineStr">
         <is>
-          <t>moradores</t>
+          <t>familias</t>
         </is>
       </c>
       <c r="C642" t="inlineStr">
         <is>
-          <t>Moradores</t>
+          <t>Famílias</t>
         </is>
       </c>
     </row>
@@ -24399,12 +24399,12 @@
       </c>
       <c r="B643" t="inlineStr">
         <is>
-          <t>associacoes_ongs</t>
+          <t>moradores</t>
         </is>
       </c>
       <c r="C643" t="inlineStr">
         <is>
-          <t>Associações / ONGs</t>
+          <t>Moradores</t>
         </is>
       </c>
     </row>
@@ -24416,12 +24416,12 @@
       </c>
       <c r="B644" t="inlineStr">
         <is>
-          <t>poder_publico</t>
+          <t>associacoes_ongs</t>
         </is>
       </c>
       <c r="C644" t="inlineStr">
         <is>
-          <t>Poder público</t>
+          <t>Associações / ONGs</t>
         </is>
       </c>
     </row>
@@ -24433,29 +24433,29 @@
       </c>
       <c r="B645" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>poder_publico</t>
         </is>
       </c>
       <c r="C645" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>Poder público</t>
         </is>
       </c>
     </row>
     <row r="646">
       <c r="A646" t="inlineStr">
         <is>
-          <t>dependencias_com</t>
+          <t>publicos_com</t>
         </is>
       </c>
       <c r="B646" t="inlineStr">
         <is>
-          <t>aprovacao_de_liderancas_poder_pu</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C646" t="inlineStr">
         <is>
-          <t>Aprovação de lideranças / poder público</t>
+          <t>Outro</t>
         </is>
       </c>
     </row>
@@ -24467,12 +24467,12 @@
       </c>
       <c r="B647" t="inlineStr">
         <is>
-          <t>recursos_financeiros</t>
+          <t>aprovacao_de_liderancas_poder_pu</t>
         </is>
       </c>
       <c r="C647" t="inlineStr">
         <is>
-          <t>Recursos financeiros</t>
+          <t>Aprovação de lideranças / poder público</t>
         </is>
       </c>
     </row>
@@ -24484,12 +24484,12 @@
       </c>
       <c r="B648" t="inlineStr">
         <is>
-          <t>parceria_externa</t>
+          <t>recursos_financeiros</t>
         </is>
       </c>
       <c r="C648" t="inlineStr">
         <is>
-          <t>Parceria externa</t>
+          <t>Recursos financeiros</t>
         </is>
       </c>
     </row>
@@ -24501,12 +24501,12 @@
       </c>
       <c r="B649" t="inlineStr">
         <is>
-          <t>formacao_previa</t>
+          <t>parceria_externa</t>
         </is>
       </c>
       <c r="C649" t="inlineStr">
         <is>
-          <t>Formação prévia</t>
+          <t>Parceria externa</t>
         </is>
       </c>
     </row>
@@ -24518,12 +24518,12 @@
       </c>
       <c r="B650" t="inlineStr">
         <is>
-          <t>nenhuma</t>
+          <t>formacao_previa</t>
         </is>
       </c>
       <c r="C650" t="inlineStr">
         <is>
-          <t>Nenhuma</t>
+          <t>Formação prévia</t>
         </is>
       </c>
     </row>
@@ -24535,29 +24535,29 @@
       </c>
       <c r="B651" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>nenhuma</t>
         </is>
       </c>
       <c r="C651" t="inlineStr">
         <is>
-          <t>Outra</t>
+          <t>Nenhuma</t>
         </is>
       </c>
     </row>
     <row r="652">
       <c r="A652" t="inlineStr">
         <is>
-          <t>evid_exec_com</t>
+          <t>dependencias_com</t>
         </is>
       </c>
       <c r="B652" t="inlineStr">
         <is>
-          <t>fotos</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C652" t="inlineStr">
         <is>
-          <t>Fotos</t>
+          <t>Outra</t>
         </is>
       </c>
     </row>
@@ -24569,12 +24569,12 @@
       </c>
       <c r="B653" t="inlineStr">
         <is>
-          <t>lista_de_presenca</t>
+          <t>fotos</t>
         </is>
       </c>
       <c r="C653" t="inlineStr">
         <is>
-          <t>Lista de presença</t>
+          <t>Fotos</t>
         </is>
       </c>
     </row>
@@ -24586,12 +24586,12 @@
       </c>
       <c r="B654" t="inlineStr">
         <is>
-          <t>producoes_da_comunidade</t>
+          <t>lista_de_presenca</t>
         </is>
       </c>
       <c r="C654" t="inlineStr">
         <is>
-          <t>Produções da comunidade</t>
+          <t>Lista de presença</t>
         </is>
       </c>
     </row>
@@ -24603,12 +24603,12 @@
       </c>
       <c r="B655" t="inlineStr">
         <is>
-          <t>registro_em_ata</t>
+          <t>producoes_da_comunidade</t>
         </is>
       </c>
       <c r="C655" t="inlineStr">
         <is>
-          <t>Registro em ata</t>
+          <t>Produções da comunidade</t>
         </is>
       </c>
     </row>
@@ -24620,12 +24620,12 @@
       </c>
       <c r="B656" t="inlineStr">
         <is>
-          <t>depoimentos</t>
+          <t>registro_em_ata</t>
         </is>
       </c>
       <c r="C656" t="inlineStr">
         <is>
-          <t>Depoimentos</t>
+          <t>Registro em ata</t>
         </is>
       </c>
     </row>
@@ -24637,29 +24637,29 @@
       </c>
       <c r="B657" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>depoimentos</t>
         </is>
       </c>
       <c r="C657" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>Depoimentos</t>
         </is>
       </c>
     </row>
     <row r="658">
       <c r="A658" t="inlineStr">
         <is>
-          <t>metodo_sel_com</t>
+          <t>evid_exec_com</t>
         </is>
       </c>
       <c r="B658" t="inlineStr">
         <is>
-          <t>votacao</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C658" t="inlineStr">
         <is>
-          <t>Votação</t>
+          <t>Outro</t>
         </is>
       </c>
     </row>
@@ -24671,12 +24671,12 @@
       </c>
       <c r="B659" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>votacao</t>
         </is>
       </c>
       <c r="C659" t="inlineStr">
         <is>
-          <t>Consenso</t>
+          <t>Votação</t>
         </is>
       </c>
     </row>
@@ -24688,12 +24688,12 @@
       </c>
       <c r="B660" t="inlineStr">
         <is>
-          <t>decisao_de_liderancas_ou_da_coor</t>
+          <t>consenso</t>
         </is>
       </c>
       <c r="C660" t="inlineStr">
         <is>
-          <t>Decisão de lideranças ou da coordenação</t>
+          <t>Consenso</t>
         </is>
       </c>
     </row>
@@ -24705,12 +24705,12 @@
       </c>
       <c r="B661" t="inlineStr">
         <is>
-          <t>criterios_tecnicos</t>
+          <t>decisao_de_liderancas_ou_da_coor</t>
         </is>
       </c>
       <c r="C661" t="inlineStr">
         <is>
-          <t>Critérios técnicos</t>
+          <t>Decisão de lideranças ou da coordenação</t>
         </is>
       </c>
     </row>
@@ -24722,12 +24722,12 @@
       </c>
       <c r="B662" t="inlineStr">
         <is>
-          <t>discussao_coletiva</t>
+          <t>criterios_tecnicos</t>
         </is>
       </c>
       <c r="C662" t="inlineStr">
         <is>
-          <t>Discussão coletiva</t>
+          <t>Critérios técnicos</t>
         </is>
       </c>
     </row>
@@ -24739,29 +24739,29 @@
       </c>
       <c r="B663" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>discussao_coletiva</t>
         </is>
       </c>
       <c r="C663" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>Discussão coletiva</t>
         </is>
       </c>
     </row>
     <row r="664">
       <c r="A664" t="inlineStr">
         <is>
-          <t>com_produz_com</t>
+          <t>metodo_sel_com</t>
         </is>
       </c>
       <c r="B664" t="inlineStr">
         <is>
-          <t>estudantes</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C664" t="inlineStr">
         <is>
-          <t>Estudantes</t>
+          <t>Outro</t>
         </is>
       </c>
     </row>
@@ -24773,12 +24773,12 @@
       </c>
       <c r="B665" t="inlineStr">
         <is>
-          <t>moradores</t>
+          <t>estudantes</t>
         </is>
       </c>
       <c r="C665" t="inlineStr">
         <is>
-          <t>Moradores</t>
+          <t>Estudantes</t>
         </is>
       </c>
     </row>
@@ -24790,12 +24790,12 @@
       </c>
       <c r="B666" t="inlineStr">
         <is>
-          <t>associacao_ong</t>
+          <t>moradores</t>
         </is>
       </c>
       <c r="C666" t="inlineStr">
         <is>
-          <t>Associação / ONG</t>
+          <t>Moradores</t>
         </is>
       </c>
     </row>
@@ -24807,12 +24807,12 @@
       </c>
       <c r="B667" t="inlineStr">
         <is>
-          <t>coletivos_de_jovens</t>
+          <t>associacao_ong</t>
         </is>
       </c>
       <c r="C667" t="inlineStr">
         <is>
-          <t>Coletivos de jovens</t>
+          <t>Associação / ONG</t>
         </is>
       </c>
     </row>
@@ -24824,12 +24824,12 @@
       </c>
       <c r="B668" t="inlineStr">
         <is>
-          <t>parceiros_externos</t>
+          <t>coletivos_de_jovens</t>
         </is>
       </c>
       <c r="C668" t="inlineStr">
         <is>
-          <t>Parceiros externos</t>
+          <t>Coletivos de jovens</t>
         </is>
       </c>
     </row>
@@ -24841,10 +24841,27 @@
       </c>
       <c r="B669" t="inlineStr">
         <is>
+          <t>parceiros_externos</t>
+        </is>
+      </c>
+      <c r="C669" t="inlineStr">
+        <is>
+          <t>Parceiros externos</t>
+        </is>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" t="inlineStr">
+        <is>
+          <t>com_produz_com</t>
+        </is>
+      </c>
+      <c r="B670" t="inlineStr">
+        <is>
           <t>outro</t>
         </is>
       </c>
-      <c r="C669" t="inlineStr">
+      <c r="C670" t="inlineStr">
         <is>
           <t>Outro</t>
         </is>

--- a/kobo/comunidade_diagnostico_completo.xlsx
+++ b/kobo/comunidade_diagnostico_completo.xlsx
@@ -3935,8 +3935,16 @@
         </is>
       </c>
       <c r="G128" t="inlineStr"/>
-      <c r="H128" t="inlineStr"/>
-      <c r="I128" t="inlineStr"/>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>not(selected(., 'nao_sabe') and count-selected(.) &gt; 1)</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>"Não sabe" não pode ser combinado com outras opções.</t>
+        </is>
+      </c>
       <c r="J128" t="inlineStr"/>
     </row>
     <row r="129">
@@ -4011,8 +4019,16 @@
       <c r="E131" t="inlineStr"/>
       <c r="F131" t="inlineStr"/>
       <c r="G131" t="inlineStr"/>
-      <c r="H131" t="inlineStr"/>
-      <c r="I131" t="inlineStr"/>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>not(selected(., 'nao_sabe') and count-selected(.) &gt; 1)</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>"Não sabe" não pode ser combinado com outras opções.</t>
+        </is>
+      </c>
       <c r="J131" t="inlineStr"/>
     </row>
     <row r="132">
@@ -4851,8 +4867,16 @@
       <c r="E163" t="inlineStr"/>
       <c r="F163" t="inlineStr"/>
       <c r="G163" t="inlineStr"/>
-      <c r="H163" t="inlineStr"/>
-      <c r="I163" t="inlineStr"/>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>not(selected(., 'nao_sabe') and count-selected(.) &gt; 1)</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>"Não sabe" não pode ser combinado com outras opções.</t>
+        </is>
+      </c>
       <c r="J163" t="inlineStr"/>
     </row>
     <row r="164">
@@ -4963,8 +4987,16 @@
       <c r="E167" t="inlineStr"/>
       <c r="F167" t="inlineStr"/>
       <c r="G167" t="inlineStr"/>
-      <c r="H167" t="inlineStr"/>
-      <c r="I167" t="inlineStr"/>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>not(selected(., 'nao_sabe') and count-selected(.) &gt; 1)</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>"Não sabe" não pode ser combinado com outras opções.</t>
+        </is>
+      </c>
       <c r="J167" t="inlineStr"/>
     </row>
     <row r="168">
@@ -5743,8 +5775,16 @@
       <c r="E197" t="inlineStr"/>
       <c r="F197" t="inlineStr"/>
       <c r="G197" t="inlineStr"/>
-      <c r="H197" t="inlineStr"/>
-      <c r="I197" t="inlineStr"/>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>not(selected(., 'nao_sabe') and count-selected(.) &gt; 1)</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>"Não sabe" não pode ser combinado com outras opções.</t>
+        </is>
+      </c>
       <c r="J197" t="inlineStr"/>
     </row>
     <row r="198">
@@ -13474,7 +13514,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C670"/>
+  <dimension ref="A1:C673"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16149,17 +16189,17 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>freq_ea</t>
+          <t>areas_curr</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>diaria</t>
+          <t>nao_sabe</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Diária</t>
+          <t>Não sabe</t>
         </is>
       </c>
     </row>
@@ -16171,12 +16211,12 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>semanal</t>
+          <t>diaria</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Semanal</t>
+          <t>Diária</t>
         </is>
       </c>
     </row>
@@ -16188,12 +16228,12 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>mensal</t>
+          <t>semanal</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Mensal</t>
+          <t>Semanal</t>
         </is>
       </c>
     </row>
@@ -16205,12 +16245,12 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>esporadica</t>
+          <t>mensal</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Esporádica</t>
+          <t>Mensal</t>
         </is>
       </c>
     </row>
@@ -16222,12 +16262,12 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>anual</t>
+          <t>esporadica</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Anual</t>
+          <t>Esporádica</t>
         </is>
       </c>
     </row>
@@ -16239,12 +16279,12 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>nao_ocorre</t>
+          <t>anual</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Não ocorre</t>
+          <t>Anual</t>
         </is>
       </c>
     </row>
@@ -16256,29 +16296,29 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>nao_sabe</t>
+          <t>nao_ocorre</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Não sabe</t>
+          <t>Não ocorre</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>papel_estud</t>
+          <t>freq_ea</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>espectador</t>
+          <t>nao_sabe</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Espectador</t>
+          <t>Não sabe</t>
         </is>
       </c>
     </row>
@@ -16290,12 +16330,12 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>participante_pontual</t>
+          <t>espectador</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Participante pontual</t>
+          <t>Espectador</t>
         </is>
       </c>
     </row>
@@ -16307,12 +16347,12 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>protagonista</t>
+          <t>participante_pontual</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Protagonista</t>
+          <t>Participante pontual</t>
         </is>
       </c>
     </row>
@@ -16324,12 +16364,12 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>coprodutor</t>
+          <t>protagonista</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Coprodutor</t>
+          <t>Protagonista</t>
         </is>
       </c>
     </row>
@@ -16341,29 +16381,29 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>nao_sabe</t>
+          <t>coprodutor</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Não sabe</t>
+          <t>Coprodutor</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>freq5</t>
+          <t>papel_estud</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>nunca</t>
+          <t>nao_sabe</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Nunca</t>
+          <t>Não sabe</t>
         </is>
       </c>
     </row>
@@ -16375,12 +16415,12 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>raramente</t>
+          <t>nunca</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Raramente</t>
+          <t>Nunca</t>
         </is>
       </c>
     </row>
@@ -16392,12 +16432,12 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>as_vezes</t>
+          <t>raramente</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Às vezes</t>
+          <t>Raramente</t>
         </is>
       </c>
     </row>
@@ -16409,12 +16449,12 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>frequentemente</t>
+          <t>as_vezes</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Frequentemente</t>
+          <t>Às vezes</t>
         </is>
       </c>
     </row>
@@ -16426,29 +16466,29 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>nao_sabe</t>
+          <t>frequentemente</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Não sabe</t>
+          <t>Frequentemente</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>temas</t>
+          <t>freq5</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>agua</t>
+          <t>nao_sabe</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Água</t>
+          <t>Não sabe</t>
         </is>
       </c>
     </row>
@@ -16460,12 +16500,12 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>biodiversidade</t>
+          <t>agua</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Biodiversidade</t>
+          <t>Água</t>
         </is>
       </c>
     </row>
@@ -16477,12 +16517,12 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>residuos</t>
+          <t>biodiversidade</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Resíduos</t>
+          <t>Biodiversidade</t>
         </is>
       </c>
     </row>
@@ -16494,12 +16534,12 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>mudancas_climaticas</t>
+          <t>residuos</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Mudanças climáticas</t>
+          <t>Resíduos</t>
         </is>
       </c>
     </row>
@@ -16511,12 +16551,12 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>energia</t>
+          <t>mudancas_climaticas</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Energia</t>
+          <t>Mudanças climáticas</t>
         </is>
       </c>
     </row>
@@ -16528,12 +16568,12 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>alimentacao</t>
+          <t>energia</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Alimentação</t>
+          <t>Energia</t>
         </is>
       </c>
     </row>
@@ -16545,12 +16585,12 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>consumo</t>
+          <t>alimentacao</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Consumo</t>
+          <t>Alimentação</t>
         </is>
       </c>
     </row>
@@ -16562,12 +16602,12 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>saneamento</t>
+          <t>consumo</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Saneamento</t>
+          <t>Consumo</t>
         </is>
       </c>
     </row>
@@ -16579,12 +16619,12 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>saude</t>
+          <t>saneamento</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Saúde</t>
+          <t>Saneamento</t>
         </is>
       </c>
     </row>
@@ -16596,12 +16636,12 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>riscos_desastres</t>
+          <t>saude</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Riscos/desastres</t>
+          <t>Saúde</t>
         </is>
       </c>
     </row>
@@ -16613,12 +16653,12 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>justica_socioambiental</t>
+          <t>riscos_desastres</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Justiça socioambiental</t>
+          <t>Riscos/desastres</t>
         </is>
       </c>
     </row>
@@ -16630,12 +16670,12 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>territorio</t>
+          <t>justica_socioambiental</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Território</t>
+          <t>Justiça socioambiental</t>
         </is>
       </c>
     </row>
@@ -16647,12 +16687,12 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>conflitos</t>
+          <t>territorio</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Conflitos</t>
+          <t>Território</t>
         </is>
       </c>
     </row>
@@ -16664,12 +16704,12 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>povos_e_comunidades_tradicionais</t>
+          <t>conflitos</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Povos e comunidades tradicionais</t>
+          <t>Conflitos</t>
         </is>
       </c>
     </row>
@@ -16681,46 +16721,46 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>povos_e_comunidades_tradicionais</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Outros</t>
+          <t>Povos e comunidades tradicionais</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>metodos</t>
+          <t>temas</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>aula_expositiva</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Aula expositiva</t>
+          <t>Outros</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>metodos</t>
+          <t>temas</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>projeto</t>
+          <t>nao_sabe</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Projeto</t>
+          <t>Não sabe</t>
         </is>
       </c>
     </row>
@@ -16732,12 +16772,12 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>oficina</t>
+          <t>aula_expositiva</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Oficina</t>
+          <t>Aula expositiva</t>
         </is>
       </c>
     </row>
@@ -16749,12 +16789,12 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>saida_de_campo</t>
+          <t>projeto</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Saída de campo</t>
+          <t>Projeto</t>
         </is>
       </c>
     </row>
@@ -16766,12 +16806,12 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>horta_experimentacao</t>
+          <t>oficina</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Horta/experimentação</t>
+          <t>Oficina</t>
         </is>
       </c>
     </row>
@@ -16783,12 +16823,12 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>rodas_de_conversa</t>
+          <t>saida_de_campo</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Rodas de conversa</t>
+          <t>Saída de campo</t>
         </is>
       </c>
     </row>
@@ -16800,12 +16840,12 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>producao_audiovisual</t>
+          <t>horta_experimentacao</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Produção audiovisual</t>
+          <t>Horta/experimentação</t>
         </is>
       </c>
     </row>
@@ -16817,12 +16857,12 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>cartografia</t>
+          <t>rodas_de_conversa</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Cartografia</t>
+          <t>Rodas de conversa</t>
         </is>
       </c>
     </row>
@@ -16834,63 +16874,63 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>producao_audiovisual</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>Produção audiovisual</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>impacto_form</t>
+          <t>metodos</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>nenhum</t>
+          <t>cartografia</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Nenhum</t>
+          <t>Cartografia</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>impacto_form</t>
+          <t>metodos</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>pouco</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Pouco</t>
+          <t>Outro</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>impacto_form</t>
+          <t>metodos</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>moderado</t>
+          <t>nao_sabe</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Moderado</t>
+          <t>Não sabe</t>
         </is>
       </c>
     </row>
@@ -16902,12 +16942,12 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>significativo</t>
+          <t>nenhum</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Significativo</t>
+          <t>Nenhum</t>
         </is>
       </c>
     </row>
@@ -16919,63 +16959,63 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>nao_sabe</t>
+          <t>pouco</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Não sabe</t>
+          <t>Pouco</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>confianca</t>
+          <t>impacto_form</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>moderado</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>1 — Nada confiante(a)</t>
+          <t>Moderado</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>confianca</t>
+          <t>impacto_form</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>significativo</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>2 — Pouco confiante</t>
+          <t>Significativo</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>confianca</t>
+          <t>impacto_form</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>nao_sabe</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>3 — Moderadamente confiante</t>
+          <t>Não sabe</t>
         </is>
       </c>
     </row>
@@ -16987,12 +17027,12 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>4 — Confiante</t>
+          <t>1 — Nada confiante(a)</t>
         </is>
       </c>
     </row>
@@ -17004,12 +17044,12 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>5 — Muito confiante</t>
+          <t>2 — Pouco confiante</t>
         </is>
       </c>
     </row>
@@ -17021,63 +17061,63 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>nao_se_aplica</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Não se aplica</t>
+          <t>3 — Moderadamente confiante</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>intensidade</t>
+          <t>confianca</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>baixa</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Baixa</t>
+          <t>4 — Confiante</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>intensidade</t>
+          <t>confianca</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>5 — Muito confiante</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>intensidade</t>
+          <t>confianca</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>alta</t>
+          <t>nao_se_aplica</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Não se aplica</t>
         </is>
       </c>
     </row>
@@ -17089,63 +17129,63 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>nao_se_aplica</t>
+          <t>baixa</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Não se aplica</t>
+          <t>Baixa</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>acesso_mat</t>
+          <t>intensidade</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>facil</t>
+          <t>media</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Fácil</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>acesso_mat</t>
+          <t>intensidade</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>moderado</t>
+          <t>alta</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Moderado</t>
+          <t>Alta</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>acesso_mat</t>
+          <t>intensidade</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>dificil</t>
+          <t>nao_se_aplica</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Difícil</t>
+          <t>Não se aplica</t>
         </is>
       </c>
     </row>
@@ -17157,12 +17197,12 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>inexistente</t>
+          <t>facil</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Inexistente</t>
+          <t>Fácil</t>
         </is>
       </c>
     </row>
@@ -17174,63 +17214,63 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>nao_sabe</t>
+          <t>moderado</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Não sabe</t>
+          <t>Moderado</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>part_estud</t>
+          <t>acesso_mat</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>espectadores</t>
+          <t>dificil</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Espectadores</t>
+          <t>Difícil</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>part_estud</t>
+          <t>acesso_mat</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>colaboradores_pontuais</t>
+          <t>inexistente</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Colaboradores pontuais</t>
+          <t>Inexistente</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>part_estud</t>
+          <t>acesso_mat</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>protagonistas_em_alguns_momentos</t>
+          <t>nao_sabe</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Protagonistas em alguns momentos</t>
+          <t>Não sabe</t>
         </is>
       </c>
     </row>
@@ -17242,12 +17282,12 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>protagonistas_continuos</t>
+          <t>espectadores</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Protagonistas contínuos</t>
+          <t>Espectadores</t>
         </is>
       </c>
     </row>
@@ -17259,63 +17299,63 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>nao_sabe</t>
+          <t>colaboradores_pontuais</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Não sabe</t>
+          <t>Colaboradores pontuais</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>continuidade_proj</t>
+          <t>part_estud</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>garantida_institucionalmente</t>
+          <t>protagonistas_em_alguns_momentos</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Garantida institucionalmente</t>
+          <t>Protagonistas em alguns momentos</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>continuidade_proj</t>
+          <t>part_estud</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>dependente_de_pessoas_especifica</t>
+          <t>protagonistas_continuos</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Dependente de pessoas específicas</t>
+          <t>Protagonistas contínuos</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>continuidade_proj</t>
+          <t>part_estud</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>incerta</t>
+          <t>nao_sabe</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Incerta</t>
+          <t>Não sabe</t>
         </is>
       </c>
     </row>
@@ -17327,63 +17367,63 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>nao_sabe</t>
+          <t>garantida_institucionalmente</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Não sabe</t>
+          <t>Garantida institucionalmente</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>nivel_part</t>
+          <t>continuidade_proj</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>informativa</t>
+          <t>dependente_de_pessoas_especifica</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Informativa (recebem informação)</t>
+          <t>Dependente de pessoas específicas</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>nivel_part</t>
+          <t>continuidade_proj</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>consultiva</t>
+          <t>incerta</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Consultiva (são ouvidos)</t>
+          <t>Incerta</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>nivel_part</t>
+          <t>continuidade_proj</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>colaborativa</t>
+          <t>nao_sabe</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Colaborativa (constroem junto)</t>
+          <t>Não sabe</t>
         </is>
       </c>
     </row>
@@ -17395,12 +17435,12 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>protagonista</t>
+          <t>informativa</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Protagonista (decidem e conduzem)</t>
+          <t>Informativa (recebem informação)</t>
         </is>
       </c>
     </row>
@@ -17412,63 +17452,63 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>nao_sabe</t>
+          <t>consultiva</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Não sabe</t>
+          <t>Consultiva (são ouvidos)</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>env_fam</t>
+          <t>nivel_part</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>ausente</t>
+          <t>colaborativa</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Ausente</t>
+          <t>Colaborativa (constroem junto)</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>env_fam</t>
+          <t>nivel_part</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>esporadico</t>
+          <t>protagonista</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Esporádico</t>
+          <t>Protagonista (decidem e conduzem)</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>env_fam</t>
+          <t>nivel_part</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>regular</t>
+          <t>nao_sabe</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Regular</t>
+          <t>Não sabe</t>
         </is>
       </c>
     </row>
@@ -17480,12 +17520,12 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>ativo_protagonista</t>
+          <t>ausente</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Ativo/protagonista</t>
+          <t>Ausente</t>
         </is>
       </c>
     </row>
@@ -17497,63 +17537,63 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>nao_sabe</t>
+          <t>esporadico</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Não sabe</t>
+          <t>Esporádico</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>barr_fam</t>
+          <t>env_fam</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>horario_de_trabalho</t>
+          <t>regular</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Horário de trabalho</t>
+          <t>Regular</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>barr_fam</t>
+          <t>env_fam</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>distancia</t>
+          <t>ativo_protagonista</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Distância</t>
+          <t>Ativo/protagonista</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>barr_fam</t>
+          <t>env_fam</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>comunicacao_inadequada</t>
+          <t>nao_sabe</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Comunicação inadequada</t>
+          <t>Não sabe</t>
         </is>
       </c>
     </row>
@@ -17565,12 +17605,12 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>falta_de_convite_convocacao</t>
+          <t>horario_de_trabalho</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Falta de convite/convocação</t>
+          <t>Horário de trabalho</t>
         </is>
       </c>
     </row>
@@ -17582,63 +17622,63 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>distancia</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Outra</t>
+          <t>Distância</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>cat_ator</t>
+          <t>barr_fam</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>sec_educacao</t>
+          <t>comunicacao_inadequada</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Secretaria de Educação</t>
+          <t>Comunicação inadequada</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>cat_ator</t>
+          <t>barr_fam</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>sec_meio_amb</t>
+          <t>falta_de_convite_convocacao</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Secretaria de Meio Ambiente</t>
+          <t>Falta de convite/convocação</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>cat_ator</t>
+          <t>barr_fam</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>defesa_civil</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Defesa Civil</t>
+          <t>Outra</t>
         </is>
       </c>
     </row>
@@ -17650,12 +17690,12 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>sec_saude</t>
+          <t>sec_educacao</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Secretaria de Saúde</t>
+          <t>Secretaria de Educação</t>
         </is>
       </c>
     </row>
@@ -17667,12 +17707,12 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>assist_social</t>
+          <t>sec_meio_amb</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Assistência Social</t>
+          <t>Secretaria de Meio Ambiente</t>
         </is>
       </c>
     </row>
@@ -17684,12 +17724,12 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>obras</t>
+          <t>defesa_civil</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Obras</t>
+          <t>Defesa Civil</t>
         </is>
       </c>
     </row>
@@ -17701,12 +17741,12 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>bombeiros</t>
+          <t>sec_saude</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Bombeiros</t>
+          <t>Secretaria de Saúde</t>
         </is>
       </c>
     </row>
@@ -17718,12 +17758,12 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>ubs</t>
+          <t>assist_social</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>UBS</t>
+          <t>Assistência Social</t>
         </is>
       </c>
     </row>
@@ -17735,12 +17775,12 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>vigilancia</t>
+          <t>obras</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Vigilância</t>
+          <t>Obras</t>
         </is>
       </c>
     </row>
@@ -17752,12 +17792,12 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>outro_publico</t>
+          <t>bombeiros</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Outro (poder público)</t>
+          <t>Bombeiros</t>
         </is>
       </c>
     </row>
@@ -17769,12 +17809,12 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>universidade</t>
+          <t>ubs</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Universidade</t>
+          <t>UBS</t>
         </is>
       </c>
     </row>
@@ -17786,12 +17826,12 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>inst_federal</t>
+          <t>vigilancia</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Instituto Federal</t>
+          <t>Vigilância</t>
         </is>
       </c>
     </row>
@@ -17803,12 +17843,12 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>escola_tecnica</t>
+          <t>outro_publico</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Escola técnica</t>
+          <t>Outro (poder público)</t>
         </is>
       </c>
     </row>
@@ -17820,12 +17860,12 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>centro_pesquisa</t>
+          <t>universidade</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Centro de pesquisa</t>
+          <t>Universidade</t>
         </is>
       </c>
     </row>
@@ -17837,12 +17877,12 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>museu</t>
+          <t>inst_federal</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Museu</t>
+          <t>Instituto Federal</t>
         </is>
       </c>
     </row>
@@ -17854,12 +17894,12 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>jardim_botanico</t>
+          <t>escola_tecnica</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Jardim botânico</t>
+          <t>Escola técnica</t>
         </is>
       </c>
     </row>
@@ -17871,12 +17911,12 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>outro_educ_ciencia</t>
+          <t>centro_pesquisa</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Outro (educação/ciência)</t>
+          <t>Centro de pesquisa</t>
         </is>
       </c>
     </row>
@@ -17888,12 +17928,12 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>assoc_moradores</t>
+          <t>museu</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Associação de moradores</t>
+          <t>Museu</t>
         </is>
       </c>
     </row>
@@ -17905,12 +17945,12 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>ong</t>
+          <t>jardim_botanico</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>ONG</t>
+          <t>Jardim botânico</t>
         </is>
       </c>
     </row>
@@ -17922,12 +17962,12 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>cooperativa</t>
+          <t>outro_educ_ciencia</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Cooperativa</t>
+          <t>Outro (educação/ciência)</t>
         </is>
       </c>
     </row>
@@ -17939,12 +17979,12 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>catadores</t>
+          <t>assoc_moradores</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Catadores</t>
+          <t>Associação de moradores</t>
         </is>
       </c>
     </row>
@@ -17956,12 +17996,12 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>mov_sociais</t>
+          <t>ong</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Movimentos sociais</t>
+          <t>ONG</t>
         </is>
       </c>
     </row>
@@ -17973,12 +18013,12 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>coletivos</t>
+          <t>cooperativa</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Coletivos</t>
+          <t>Cooperativa</t>
         </is>
       </c>
     </row>
@@ -17990,12 +18030,12 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>grupos_culturais</t>
+          <t>catadores</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Grupos culturais</t>
+          <t>Catadores</t>
         </is>
       </c>
     </row>
@@ -18007,12 +18047,12 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>org_comunit_relig</t>
+          <t>mov_sociais</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Organizações comunitárias/religiosas</t>
+          <t>Movimentos sociais</t>
         </is>
       </c>
     </row>
@@ -18024,12 +18064,12 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>outro_soc_civil</t>
+          <t>coletivos</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Outro (sociedade civil)</t>
+          <t>Coletivos</t>
         </is>
       </c>
     </row>
@@ -18041,12 +18081,12 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>povos_indigenas</t>
+          <t>grupos_culturais</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Povos indígenas</t>
+          <t>Grupos culturais</t>
         </is>
       </c>
     </row>
@@ -18058,12 +18098,12 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>quilombolas</t>
+          <t>org_comunit_relig</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Quilombolas</t>
+          <t>Organizações comunitárias/religiosas</t>
         </is>
       </c>
     </row>
@@ -18075,12 +18115,12 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>agric_familiares</t>
+          <t>outro_soc_civil</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Agricultores familiares</t>
+          <t>Outro (sociedade civil)</t>
         </is>
       </c>
     </row>
@@ -18092,12 +18132,12 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>pescadores</t>
+          <t>povos_indigenas</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Pescadores</t>
+          <t>Povos indígenas</t>
         </is>
       </c>
     </row>
@@ -18109,12 +18149,12 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>com_tradicionais</t>
+          <t>quilombolas</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Comunidades tradicionais</t>
+          <t>Quilombolas</t>
         </is>
       </c>
     </row>
@@ -18126,12 +18166,12 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>liderancas</t>
+          <t>agric_familiares</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Lideranças</t>
+          <t>Agricultores familiares</t>
         </is>
       </c>
     </row>
@@ -18143,12 +18183,12 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>detentores_saberes</t>
+          <t>pescadores</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Detentores de conhecimentos locais</t>
+          <t>Pescadores</t>
         </is>
       </c>
     </row>
@@ -18160,63 +18200,63 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>outro_comunidades</t>
+          <t>com_tradicionais</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Outro (comunidades e conhecimentos)</t>
+          <t>Comunidades tradicionais</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>nivel_rel_grade</t>
+          <t>cat_ator</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>nao_existe</t>
+          <t>liderancas</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Não existe no território</t>
+          <t>Lideranças</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>nivel_rel_grade</t>
+          <t>cat_ator</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>nao_sei</t>
+          <t>detentores_saberes</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Não sei se existe</t>
+          <t>Detentores de conhecimentos locais</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>nivel_rel_grade</t>
+          <t>cat_ator</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>sem_contato</t>
+          <t>outro_comunidades</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Existe, mas nunca houve contato</t>
+          <t>Outro (comunidades e conhecimentos)</t>
         </is>
       </c>
     </row>
@@ -18228,12 +18268,12 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>contato_pontual</t>
+          <t>nao_existe</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Contato pontual, sem combinação formal (ainda não é parceiro(a))</t>
+          <t>Não existe no território</t>
         </is>
       </c>
     </row>
@@ -18245,12 +18285,12 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>parceria</t>
+          <t>nao_sei</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Parceria — já colaboram em ações combinadas</t>
+          <t>Não sei se existe</t>
         </is>
       </c>
     </row>
@@ -18262,63 +18302,63 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>articulacao</t>
+          <t>sem_contato</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Articulação permanente — parceria contínua e estruturada</t>
+          <t>Existe, mas nunca houve contato</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>canais</t>
+          <t>nivel_rel_grade</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>whatsapp</t>
+          <t>contato_pontual</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>WhatsApp</t>
+          <t>Contato pontual, sem combinação formal (ainda não é parceiro(a))</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>canais</t>
+          <t>nivel_rel_grade</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>comunicados_impressos</t>
+          <t>parceria</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Comunicados impressos</t>
+          <t>Parceria — já colaboram em ações combinadas</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>canais</t>
+          <t>nivel_rel_grade</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>reunioes</t>
+          <t>articulacao</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Reuniões</t>
+          <t>Articulação permanente — parceria contínua e estruturada</t>
         </is>
       </c>
     </row>
@@ -18330,12 +18370,12 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>redes_sociais</t>
+          <t>whatsapp</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Redes sociais</t>
+          <t>WhatsApp</t>
         </is>
       </c>
     </row>
@@ -18347,12 +18387,12 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>alto_falante_radio_local</t>
+          <t>comunicados_impressos</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Alto-falante/rádio local</t>
+          <t>Comunicados impressos</t>
         </is>
       </c>
     </row>
@@ -18364,63 +18404,63 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>reunioes</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>Reuniões</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>suficiente</t>
+          <t>canais</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>sim</t>
+          <t>redes_sociais</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Redes sociais</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>suficiente</t>
+          <t>canais</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>parcialmente</t>
+          <t>alto_falante_radio_local</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Parcialmente</t>
+          <t>Alto-falante/rádio local</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>suficiente</t>
+          <t>canais</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>nao</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Outro</t>
         </is>
       </c>
     </row>
@@ -18432,63 +18472,63 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>nao_sabe</t>
+          <t>sim</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Não sabe</t>
+          <t>Sim</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>barr_artic</t>
+          <t>suficiente</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>falta_de_contato</t>
+          <t>parcialmente</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Falta de contato</t>
+          <t>Parcialmente</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>barr_artic</t>
+          <t>suficiente</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>burocracia</t>
+          <t>nao</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Burocracia</t>
+          <t>Não</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>barr_artic</t>
+          <t>suficiente</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>desconfianca_historico_de_relaca</t>
+          <t>nao_sabe</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Desconfiança/histórico de relação</t>
+          <t>Não sabe</t>
         </is>
       </c>
     </row>
@@ -18500,12 +18540,12 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>falta_de_tempo</t>
+          <t>falta_de_contato</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Falta de tempo</t>
+          <t>Falta de contato</t>
         </is>
       </c>
     </row>
@@ -18517,63 +18557,63 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>burocracia</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Outra</t>
+          <t>Burocracia</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>ameacas</t>
+          <t>barr_artic</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>enchente</t>
+          <t>desconfianca_historico_de_relaca</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Enchente</t>
+          <t>Desconfiança/histórico de relação</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>ameacas</t>
+          <t>barr_artic</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>inundacao</t>
+          <t>falta_de_tempo</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Inundação</t>
+          <t>Falta de tempo</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>ameacas</t>
+          <t>barr_artic</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>alagamento</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Alagamento</t>
+          <t>Outra</t>
         </is>
       </c>
     </row>
@@ -18585,12 +18625,12 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>enxurrada</t>
+          <t>enchente</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Enxurrada</t>
+          <t>Enchente</t>
         </is>
       </c>
     </row>
@@ -18602,12 +18642,12 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>deslizamento</t>
+          <t>inundacao</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Deslizamento</t>
+          <t>Inundação</t>
         </is>
       </c>
     </row>
@@ -18619,12 +18659,12 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>erosao</t>
+          <t>alagamento</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Erosão</t>
+          <t>Alagamento</t>
         </is>
       </c>
     </row>
@@ -18636,12 +18676,12 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>estiagem_seca</t>
+          <t>enxurrada</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Estiagem/seca</t>
+          <t>Enxurrada</t>
         </is>
       </c>
     </row>
@@ -18653,12 +18693,12 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>falta_de_agua</t>
+          <t>deslizamento</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Falta de água</t>
+          <t>Deslizamento</t>
         </is>
       </c>
     </row>
@@ -18670,12 +18710,12 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>onda_de_calor</t>
+          <t>erosao</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Onda de calor</t>
+          <t>Erosão</t>
         </is>
       </c>
     </row>
@@ -18687,12 +18727,12 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>frio_intenso</t>
+          <t>estiagem_seca</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Frio intenso</t>
+          <t>Estiagem/seca</t>
         </is>
       </c>
     </row>
@@ -18704,12 +18744,12 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>tempestades</t>
+          <t>falta_de_agua</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Tempestades</t>
+          <t>Falta de água</t>
         </is>
       </c>
     </row>
@@ -18721,12 +18761,12 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>vendavais</t>
+          <t>onda_de_calor</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Vendavais</t>
+          <t>Onda de calor</t>
         </is>
       </c>
     </row>
@@ -18738,12 +18778,12 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>granizo</t>
+          <t>frio_intenso</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Granizo</t>
+          <t>Frio intenso</t>
         </is>
       </c>
     </row>
@@ -18755,12 +18795,12 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>ciclones</t>
+          <t>tempestades</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Ciclones</t>
+          <t>Tempestades</t>
         </is>
       </c>
     </row>
@@ -18772,12 +18812,12 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>queimadas</t>
+          <t>vendavais</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Queimadas</t>
+          <t>Vendavais</t>
         </is>
       </c>
     </row>
@@ -18789,12 +18829,12 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>incendios</t>
+          <t>granizo</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Incêndios</t>
+          <t>Granizo</t>
         </is>
       </c>
     </row>
@@ -18806,12 +18846,12 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>fumaca_poluicao_atmosferica</t>
+          <t>ciclones</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Fumaça/poluição atmosférica</t>
+          <t>Ciclones</t>
         </is>
       </c>
     </row>
@@ -18823,12 +18863,12 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>contaminacao_da_agua</t>
+          <t>queimadas</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Contaminação da água</t>
+          <t>Queimadas</t>
         </is>
       </c>
     </row>
@@ -18840,12 +18880,12 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>problemas_relacionados_a_residuo</t>
+          <t>incendios</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Problemas relacionados a resíduos</t>
+          <t>Incêndios</t>
         </is>
       </c>
     </row>
@@ -18857,63 +18897,63 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>fumaca_poluicao_atmosferica</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>Outros</t>
+          <t>Fumaça/poluição atmosférica</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>base_percepcao</t>
+          <t>ameacas</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>observacao_ao_longo_dos_anos</t>
+          <t>contaminacao_da_agua</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Observação ao longo dos anos</t>
+          <t>Contaminação da água</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>base_percepcao</t>
+          <t>ameacas</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>relatos_de_moradores_antigos</t>
+          <t>problemas_relacionados_a_residuo</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>Relatos de moradores antigos</t>
+          <t>Problemas relacionados a resíduos</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>base_percepcao</t>
+          <t>ameacas</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>comparacao_com_registros</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>Comparação com registros</t>
+          <t>Outros</t>
         </is>
       </c>
     </row>
@@ -18925,12 +18965,12 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>noticias</t>
+          <t>observacao_ao_longo_dos_anos</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>Notícias</t>
+          <t>Observação ao longo dos anos</t>
         </is>
       </c>
     </row>
@@ -18942,63 +18982,63 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>nao_sabe</t>
+          <t>relatos_de_moradores_antigos</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Não sabe</t>
+          <t>Relatos de moradores antigos</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>fontes_risco</t>
+          <t>base_percepcao</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>defesa_civil</t>
+          <t>comparacao_com_registros</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Defesa Civil</t>
+          <t>Comparação com registros</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>fontes_risco</t>
+          <t>base_percepcao</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>dados_meteorologicos</t>
+          <t>noticias</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Dados meteorológicos (ex.: INMET)</t>
+          <t>Notícias</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>fontes_risco</t>
+          <t>base_percepcao</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>universidade</t>
+          <t>nao_sabe</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Universidade</t>
+          <t>Não sabe</t>
         </is>
       </c>
     </row>
@@ -19010,12 +19050,12 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>ong</t>
+          <t>defesa_civil</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>ONG</t>
+          <t>Defesa Civil</t>
         </is>
       </c>
     </row>
@@ -19027,12 +19067,12 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>conhecimento_tradicional</t>
+          <t>dados_meteorologicos</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>Conhecimento tradicional</t>
+          <t>Dados meteorológicos (ex.: INMET)</t>
         </is>
       </c>
     </row>
@@ -19044,12 +19084,12 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>nao_ha_fonte_consultada</t>
+          <t>universidade</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>Não há fonte consultada</t>
+          <t>Universidade</t>
         </is>
       </c>
     </row>
@@ -19061,63 +19101,63 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>ong</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>Outra</t>
+          <t>ONG</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>freq_risco</t>
+          <t>fontes_risco</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>raro</t>
+          <t>conhecimento_tradicional</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>Raro (já ocorreu uma vez)</t>
+          <t>Conhecimento tradicional</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>freq_risco</t>
+          <t>fontes_risco</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>ocasional</t>
+          <t>nao_ha_fonte_consultada</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>Ocasional</t>
+          <t>Não há fonte consultada</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>freq_risco</t>
+          <t>fontes_risco</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>frequente</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>Frequente</t>
+          <t>Outra</t>
         </is>
       </c>
     </row>
@@ -19129,12 +19169,12 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>muito_frequente_recorrente</t>
+          <t>raro</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>Muito frequente/recorrente</t>
+          <t>Raro (já ocorreu uma vez)</t>
         </is>
       </c>
     </row>
@@ -19146,63 +19186,63 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>nao_sabe</t>
+          <t>ocasional</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>Não sabe</t>
+          <t>Ocasional</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>cond_amplia</t>
+          <t>freq_risco</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>acessibilidade_limitada_nas_rota</t>
+          <t>frequente</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>Acessibilidade limitada nas rotas de saída</t>
+          <t>Frequente</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>cond_amplia</t>
+          <t>freq_risco</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>ausencia_de_sinalizacao_de_emerg</t>
+          <t>muito_frequente_recorrente</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>Ausência de sinalização de emergência</t>
+          <t>Muito frequente/recorrente</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>cond_amplia</t>
+          <t>freq_risco</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>estrutura_fisica_fragilizada</t>
+          <t>nao_sabe</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>Estrutura física fragilizada</t>
+          <t>Não sabe</t>
         </is>
       </c>
     </row>
@@ -19214,12 +19254,12 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>ausencia_de_comunicacao_acessive</t>
+          <t>acessibilidade_limitada_nas_rota</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>Ausência de comunicação acessível (Libras/Braile/linguagem simples)</t>
+          <t>Acessibilidade limitada nas rotas de saída</t>
         </is>
       </c>
     </row>
@@ -19231,12 +19271,12 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>ausencia_de_plano_de_evacuacao_a</t>
+          <t>ausencia_de_sinalizacao_de_emerg</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>Ausência de plano de evacuação adaptado</t>
+          <t>Ausência de sinalização de emergência</t>
         </is>
       </c>
     </row>
@@ -19248,12 +19288,12 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>distancia_de_pontos_de_apoio_soc</t>
+          <t>estrutura_fisica_fragilizada</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>Distância de pontos de apoio/socorro</t>
+          <t>Estrutura física fragilizada</t>
         </is>
       </c>
     </row>
@@ -19265,63 +19305,63 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>ausencia_de_comunicacao_acessive</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>Outra condição</t>
+          <t>Ausência de comunicação acessível (Libras/Braile/linguagem simples)</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>cap_resp</t>
+          <t>cond_amplia</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>brigada_equipe_treinada</t>
+          <t>ausencia_de_plano_de_evacuacao_a</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>Brigada/equipe treinada</t>
+          <t>Ausência de plano de evacuação adaptado</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>cap_resp</t>
+          <t>cond_amplia</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>plano_de_evacuacao</t>
+          <t>distancia_de_pontos_de_apoio_soc</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>Plano de evacuação</t>
+          <t>Distância de pontos de apoio/socorro</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>cap_resp</t>
+          <t>cond_amplia</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>comunicacao_de_alerta</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>Comunicação de alerta</t>
+          <t>Outra condição</t>
         </is>
       </c>
     </row>
@@ -19333,12 +19373,12 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>apoio_de_rede_externa</t>
+          <t>brigada_equipe_treinada</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>Apoio de rede externa</t>
+          <t>Brigada/equipe treinada</t>
         </is>
       </c>
     </row>
@@ -19350,12 +19390,12 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>kit_de_emergencia</t>
+          <t>plano_de_evacuacao</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>Kit de emergência</t>
+          <t>Plano de evacuação</t>
         </is>
       </c>
     </row>
@@ -19367,12 +19407,12 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>nenhuma_identificada</t>
+          <t>comunicacao_de_alerta</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>Nenhuma identificada</t>
+          <t>Comunicação de alerta</t>
         </is>
       </c>
     </row>
@@ -19384,63 +19424,63 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>apoio_de_rede_externa</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>Outra</t>
+          <t>Apoio de rede externa</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>aval_cap</t>
+          <t>cap_resp</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>boa</t>
+          <t>kit_de_emergencia</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Kit de emergência</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>aval_cap</t>
+          <t>cap_resp</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>regular</t>
+          <t>nenhuma_identificada</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>Regular</t>
+          <t>Nenhuma identificada</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>aval_cap</t>
+          <t>cap_resp</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>fraca</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>Fraca</t>
+          <t>Outra</t>
         </is>
       </c>
     </row>
@@ -19452,12 +19492,12 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>inexistente</t>
+          <t>boa</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>Inexistente</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
@@ -19469,63 +19509,63 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>nao_sabe</t>
+          <t>regular</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>Não sabe</t>
+          <t>Regular</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>bma_ns</t>
+          <t>aval_cap</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>baixa</t>
+          <t>fraca</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>Baixa</t>
+          <t>Fraca</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>bma_ns</t>
+          <t>aval_cap</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>inexistente</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Inexistente</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>bma_ns</t>
+          <t>aval_cap</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>alta</t>
+          <t>nao_sabe</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Não sabe</t>
         </is>
       </c>
     </row>
@@ -19537,114 +19577,114 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>nao_sabe</t>
+          <t>baixa</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>Não sabe</t>
+          <t>Baixa</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>bma</t>
+          <t>bma_ns</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>baixa</t>
+          <t>media</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>Baixa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>bma</t>
+          <t>bma_ns</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>alta</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Alta</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>bma</t>
+          <t>bma_ns</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>alta</t>
+          <t>nao_sabe</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Não sabe</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>prio_1a5</t>
+          <t>bma</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>baixa</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>1 — Muito baixa</t>
+          <t>Baixa</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>prio_1a5</t>
+          <t>bma</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>media</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>prio_1a5</t>
+          <t>bma</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>alta</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>3 — Média</t>
+          <t>Alta</t>
         </is>
       </c>
     </row>
@@ -19656,12 +19696,12 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1 — Muito baixa</t>
         </is>
       </c>
     </row>
@@ -19673,114 +19713,114 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>5 — Muito alta</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>marc_risco</t>
+          <t>prio_1a5</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>lacuna</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>Não sabemos avaliar isso com segurança (gera lacuna de conhecimento)</t>
+          <t>3 — Média</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>marc_risco</t>
+          <t>prio_1a5</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>aval_externa</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>Requer avaliação técnica externa</t>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>marc_risco</t>
+          <t>prio_1a5</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>selecionado</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>Selecionar este risco para a Leitura Integrada e planejamento</t>
+          <t>5 — Muito alta</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>acionavel</t>
+          <t>marc_risco</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>a_escola_pode_agir_sozinha</t>
+          <t>lacuna</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>A comunidade pode agir sozinha</t>
+          <t>Não sabemos avaliar isso com segurança (gera lacuna de conhecimento)</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>acionavel</t>
+          <t>marc_risco</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>precisa_de_parceria</t>
+          <t>aval_externa</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>Precisa de parceria</t>
+          <t>Requer avaliação técnica externa</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>acionavel</t>
+          <t>marc_risco</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>esta_fora_do_alcance_da_escola</t>
+          <t>selecionado</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>Está fora do alcance da comunidade</t>
+          <t>Selecionar este risco para a Leitura Integrada e planejamento</t>
         </is>
       </c>
     </row>
@@ -19792,63 +19832,63 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>nao_sabe</t>
+          <t>a_escola_pode_agir_sozinha</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>Não sabe</t>
+          <t>A comunidade pode agir sozinha</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>resp_tipo</t>
+          <t>acionavel</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>acao_estrutural</t>
+          <t>precisa_de_parceria</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>Ação estrutural</t>
+          <t>Precisa de parceria</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>resp_tipo</t>
+          <t>acionavel</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>acao_pedagogica</t>
+          <t>esta_fora_do_alcance_da_escola</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>Ação pedagógica</t>
+          <t>Está fora do alcance da comunidade</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>resp_tipo</t>
+          <t>acionavel</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>articulacao_institucional</t>
+          <t>nao_sabe</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>Articulação institucional</t>
+          <t>Não sabe</t>
         </is>
       </c>
     </row>
@@ -19860,12 +19900,12 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>comunicacao</t>
+          <t>acao_estrutural</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>Comunicação</t>
+          <t>Ação estrutural</t>
         </is>
       </c>
     </row>
@@ -19877,12 +19917,12 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>mobilizacao_comunitaria</t>
+          <t>acao_pedagogica</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>Mobilização comunitária</t>
+          <t>Ação pedagógica</t>
         </is>
       </c>
     </row>
@@ -19894,12 +19934,12 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>monitoramento</t>
+          <t>articulacao_institucional</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>Monitoramento</t>
+          <t>Articulação institucional</t>
         </is>
       </c>
     </row>
@@ -19911,63 +19951,63 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>comunicacao</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>Comunicação</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>status_ativ</t>
+          <t>resp_tipo</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>planejada</t>
+          <t>mobilizacao_comunitaria</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>Planejada</t>
+          <t>Mobilização comunitária</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>status_ativ</t>
+          <t>resp_tipo</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>em_andamento</t>
+          <t>monitoramento</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>Em andamento</t>
+          <t>Monitoramento</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>status_ativ</t>
+          <t>resp_tipo</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>concluida</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>Concluída</t>
+          <t>Outro</t>
         </is>
       </c>
     </row>
@@ -19979,63 +20019,63 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>nao_realizada</t>
+          <t>planejada</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>Não realizada</t>
+          <t>Planejada</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>papel_estud2</t>
+          <t>status_ativ</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>espectador</t>
+          <t>em_andamento</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>Espectador</t>
+          <t>Em andamento</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>papel_estud2</t>
+          <t>status_ativ</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>participante</t>
+          <t>concluida</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>Participante</t>
+          <t>Concluída</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>papel_estud2</t>
+          <t>status_ativ</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>protagonista</t>
+          <t>nao_realizada</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>Protagonista</t>
+          <t>Não realizada</t>
         </is>
       </c>
     </row>
@@ -20047,63 +20087,63 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>coprodutor</t>
+          <t>espectador</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>Coprodutor</t>
+          <t>Espectador</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>viabilidade</t>
+          <t>papel_estud2</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>alta</t>
+          <t>participante</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Participante</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>viabilidade</t>
+          <t>papel_estud2</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>protagonista</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Protagonista</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>viabilidade</t>
+          <t>papel_estud2</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>baixa</t>
+          <t>coprodutor</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>Baixa</t>
+          <t>Coprodutor</t>
         </is>
       </c>
     </row>
@@ -20115,63 +20155,63 @@
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>incerta</t>
+          <t>alta</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>Incerta</t>
+          <t>Alta</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>barr_impl</t>
+          <t>viabilidade</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>tempo</t>
+          <t>media</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>Tempo</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>barr_impl</t>
+          <t>viabilidade</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>recursos</t>
+          <t>baixa</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>Recursos</t>
+          <t>Baixa</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>barr_impl</t>
+          <t>viabilidade</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>articulacao</t>
+          <t>incerta</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>Articulação</t>
+          <t>Incerta</t>
         </is>
       </c>
     </row>
@@ -20183,12 +20223,12 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>clima</t>
+          <t>tempo</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>Clima</t>
+          <t>Tempo</t>
         </is>
       </c>
     </row>
@@ -20200,12 +20240,12 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>adesao</t>
+          <t>recursos</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>Adesão</t>
+          <t>Recursos</t>
         </is>
       </c>
     </row>
@@ -20217,114 +20257,114 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>articulacao</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>Outra</t>
+          <t>Articulação</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>coerencia</t>
+          <t>barr_impl</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>coerente</t>
+          <t>clima</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>Coerente</t>
+          <t>Clima</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>coerencia</t>
+          <t>barr_impl</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>parcialmente_coerente</t>
+          <t>adesao</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>Parcialmente coerente</t>
+          <t>Adesão</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>coerencia</t>
+          <t>barr_impl</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>nao_tenho_certeza</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>Não tenho certeza</t>
+          <t>Outra</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>com_final</t>
+          <t>coerencia</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>informar</t>
+          <t>coerente</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>Informar</t>
+          <t>Coerente</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>com_final</t>
+          <t>coerencia</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>sensibilizar</t>
+          <t>parcialmente_coerente</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>Sensibilizar</t>
+          <t>Parcialmente coerente</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>com_final</t>
+          <t>coerencia</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>mobilizar</t>
+          <t>nao_tenho_certeza</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>Mobilizar</t>
+          <t>Não tenho certeza</t>
         </is>
       </c>
     </row>
@@ -20336,12 +20376,12 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>prestar_contas</t>
+          <t>informar</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>Prestar contas</t>
+          <t>Informar</t>
         </is>
       </c>
     </row>
@@ -20353,12 +20393,12 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>dar_voz_a_comunidade</t>
+          <t>sensibilizar</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>Dar voz à comunidade</t>
+          <t>Sensibilizar</t>
         </is>
       </c>
     </row>
@@ -20370,63 +20410,63 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>mobilizar</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>Mobilizar</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>com_publico</t>
+          <t>com_final</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>estudantes</t>
+          <t>prestar_contas</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>Estudantes</t>
+          <t>Prestar contas</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>com_publico</t>
+          <t>com_final</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>professores</t>
+          <t>dar_voz_a_comunidade</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>Professores(as)</t>
+          <t>Dar voz à comunidade</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>com_publico</t>
+          <t>com_final</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>familias</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>Famílias</t>
+          <t>Outro</t>
         </is>
       </c>
     </row>
@@ -20438,12 +20478,12 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>comunidade</t>
+          <t>estudantes</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>Comunidade</t>
+          <t>Estudantes</t>
         </is>
       </c>
     </row>
@@ -20455,12 +20495,12 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>poder_publico</t>
+          <t>professores</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>Poder público</t>
+          <t>Professores(as)</t>
         </is>
       </c>
     </row>
@@ -20472,63 +20512,63 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>familias</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>Famílias</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>com_escuta</t>
+          <t>com_publico</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>caixa_de_sugestoes</t>
+          <t>comunidade</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>Caixa de sugestões</t>
+          <t>Comunidade</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>com_escuta</t>
+          <t>com_publico</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>roda_de_conversa</t>
+          <t>poder_publico</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>Roda de conversa</t>
+          <t>Poder público</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>com_escuta</t>
+          <t>com_publico</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>formulario</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>Formulário</t>
+          <t>Outro</t>
         </is>
       </c>
     </row>
@@ -20540,12 +20580,12 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>redes_sociais</t>
+          <t>caixa_de_sugestoes</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>Redes sociais</t>
+          <t>Caixa de sugestões</t>
         </is>
       </c>
     </row>
@@ -20557,12 +20597,12 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>reuniao</t>
+          <t>roda_de_conversa</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>Reunião</t>
+          <t>Roda de conversa</t>
         </is>
       </c>
     </row>
@@ -20574,63 +20614,63 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>formulario</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>Formulário</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>com_midia</t>
+          <t>com_escuta</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>cartaz</t>
+          <t>redes_sociais</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>Cartaz</t>
+          <t>Redes sociais</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>com_midia</t>
+          <t>com_escuta</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>radio_escolar</t>
+          <t>reuniao</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>Rádio escolar</t>
+          <t>Reunião</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>com_midia</t>
+          <t>com_escuta</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>video</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>Vídeo</t>
+          <t>Outro</t>
         </is>
       </c>
     </row>
@@ -20642,12 +20682,12 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>redes_sociais</t>
+          <t>cartaz</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>Redes sociais</t>
+          <t>Cartaz</t>
         </is>
       </c>
     </row>
@@ -20659,12 +20699,12 @@
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>jornal_mural</t>
+          <t>radio_escolar</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>Jornal mural</t>
+          <t>Rádio escolar</t>
         </is>
       </c>
     </row>
@@ -20676,12 +20716,12 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>teatro</t>
+          <t>video</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>Teatro</t>
+          <t>Vídeo</t>
         </is>
       </c>
     </row>
@@ -20693,12 +20733,12 @@
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>podcast</t>
+          <t>redes_sociais</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>Podcast</t>
+          <t>Redes sociais</t>
         </is>
       </c>
     </row>
@@ -20710,63 +20750,63 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>jornal_mural</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>Jornal mural</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>com_barr</t>
+          <t>com_midia</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>idioma_linguagem_tecnica</t>
+          <t>teatro</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>Idioma/linguagem técnica</t>
+          <t>Teatro</t>
         </is>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>com_barr</t>
+          <t>com_midia</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>acessibilidade_para_pessoas_com_</t>
+          <t>podcast</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>Acessibilidade para pessoas com deficiência</t>
+          <t>Podcast</t>
         </is>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>com_barr</t>
+          <t>com_midia</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>falta_de_conectividade</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>Falta de conectividade</t>
+          <t>Outro</t>
         </is>
       </c>
     </row>
@@ -20778,12 +20818,12 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>alfabetizacao</t>
+          <t>idioma_linguagem_tecnica</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>Alfabetização</t>
+          <t>Idioma/linguagem técnica</t>
         </is>
       </c>
     </row>
@@ -20795,63 +20835,63 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>acessibilidade_para_pessoas_com_</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>Outra</t>
+          <t>Acessibilidade para pessoas com deficiência</t>
         </is>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>com_decisao</t>
+          <t>com_barr</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>nenhuma</t>
+          <t>falta_de_conectividade</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>Nenhuma</t>
+          <t>Falta de conectividade</t>
         </is>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>com_decisao</t>
+          <t>com_barr</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>sao_consultados</t>
+          <t>alfabetizacao</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>São consultados</t>
+          <t>Alfabetização</t>
         </is>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>com_decisao</t>
+          <t>com_barr</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>colaboram_na_producao</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>Colaboram na produção</t>
+          <t>Outra</t>
         </is>
       </c>
     </row>
@@ -20863,114 +20903,114 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>decidem_conteudo_formato</t>
+          <t>nenhuma</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>Decidem conteúdo/formato</t>
+          <t>Nenhuma</t>
         </is>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>ind_tipo</t>
+          <t>com_decisao</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>processo</t>
+          <t>sao_consultados</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>Processo</t>
+          <t>São consultados</t>
         </is>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>ind_tipo</t>
+          <t>com_decisao</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>participacao</t>
+          <t>colaboram_na_producao</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>Participação</t>
+          <t>Colaboram na produção</t>
         </is>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>ind_tipo</t>
+          <t>com_decisao</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>resultado</t>
+          <t>decidem_conteudo_formato</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>Resultado</t>
+          <t>Decidem conteúdo/formato</t>
         </is>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>periodicidade</t>
+          <t>ind_tipo</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>mensal</t>
+          <t>processo</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>Mensal</t>
+          <t>Processo</t>
         </is>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>periodicidade</t>
+          <t>ind_tipo</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>bimestral</t>
+          <t>participacao</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>Bimestral</t>
+          <t>Participação</t>
         </is>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>periodicidade</t>
+          <t>ind_tipo</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>trimestral</t>
+          <t>resultado</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>Trimestral</t>
+          <t>Resultado</t>
         </is>
       </c>
     </row>
@@ -20982,12 +21022,12 @@
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>semestral</t>
+          <t>mensal</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>Semestral</t>
+          <t>Mensal</t>
         </is>
       </c>
     </row>
@@ -20999,12 +21039,12 @@
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>anual</t>
+          <t>bimestral</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>Anual</t>
+          <t>Bimestral</t>
         </is>
       </c>
     </row>
@@ -21016,63 +21056,63 @@
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>por_evento</t>
+          <t>trimestral</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>Por evento</t>
+          <t>Trimestral</t>
         </is>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>perfil_com</t>
+          <t>periodicidade</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>estudante</t>
+          <t>semestral</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>Estudante</t>
+          <t>Semestral</t>
         </is>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>perfil_com</t>
+          <t>periodicidade</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>ex_escola</t>
+          <t>anual</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>Pessoa que já trabalhou em escola, mas atualmente não trabalha</t>
+          <t>Anual</t>
         </is>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>perfil_com</t>
+          <t>periodicidade</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>ong</t>
+          <t>por_evento</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>Pessoa de ONG ou outra organização da sociedade civil</t>
+          <t>Por evento</t>
         </is>
       </c>
     </row>
@@ -21084,63 +21124,63 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>estudante</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>Estudante</t>
         </is>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>nivel_estudo</t>
+          <t>perfil_com</t>
         </is>
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>ensino_fundamental</t>
+          <t>ex_escola</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>Ensino Fundamental</t>
+          <t>Pessoa que já trabalhou em escola, mas atualmente não trabalha</t>
         </is>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>nivel_estudo</t>
+          <t>perfil_com</t>
         </is>
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>ensino_medio</t>
+          <t>ong</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>Ensino Médio</t>
+          <t>Pessoa de ONG ou outra organização da sociedade civil</t>
         </is>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>nivel_estudo</t>
+          <t>perfil_com</t>
         </is>
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>eja</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>EJA</t>
+          <t>Outro</t>
         </is>
       </c>
     </row>
@@ -21152,12 +21192,12 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>ensino_tecnico_profissional</t>
+          <t>ensino_fundamental</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>Ensino técnico/profissional</t>
+          <t>Ensino Fundamental</t>
         </is>
       </c>
     </row>
@@ -21169,12 +21209,12 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>graduacao</t>
+          <t>ensino_medio</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>Graduação</t>
+          <t>Ensino Médio</t>
         </is>
       </c>
     </row>
@@ -21186,12 +21226,12 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>pos_graduacao</t>
+          <t>eja</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>Pós-graduação</t>
+          <t>EJA</t>
         </is>
       </c>
     </row>
@@ -21203,63 +21243,63 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>ensino_tecnico_profissional</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>Ensino técnico/profissional</t>
         </is>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>funcao_ex</t>
+          <t>nivel_estudo</t>
         </is>
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>professor</t>
+          <t>graduacao</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>Professor(a)</t>
+          <t>Graduação</t>
         </is>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>funcao_ex</t>
+          <t>nivel_estudo</t>
         </is>
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>gestor_direcao</t>
+          <t>pos_graduacao</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>Gestor(a) / Direção</t>
+          <t>Pós-graduação</t>
         </is>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>funcao_ex</t>
+          <t>nivel_estudo</t>
         </is>
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>coordenacao_supervisao_pedagogic</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>Coordenação / supervisão pedagógica</t>
+          <t>Outro</t>
         </is>
       </c>
     </row>
@@ -21271,12 +21311,12 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>apoio_escolar_funcionario</t>
+          <t>professor</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>Apoio escolar / funcionário(a)</t>
+          <t>Professor(a)</t>
         </is>
       </c>
     </row>
@@ -21288,63 +21328,63 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>gestor_direcao</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>Gestor(a) / Direção</t>
         </is>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>ong_area</t>
+          <t>funcao_ex</t>
         </is>
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>educacao</t>
+          <t>coordenacao_supervisao_pedagogic</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>Educação</t>
+          <t>Coordenação / supervisão pedagógica</t>
         </is>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>ong_area</t>
+          <t>funcao_ex</t>
         </is>
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>meio_ambiente</t>
+          <t>apoio_escolar_funcionario</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>Meio ambiente</t>
+          <t>Apoio escolar / funcionário(a)</t>
         </is>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>ong_area</t>
+          <t>funcao_ex</t>
         </is>
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>direitos_humanos</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>Direitos humanos</t>
+          <t>Outro</t>
         </is>
       </c>
     </row>
@@ -21356,12 +21396,12 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>saude</t>
+          <t>educacao</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>Saúde</t>
+          <t>Educação</t>
         </is>
       </c>
     </row>
@@ -21373,12 +21413,12 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>cultura</t>
+          <t>meio_ambiente</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>Cultura</t>
+          <t>Meio ambiente</t>
         </is>
       </c>
     </row>
@@ -21390,12 +21430,12 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>assistencia_social</t>
+          <t>direitos_humanos</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>Assistência social</t>
+          <t>Direitos humanos</t>
         </is>
       </c>
     </row>
@@ -21407,12 +21447,12 @@
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>povos_e_comunidades_tradicionais</t>
+          <t>saude</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>Povos e comunidades tradicionais</t>
+          <t>Saúde</t>
         </is>
       </c>
     </row>
@@ -21424,63 +21464,63 @@
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>cultura</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>Cultura</t>
         </is>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>vinculo_escola</t>
+          <t>ong_area</t>
         </is>
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>nenhum</t>
+          <t>assistencia_social</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>Nenhum vínculo atual com escola</t>
+          <t>Assistência social</t>
         </is>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>vinculo_escola</t>
+          <t>ong_area</t>
         </is>
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>familiar_de_estudante</t>
+          <t>povos_e_comunidades_tradicionais</t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>Familiar de estudante</t>
+          <t>Povos e comunidades tradicionais</t>
         </is>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>vinculo_escola</t>
+          <t>ong_area</t>
         </is>
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>ex_aluno</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>Ex-aluno(a)</t>
+          <t>Outro</t>
         </is>
       </c>
     </row>
@@ -21492,12 +21532,12 @@
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>voluntario_ou_parceiro_de_escola</t>
+          <t>nenhum</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>Voluntário(a) ou parceiro(a) de escola</t>
+          <t>Nenhum vínculo atual com escola</t>
         </is>
       </c>
     </row>
@@ -21509,12 +21549,12 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>atuo_em_projetos_em_escolas_por_</t>
+          <t>familiar_de_estudante</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>Atuo em projetos em escolas por meio de organização</t>
+          <t>Familiar de estudante</t>
         </is>
       </c>
     </row>
@@ -21526,63 +21566,63 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>ex_aluno</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>Ex-aluno(a)</t>
         </is>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>onde_ea_com</t>
+          <t>vinculo_escola</t>
         </is>
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>escolas_do_territorio</t>
+          <t>voluntario_ou_parceiro_de_escola</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>Escolas do território</t>
+          <t>Voluntário(a) ou parceiro(a) de escola</t>
         </is>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>onde_ea_com</t>
+          <t>vinculo_escola</t>
         </is>
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>associacoes_ongs</t>
+          <t>atuo_em_projetos_em_escolas_por_</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>Associações / ONGs</t>
+          <t>Atuo em projetos em escolas por meio de organização</t>
         </is>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>onde_ea_com</t>
+          <t>vinculo_escola</t>
         </is>
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>mutiroes_e_acoes_comunitarias</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>Mutirões e ações comunitárias</t>
+          <t>Outro</t>
         </is>
       </c>
     </row>
@@ -21594,12 +21634,12 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>igrejas_grupos_religiosos</t>
+          <t>escolas_do_territorio</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>Igrejas / grupos religiosos</t>
+          <t>Escolas do território</t>
         </is>
       </c>
     </row>
@@ -21611,12 +21651,12 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>coletivos_e_grupos_de_jovens</t>
+          <t>associacoes_ongs</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>Coletivos e grupos de jovens</t>
+          <t>Associações / ONGs</t>
         </is>
       </c>
     </row>
@@ -21628,12 +21668,12 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>universidades_institutos</t>
+          <t>mutiroes_e_acoes_comunitarias</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>Universidades / institutos</t>
+          <t>Mutirões e ações comunitárias</t>
         </is>
       </c>
     </row>
@@ -21645,12 +21685,12 @@
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>rodas_de_conversa_e_oficinas</t>
+          <t>igrejas_grupos_religiosos</t>
         </is>
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>Rodas de conversa e oficinas</t>
+          <t>Igrejas / grupos religiosos</t>
         </is>
       </c>
     </row>
@@ -21662,12 +21702,12 @@
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>redes_sociais_comunicacao</t>
+          <t>coletivos_e_grupos_de_jovens</t>
         </is>
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>Redes sociais / comunicação</t>
+          <t>Coletivos e grupos de jovens</t>
         </is>
       </c>
     </row>
@@ -21679,12 +21719,12 @@
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>nao_acontece</t>
+          <t>universidades_institutos</t>
         </is>
       </c>
       <c r="C483" t="inlineStr">
         <is>
-          <t>Não acontece</t>
+          <t>Universidades / institutos</t>
         </is>
       </c>
     </row>
@@ -21696,63 +21736,63 @@
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>rodas_de_conversa_e_oficinas</t>
         </is>
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>Rodas de conversa e oficinas</t>
         </is>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>instit_com</t>
+          <t>onde_ea_com</t>
         </is>
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>inexistente</t>
+          <t>redes_sociais_comunicacao</t>
         </is>
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>Inexistente</t>
+          <t>Redes sociais / comunicação</t>
         </is>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>instit_com</t>
+          <t>onde_ea_com</t>
         </is>
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>isolada_ocasional</t>
+          <t>nao_acontece</t>
         </is>
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>Isolada/ocasional</t>
+          <t>Não acontece</t>
         </is>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>instit_com</t>
+          <t>onde_ea_com</t>
         </is>
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>recorrente_dependente_de_poucas_</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>Recorrente, dependente de poucas pessoas</t>
+          <t>Outro</t>
         </is>
       </c>
     </row>
@@ -21764,12 +21804,12 @@
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>presente_em_diferentes_grupos_or</t>
+          <t>inexistente</t>
         </is>
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>Presente em diferentes grupos/organizações</t>
+          <t>Inexistente</t>
         </is>
       </c>
     </row>
@@ -21781,12 +21821,12 @@
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>integrada_as_acoes_da_comunidade</t>
+          <t>isolada_ocasional</t>
         </is>
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>Integrada às ações da comunidade</t>
+          <t>Isolada/ocasional</t>
         </is>
       </c>
     </row>
@@ -21798,12 +21838,12 @@
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>continua_e_reconhecida_pela_comu</t>
+          <t>recorrente_dependente_de_poucas_</t>
         </is>
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>Contínua e reconhecida pela comunidade</t>
+          <t>Recorrente, dependente de poucas pessoas</t>
         </is>
       </c>
     </row>
@@ -21815,63 +21855,63 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>nao_sabe</t>
+          <t>presente_em_diferentes_grupos_or</t>
         </is>
       </c>
       <c r="C491" t="inlineStr">
         <is>
-          <t>Não sabe</t>
+          <t>Presente em diferentes grupos/organizações</t>
         </is>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>esc_territorio</t>
+          <t>instit_com</t>
         </is>
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>sim_com_frequencia</t>
+          <t>integrada_as_acoes_da_comunidade</t>
         </is>
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>Sim, com frequência</t>
+          <t>Integrada às ações da comunidade</t>
         </is>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>esc_territorio</t>
+          <t>instit_com</t>
         </is>
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>as_vezes</t>
+          <t>continua_e_reconhecida_pela_comu</t>
         </is>
       </c>
       <c r="C493" t="inlineStr">
         <is>
-          <t>Às vezes</t>
+          <t>Contínua e reconhecida pela comunidade</t>
         </is>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>esc_territorio</t>
+          <t>instit_com</t>
         </is>
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>raramente</t>
+          <t>nao_sabe</t>
         </is>
       </c>
       <c r="C494" t="inlineStr">
         <is>
-          <t>Raramente</t>
+          <t>Não sabe</t>
         </is>
       </c>
     </row>
@@ -21883,12 +21923,12 @@
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>nao</t>
+          <t>sim_com_frequencia</t>
         </is>
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim, com frequência</t>
         </is>
       </c>
     </row>
@@ -21900,12 +21940,12 @@
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>nao_existe_escola_no_territorio</t>
+          <t>as_vezes</t>
         </is>
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>Não existe escola no território</t>
+          <t>Às vezes</t>
         </is>
       </c>
     </row>
@@ -21917,63 +21957,63 @@
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>nao_sei</t>
+          <t>raramente</t>
         </is>
       </c>
       <c r="C497" t="inlineStr">
         <is>
-          <t>Não sei</t>
+          <t>Raramente</t>
         </is>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>contexto_ea_com</t>
+          <t>esc_territorio</t>
         </is>
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>escola</t>
+          <t>nao</t>
         </is>
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>Escola</t>
+          <t>Não</t>
         </is>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>contexto_ea_com</t>
+          <t>esc_territorio</t>
         </is>
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>espaco_comunitario_associacao</t>
+          <t>nao_existe_escola_no_territorio</t>
         </is>
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>Espaço comunitário / associação</t>
+          <t>Não existe escola no território</t>
         </is>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>contexto_ea_com</t>
+          <t>esc_territorio</t>
         </is>
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>rua_praca_ou_area_externa</t>
+          <t>nao_sei</t>
         </is>
       </c>
       <c r="C500" t="inlineStr">
         <is>
-          <t>Rua, praça ou área externa</t>
+          <t>Não sei</t>
         </is>
       </c>
     </row>
@@ -21985,12 +22025,12 @@
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>visita_de_campo_trilha</t>
+          <t>escola</t>
         </is>
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>Visita de campo / trilha</t>
+          <t>Escola</t>
         </is>
       </c>
     </row>
@@ -22002,12 +22042,12 @@
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>evento_feira</t>
+          <t>espaco_comunitario_associacao</t>
         </is>
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>Evento / feira</t>
+          <t>Espaço comunitário / associação</t>
         </is>
       </c>
     </row>
@@ -22019,12 +22059,12 @@
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>online_redes_sociais</t>
+          <t>rua_praca_ou_area_externa</t>
         </is>
       </c>
       <c r="C503" t="inlineStr">
         <is>
-          <t>Online / redes sociais</t>
+          <t>Rua, praça ou área externa</t>
         </is>
       </c>
     </row>
@@ -22036,63 +22076,63 @@
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>visita_de_campo_trilha</t>
         </is>
       </c>
       <c r="C504" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>Visita de campo / trilha</t>
         </is>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>quem_planejou_com</t>
+          <t>contexto_ea_com</t>
         </is>
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>estudantes</t>
+          <t>evento_feira</t>
         </is>
       </c>
       <c r="C505" t="inlineStr">
         <is>
-          <t>Estudantes</t>
+          <t>Evento / feira</t>
         </is>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>quem_planejou_com</t>
+          <t>contexto_ea_com</t>
         </is>
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>professores</t>
+          <t>online_redes_sociais</t>
         </is>
       </c>
       <c r="C506" t="inlineStr">
         <is>
-          <t>Professores(as)</t>
+          <t>Online / redes sociais</t>
         </is>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>quem_planejou_com</t>
+          <t>contexto_ea_com</t>
         </is>
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>associacao_ong</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C507" t="inlineStr">
         <is>
-          <t>Associação / ONG</t>
+          <t>Outro</t>
         </is>
       </c>
     </row>
@@ -22104,12 +22144,12 @@
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>liderancas_comunitarias</t>
+          <t>estudantes</t>
         </is>
       </c>
       <c r="C508" t="inlineStr">
         <is>
-          <t>Lideranças comunitárias</t>
+          <t>Estudantes</t>
         </is>
       </c>
     </row>
@@ -22121,12 +22161,12 @@
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>poder_publico</t>
+          <t>professores</t>
         </is>
       </c>
       <c r="C509" t="inlineStr">
         <is>
-          <t>Poder público</t>
+          <t>Professores(as)</t>
         </is>
       </c>
     </row>
@@ -22138,12 +22178,12 @@
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>universidade_instituto</t>
+          <t>associacao_ong</t>
         </is>
       </c>
       <c r="C510" t="inlineStr">
         <is>
-          <t>Universidade / instituto</t>
+          <t>Associação / ONG</t>
         </is>
       </c>
     </row>
@@ -22155,12 +22195,12 @@
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>moradores_em_geral</t>
+          <t>liderancas_comunitarias</t>
         </is>
       </c>
       <c r="C511" t="inlineStr">
         <is>
-          <t>Moradores em geral</t>
+          <t>Lideranças comunitárias</t>
         </is>
       </c>
     </row>
@@ -22172,63 +22212,63 @@
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>poder_publico</t>
         </is>
       </c>
       <c r="C512" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>Poder público</t>
         </is>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>continuidade_com</t>
+          <t>quem_planejou_com</t>
         </is>
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>depende_de_pessoas_especificas</t>
+          <t>universidade_instituto</t>
         </is>
       </c>
       <c r="C513" t="inlineStr">
         <is>
-          <t>Depende de pessoas específicas</t>
+          <t>Universidade / instituto</t>
         </is>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>continuidade_com</t>
+          <t>quem_planejou_com</t>
         </is>
       </c>
       <c r="B514" t="inlineStr">
         <is>
-          <t>garantida</t>
+          <t>moradores_em_geral</t>
         </is>
       </c>
       <c r="C514" t="inlineStr">
         <is>
-          <t>Tem continuidade garantida (organização ou parceria)</t>
+          <t>Moradores em geral</t>
         </is>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>continuidade_com</t>
+          <t>quem_planejou_com</t>
         </is>
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>incerta</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C515" t="inlineStr">
         <is>
-          <t>Incerta</t>
+          <t>Outro</t>
         </is>
       </c>
     </row>
@@ -22240,63 +22280,63 @@
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>nao_sabe</t>
+          <t>depende_de_pessoas_especificas</t>
         </is>
       </c>
       <c r="C516" t="inlineStr">
         <is>
-          <t>Não sabe</t>
+          <t>Depende de pessoas específicas</t>
         </is>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>causa_dif_com</t>
+          <t>continuidade_com</t>
         </is>
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>falta_de_formacao</t>
+          <t>garantida</t>
         </is>
       </c>
       <c r="C517" t="inlineStr">
         <is>
-          <t>Falta de formação</t>
+          <t>Tem continuidade garantida (organização ou parceria)</t>
         </is>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>causa_dif_com</t>
+          <t>continuidade_com</t>
         </is>
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>falta_de_material</t>
+          <t>incerta</t>
         </is>
       </c>
       <c r="C518" t="inlineStr">
         <is>
-          <t>Falta de material</t>
+          <t>Incerta</t>
         </is>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>causa_dif_com</t>
+          <t>continuidade_com</t>
         </is>
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>tema_sensivel_delicado</t>
+          <t>nao_sabe</t>
         </is>
       </c>
       <c r="C519" t="inlineStr">
         <is>
-          <t>Tema sensível/delicado</t>
+          <t>Não sabe</t>
         </is>
       </c>
     </row>
@@ -22308,12 +22348,12 @@
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>falta_de_tempo</t>
+          <t>falta_de_formacao</t>
         </is>
       </c>
       <c r="C520" t="inlineStr">
         <is>
-          <t>Falta de tempo</t>
+          <t>Falta de formação</t>
         </is>
       </c>
     </row>
@@ -22325,12 +22365,12 @@
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>falta_de_apoio_ou_recursos</t>
+          <t>falta_de_material</t>
         </is>
       </c>
       <c r="C521" t="inlineStr">
         <is>
-          <t>Falta de apoio ou recursos</t>
+          <t>Falta de material</t>
         </is>
       </c>
     </row>
@@ -22342,63 +22382,63 @@
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>tema_sensivel_delicado</t>
         </is>
       </c>
       <c r="C522" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>Tema sensível/delicado</t>
         </is>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>apoio_com</t>
+          <t>causa_dif_com</t>
         </is>
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>formacao</t>
+          <t>falta_de_tempo</t>
         </is>
       </c>
       <c r="C523" t="inlineStr">
         <is>
-          <t>Formação</t>
+          <t>Falta de tempo</t>
         </is>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>apoio_com</t>
+          <t>causa_dif_com</t>
         </is>
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>material_educativo</t>
+          <t>falta_de_apoio_ou_recursos</t>
         </is>
       </c>
       <c r="C524" t="inlineStr">
         <is>
-          <t>Material educativo</t>
+          <t>Falta de apoio ou recursos</t>
         </is>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>apoio_com</t>
+          <t>causa_dif_com</t>
         </is>
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>tempo_para_se_organizar</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C525" t="inlineStr">
         <is>
-          <t>Tempo para se organizar</t>
+          <t>Outro</t>
         </is>
       </c>
     </row>
@@ -22410,12 +22450,12 @@
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>apoio_de_liderancas_poder_public</t>
+          <t>formacao</t>
         </is>
       </c>
       <c r="C526" t="inlineStr">
         <is>
-          <t>Apoio de lideranças / poder público</t>
+          <t>Formação</t>
         </is>
       </c>
     </row>
@@ -22427,12 +22467,12 @@
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>parcerias</t>
+          <t>material_educativo</t>
         </is>
       </c>
       <c r="C527" t="inlineStr">
         <is>
-          <t>Parcerias</t>
+          <t>Material educativo</t>
         </is>
       </c>
     </row>
@@ -22444,12 +22484,12 @@
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>recursos_financeiros</t>
+          <t>tempo_para_se_organizar</t>
         </is>
       </c>
       <c r="C528" t="inlineStr">
         <is>
-          <t>Recursos financeiros</t>
+          <t>Tempo para se organizar</t>
         </is>
       </c>
     </row>
@@ -22461,63 +22501,63 @@
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>apoio_de_liderancas_poder_public</t>
         </is>
       </c>
       <c r="C529" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>Apoio de lideranças / poder público</t>
         </is>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>barreiras_com</t>
+          <t>apoio_com</t>
         </is>
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>tempo</t>
+          <t>parcerias</t>
         </is>
       </c>
       <c r="C530" t="inlineStr">
         <is>
-          <t>Tempo</t>
+          <t>Parcerias</t>
         </is>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>barreiras_com</t>
+          <t>apoio_com</t>
         </is>
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>formacao</t>
+          <t>recursos_financeiros</t>
         </is>
       </c>
       <c r="C531" t="inlineStr">
         <is>
-          <t>Formação</t>
+          <t>Recursos financeiros</t>
         </is>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>barreiras_com</t>
+          <t>apoio_com</t>
         </is>
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>materiais</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C532" t="inlineStr">
         <is>
-          <t>Materiais</t>
+          <t>Outro</t>
         </is>
       </c>
     </row>
@@ -22529,12 +22569,12 @@
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>recursos_financeiros</t>
+          <t>tempo</t>
         </is>
       </c>
       <c r="C533" t="inlineStr">
         <is>
-          <t>Recursos financeiros</t>
+          <t>Tempo</t>
         </is>
       </c>
     </row>
@@ -22546,12 +22586,12 @@
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>apoio_do_poder_publico</t>
+          <t>formacao</t>
         </is>
       </c>
       <c r="C534" t="inlineStr">
         <is>
-          <t>Apoio do poder público</t>
+          <t>Formação</t>
         </is>
       </c>
     </row>
@@ -22563,12 +22603,12 @@
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>apoio_de_liderancas</t>
+          <t>materiais</t>
         </is>
       </c>
       <c r="C535" t="inlineStr">
         <is>
-          <t>Apoio de lideranças</t>
+          <t>Materiais</t>
         </is>
       </c>
     </row>
@@ -22580,12 +22620,12 @@
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>organizacao_coletiva_planejament</t>
+          <t>recursos_financeiros</t>
         </is>
       </c>
       <c r="C536" t="inlineStr">
         <is>
-          <t>Organização coletiva / planejamento conjunto</t>
+          <t>Recursos financeiros</t>
         </is>
       </c>
     </row>
@@ -22597,12 +22637,12 @@
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>informacoes_sobre_o_territorio</t>
+          <t>apoio_do_poder_publico</t>
         </is>
       </c>
       <c r="C537" t="inlineStr">
         <is>
-          <t>Informações sobre o território</t>
+          <t>Apoio do poder público</t>
         </is>
       </c>
     </row>
@@ -22614,12 +22654,12 @@
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>descontinuidade_das_acoes</t>
+          <t>apoio_de_liderancas</t>
         </is>
       </c>
       <c r="C538" t="inlineStr">
         <is>
-          <t>Descontinuidade das ações</t>
+          <t>Apoio de lideranças</t>
         </is>
       </c>
     </row>
@@ -22631,12 +22671,12 @@
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>rotatividade_de_pessoas</t>
+          <t>organizacao_coletiva_planejament</t>
         </is>
       </c>
       <c r="C539" t="inlineStr">
         <is>
-          <t>Rotatividade de pessoas</t>
+          <t>Organização coletiva / planejamento conjunto</t>
         </is>
       </c>
     </row>
@@ -22648,63 +22688,63 @@
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>informacoes_sobre_o_territorio</t>
         </is>
       </c>
       <c r="C540" t="inlineStr">
         <is>
-          <t>Outras</t>
+          <t>Informações sobre o território</t>
         </is>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t>materiais_com</t>
+          <t>barreiras_com</t>
         </is>
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>livros_e_cartilhas</t>
+          <t>descontinuidade_das_acoes</t>
         </is>
       </c>
       <c r="C541" t="inlineStr">
         <is>
-          <t>Livros e cartilhas</t>
+          <t>Descontinuidade das ações</t>
         </is>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="inlineStr">
         <is>
-          <t>materiais_com</t>
+          <t>barreiras_com</t>
         </is>
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>videos</t>
+          <t>rotatividade_de_pessoas</t>
         </is>
       </c>
       <c r="C542" t="inlineStr">
         <is>
-          <t>Vídeos</t>
+          <t>Rotatividade de pessoas</t>
         </is>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="inlineStr">
         <is>
-          <t>materiais_com</t>
+          <t>barreiras_com</t>
         </is>
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>jogos</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C543" t="inlineStr">
         <is>
-          <t>Jogos</t>
+          <t>Outras</t>
         </is>
       </c>
     </row>
@@ -22716,12 +22756,12 @@
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>materiais_produzidos_pela_comuni</t>
+          <t>livros_e_cartilhas</t>
         </is>
       </c>
       <c r="C544" t="inlineStr">
         <is>
-          <t>Materiais produzidos pela comunidade/organização</t>
+          <t>Livros e cartilhas</t>
         </is>
       </c>
     </row>
@@ -22733,12 +22773,12 @@
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>recursos_digitais</t>
+          <t>videos</t>
         </is>
       </c>
       <c r="C545" t="inlineStr">
         <is>
-          <t>Recursos digitais</t>
+          <t>Vídeos</t>
         </is>
       </c>
     </row>
@@ -22750,12 +22790,12 @@
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>nenhum</t>
+          <t>jogos</t>
         </is>
       </c>
       <c r="C546" t="inlineStr">
         <is>
-          <t>Nenhum</t>
+          <t>Jogos</t>
         </is>
       </c>
     </row>
@@ -22767,63 +22807,63 @@
       </c>
       <c r="B547" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>materiais_produzidos_pela_comuni</t>
         </is>
       </c>
       <c r="C547" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>Materiais produzidos pela comunidade/organização</t>
         </is>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="inlineStr">
         <is>
-          <t>quem_part_com</t>
+          <t>materiais_com</t>
         </is>
       </c>
       <c r="B548" t="inlineStr">
         <is>
-          <t>estudantes</t>
+          <t>recursos_digitais</t>
         </is>
       </c>
       <c r="C548" t="inlineStr">
         <is>
-          <t>Estudantes</t>
+          <t>Recursos digitais</t>
         </is>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>quem_part_com</t>
+          <t>materiais_com</t>
         </is>
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>professores</t>
+          <t>nenhum</t>
         </is>
       </c>
       <c r="C549" t="inlineStr">
         <is>
-          <t>Professores(as)</t>
+          <t>Nenhum</t>
         </is>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>quem_part_com</t>
+          <t>materiais_com</t>
         </is>
       </c>
       <c r="B550" t="inlineStr">
         <is>
-          <t>familias</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C550" t="inlineStr">
         <is>
-          <t>Famílias</t>
+          <t>Outro</t>
         </is>
       </c>
     </row>
@@ -22835,12 +22875,12 @@
       </c>
       <c r="B551" t="inlineStr">
         <is>
-          <t>moradores</t>
+          <t>estudantes</t>
         </is>
       </c>
       <c r="C551" t="inlineStr">
         <is>
-          <t>Moradores</t>
+          <t>Estudantes</t>
         </is>
       </c>
     </row>
@@ -22852,12 +22892,12 @@
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>liderancas_comunitarias</t>
+          <t>professores</t>
         </is>
       </c>
       <c r="C552" t="inlineStr">
         <is>
-          <t>Lideranças comunitárias</t>
+          <t>Professores(as)</t>
         </is>
       </c>
     </row>
@@ -22869,12 +22909,12 @@
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>associacoes_ongs</t>
+          <t>familias</t>
         </is>
       </c>
       <c r="C553" t="inlineStr">
         <is>
-          <t>Associações / ONGs</t>
+          <t>Famílias</t>
         </is>
       </c>
     </row>
@@ -22886,12 +22926,12 @@
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>poder_publico</t>
+          <t>moradores</t>
         </is>
       </c>
       <c r="C554" t="inlineStr">
         <is>
-          <t>Poder público</t>
+          <t>Moradores</t>
         </is>
       </c>
     </row>
@@ -22903,63 +22943,63 @@
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>liderancas_comunitarias</t>
         </is>
       </c>
       <c r="C555" t="inlineStr">
         <is>
-          <t>Outros</t>
+          <t>Lideranças comunitárias</t>
         </is>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="inlineStr">
         <is>
-          <t>esp_com</t>
+          <t>quem_part_com</t>
         </is>
       </c>
       <c r="B556" t="inlineStr">
         <is>
-          <t>associacao_de_moradores</t>
+          <t>associacoes_ongs</t>
         </is>
       </c>
       <c r="C556" t="inlineStr">
         <is>
-          <t>Associação de moradores</t>
+          <t>Associações / ONGs</t>
         </is>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="inlineStr">
         <is>
-          <t>esp_com</t>
+          <t>quem_part_com</t>
         </is>
       </c>
       <c r="B557" t="inlineStr">
         <is>
-          <t>conselho_comunitario</t>
+          <t>poder_publico</t>
         </is>
       </c>
       <c r="C557" t="inlineStr">
         <is>
-          <t>Conselho comunitário</t>
+          <t>Poder público</t>
         </is>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="inlineStr">
         <is>
-          <t>esp_com</t>
+          <t>quem_part_com</t>
         </is>
       </c>
       <c r="B558" t="inlineStr">
         <is>
-          <t>assembleias_reunioes_comunitaria</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C558" t="inlineStr">
         <is>
-          <t>Assembleias / reuniões comunitárias</t>
+          <t>Outros</t>
         </is>
       </c>
     </row>
@@ -22971,12 +23011,12 @@
       </c>
       <c r="B559" t="inlineStr">
         <is>
-          <t>gremio_estudantil_coletivos_de_j</t>
+          <t>associacao_de_moradores</t>
         </is>
       </c>
       <c r="C559" t="inlineStr">
         <is>
-          <t>Grêmio estudantil / coletivos de jovens</t>
+          <t>Associação de moradores</t>
         </is>
       </c>
     </row>
@@ -22988,12 +23028,12 @@
       </c>
       <c r="B560" t="inlineStr">
         <is>
-          <t>conselhos_de_politicas_publicas</t>
+          <t>conselho_comunitario</t>
         </is>
       </c>
       <c r="C560" t="inlineStr">
         <is>
-          <t>Conselhos de políticas públicas</t>
+          <t>Conselho comunitário</t>
         </is>
       </c>
     </row>
@@ -23005,12 +23045,12 @@
       </c>
       <c r="B561" t="inlineStr">
         <is>
-          <t>nenhum</t>
+          <t>assembleias_reunioes_comunitaria</t>
         </is>
       </c>
       <c r="C561" t="inlineStr">
         <is>
-          <t>Nenhum</t>
+          <t>Assembleias / reuniões comunitárias</t>
         </is>
       </c>
     </row>
@@ -23022,63 +23062,63 @@
       </c>
       <c r="B562" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>gremio_estudantil_coletivos_de_j</t>
         </is>
       </c>
       <c r="C562" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>Grêmio estudantil / coletivos de jovens</t>
         </is>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="inlineStr">
         <is>
-          <t>instancias_com</t>
+          <t>esp_com</t>
         </is>
       </c>
       <c r="B563" t="inlineStr">
         <is>
-          <t>associacao_de_moradores</t>
+          <t>conselhos_de_politicas_publicas</t>
         </is>
       </c>
       <c r="C563" t="inlineStr">
         <is>
-          <t>Associação de moradores</t>
+          <t>Conselhos de políticas públicas</t>
         </is>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="inlineStr">
         <is>
-          <t>instancias_com</t>
+          <t>esp_com</t>
         </is>
       </c>
       <c r="B564" t="inlineStr">
         <is>
-          <t>conselho_comunitario</t>
+          <t>nenhum</t>
         </is>
       </c>
       <c r="C564" t="inlineStr">
         <is>
-          <t>Conselho comunitário</t>
+          <t>Nenhum</t>
         </is>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="inlineStr">
         <is>
-          <t>instancias_com</t>
+          <t>esp_com</t>
         </is>
       </c>
       <c r="B565" t="inlineStr">
         <is>
-          <t>conselho_escolar</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C565" t="inlineStr">
         <is>
-          <t>Conselho escolar</t>
+          <t>Outro</t>
         </is>
       </c>
     </row>
@@ -23090,12 +23130,12 @@
       </c>
       <c r="B566" t="inlineStr">
         <is>
-          <t>conselhos_de_politicas_publicas</t>
+          <t>associacao_de_moradores</t>
         </is>
       </c>
       <c r="C566" t="inlineStr">
         <is>
-          <t>Conselhos de políticas públicas</t>
+          <t>Associação de moradores</t>
         </is>
       </c>
     </row>
@@ -23107,12 +23147,12 @@
       </c>
       <c r="B567" t="inlineStr">
         <is>
-          <t>gremio_coletivos</t>
+          <t>conselho_comunitario</t>
         </is>
       </c>
       <c r="C567" t="inlineStr">
         <is>
-          <t>Grêmio / coletivos</t>
+          <t>Conselho comunitário</t>
         </is>
       </c>
     </row>
@@ -23124,12 +23164,12 @@
       </c>
       <c r="B568" t="inlineStr">
         <is>
-          <t>nenhuma</t>
+          <t>conselho_escolar</t>
         </is>
       </c>
       <c r="C568" t="inlineStr">
         <is>
-          <t>Nenhuma</t>
+          <t>Conselho escolar</t>
         </is>
       </c>
     </row>
@@ -23141,63 +23181,63 @@
       </c>
       <c r="B569" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>conselhos_de_politicas_publicas</t>
         </is>
       </c>
       <c r="C569" t="inlineStr">
         <is>
-          <t>Outra</t>
+          <t>Conselhos de políticas públicas</t>
         </is>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="inlineStr">
         <is>
-          <t>impacto_alag_com</t>
+          <t>instancias_com</t>
         </is>
       </c>
       <c r="B570" t="inlineStr">
         <is>
-          <t>danos_as_moradias</t>
+          <t>gremio_coletivos</t>
         </is>
       </c>
       <c r="C570" t="inlineStr">
         <is>
-          <t>Danos às moradias</t>
+          <t>Grêmio / coletivos</t>
         </is>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="inlineStr">
         <is>
-          <t>impacto_alag_com</t>
+          <t>instancias_com</t>
         </is>
       </c>
       <c r="B571" t="inlineStr">
         <is>
-          <t>danos_a_ruas_estradas_ou_pontes</t>
+          <t>nenhuma</t>
         </is>
       </c>
       <c r="C571" t="inlineStr">
         <is>
-          <t>Danos a ruas, estradas ou pontes</t>
+          <t>Nenhuma</t>
         </is>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="inlineStr">
         <is>
-          <t>impacto_alag_com</t>
+          <t>instancias_com</t>
         </is>
       </c>
       <c r="B572" t="inlineStr">
         <is>
-          <t>acesso_interrompido</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C572" t="inlineStr">
         <is>
-          <t>Acesso interrompido (trabalho, escola, saúde)</t>
+          <t>Outra</t>
         </is>
       </c>
     </row>
@@ -23209,12 +23249,12 @@
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>contaminacao_da_agua</t>
+          <t>danos_as_moradias</t>
         </is>
       </c>
       <c r="C573" t="inlineStr">
         <is>
-          <t>Contaminação da água</t>
+          <t>Danos às moradias</t>
         </is>
       </c>
     </row>
@@ -23226,12 +23266,12 @@
       </c>
       <c r="B574" t="inlineStr">
         <is>
-          <t>perda_de_bens_ou_plantacoes</t>
+          <t>danos_a_ruas_estradas_ou_pontes</t>
         </is>
       </c>
       <c r="C574" t="inlineStr">
         <is>
-          <t>Perda de bens ou plantações</t>
+          <t>Danos a ruas, estradas ou pontes</t>
         </is>
       </c>
     </row>
@@ -23243,12 +23283,12 @@
       </c>
       <c r="B575" t="inlineStr">
         <is>
-          <t>impacto_na_saude</t>
+          <t>acesso_interrompido</t>
         </is>
       </c>
       <c r="C575" t="inlineStr">
         <is>
-          <t>Impacto na saúde</t>
+          <t>Acesso interrompido (trabalho, escola, saúde)</t>
         </is>
       </c>
     </row>
@@ -23260,12 +23300,12 @@
       </c>
       <c r="B576" t="inlineStr">
         <is>
-          <t>interrupcao_de_aulas</t>
+          <t>contaminacao_da_agua</t>
         </is>
       </c>
       <c r="C576" t="inlineStr">
         <is>
-          <t>Interrupção de aulas</t>
+          <t>Contaminação da água</t>
         </is>
       </c>
     </row>
@@ -23277,63 +23317,63 @@
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>perda_de_bens_ou_plantacoes</t>
         </is>
       </c>
       <c r="C577" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>Perda de bens ou plantações</t>
         </is>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="inlineStr">
         <is>
-          <t>impacto_clima_com</t>
+          <t>impacto_alag_com</t>
         </is>
       </c>
       <c r="B578" t="inlineStr">
         <is>
-          <t>danos_materiais</t>
+          <t>impacto_na_saude</t>
         </is>
       </c>
       <c r="C578" t="inlineStr">
         <is>
-          <t>Danos materiais</t>
+          <t>Impacto na saúde</t>
         </is>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="inlineStr">
         <is>
-          <t>impacto_clima_com</t>
+          <t>impacto_alag_com</t>
         </is>
       </c>
       <c r="B579" t="inlineStr">
         <is>
-          <t>deslocamento_de_pessoas</t>
+          <t>interrupcao_de_aulas</t>
         </is>
       </c>
       <c r="C579" t="inlineStr">
         <is>
-          <t>Deslocamento de pessoas (necessidade de migração)</t>
+          <t>Interrupção de aulas</t>
         </is>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="inlineStr">
         <is>
-          <t>impacto_clima_com</t>
+          <t>impacto_alag_com</t>
         </is>
       </c>
       <c r="B580" t="inlineStr">
         <is>
-          <t>obitos</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C580" t="inlineStr">
         <is>
-          <t>Óbitos</t>
+          <t>Outro</t>
         </is>
       </c>
     </row>
@@ -23345,12 +23385,12 @@
       </c>
       <c r="B581" t="inlineStr">
         <is>
-          <t>perda_de_renda_ou_plantacoes</t>
+          <t>danos_materiais</t>
         </is>
       </c>
       <c r="C581" t="inlineStr">
         <is>
-          <t>Perda de renda ou plantações</t>
+          <t>Danos materiais</t>
         </is>
       </c>
     </row>
@@ -23362,12 +23402,12 @@
       </c>
       <c r="B582" t="inlineStr">
         <is>
-          <t>impacto_na_saude</t>
+          <t>deslocamento_de_pessoas</t>
         </is>
       </c>
       <c r="C582" t="inlineStr">
         <is>
-          <t>Impacto na saúde</t>
+          <t>Deslocamento de pessoas (necessidade de migração)</t>
         </is>
       </c>
     </row>
@@ -23379,12 +23419,12 @@
       </c>
       <c r="B583" t="inlineStr">
         <is>
-          <t>impacto_emocional</t>
+          <t>obitos</t>
         </is>
       </c>
       <c r="C583" t="inlineStr">
         <is>
-          <t>Impacto emocional</t>
+          <t>Óbitos</t>
         </is>
       </c>
     </row>
@@ -23396,12 +23436,12 @@
       </c>
       <c r="B584" t="inlineStr">
         <is>
-          <t>interrupcao_de_aulas_ou_do_traba</t>
+          <t>perda_de_renda_ou_plantacoes</t>
         </is>
       </c>
       <c r="C584" t="inlineStr">
         <is>
-          <t>Interrupção de aulas ou do trabalho</t>
+          <t>Perda de renda ou plantações</t>
         </is>
       </c>
     </row>
@@ -23413,63 +23453,63 @@
       </c>
       <c r="B585" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>impacto_na_saude</t>
         </is>
       </c>
       <c r="C585" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>Impacto na saúde</t>
         </is>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="inlineStr">
         <is>
-          <t>impacto_risco_com</t>
+          <t>impacto_clima_com</t>
         </is>
       </c>
       <c r="B586" t="inlineStr">
         <is>
-          <t>danos_as_moradias</t>
+          <t>impacto_emocional</t>
         </is>
       </c>
       <c r="C586" t="inlineStr">
         <is>
-          <t>Danos às moradias</t>
+          <t>Impacto emocional</t>
         </is>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="inlineStr">
         <is>
-          <t>impacto_risco_com</t>
+          <t>impacto_clima_com</t>
         </is>
       </c>
       <c r="B587" t="inlineStr">
         <is>
-          <t>acesso_interrompido</t>
+          <t>interrupcao_de_aulas_ou_do_traba</t>
         </is>
       </c>
       <c r="C587" t="inlineStr">
         <is>
-          <t>Acesso interrompido</t>
+          <t>Interrupção de aulas ou do trabalho</t>
         </is>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="inlineStr">
         <is>
-          <t>impacto_risco_com</t>
+          <t>impacto_clima_com</t>
         </is>
       </c>
       <c r="B588" t="inlineStr">
         <is>
-          <t>perda_de_bens_materiais</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C588" t="inlineStr">
         <is>
-          <t>Perda de bens/materiais</t>
+          <t>Outro</t>
         </is>
       </c>
     </row>
@@ -23481,12 +23521,12 @@
       </c>
       <c r="B589" t="inlineStr">
         <is>
-          <t>impacto_na_saude</t>
+          <t>danos_as_moradias</t>
         </is>
       </c>
       <c r="C589" t="inlineStr">
         <is>
-          <t>Impacto na saúde</t>
+          <t>Danos às moradias</t>
         </is>
       </c>
     </row>
@@ -23498,12 +23538,12 @@
       </c>
       <c r="B590" t="inlineStr">
         <is>
-          <t>impacto_emocional</t>
+          <t>acesso_interrompido</t>
         </is>
       </c>
       <c r="C590" t="inlineStr">
         <is>
-          <t>Impacto emocional</t>
+          <t>Acesso interrompido</t>
         </is>
       </c>
     </row>
@@ -23515,12 +23555,12 @@
       </c>
       <c r="B591" t="inlineStr">
         <is>
-          <t>perda_de_renda_ou_plantacoes</t>
+          <t>perda_de_bens_materiais</t>
         </is>
       </c>
       <c r="C591" t="inlineStr">
         <is>
-          <t>Perda de renda ou plantações</t>
+          <t>Perda de bens/materiais</t>
         </is>
       </c>
     </row>
@@ -23532,12 +23572,12 @@
       </c>
       <c r="B592" t="inlineStr">
         <is>
-          <t>interrupcao_de_aulas_ou_do_traba</t>
+          <t>impacto_na_saude</t>
         </is>
       </c>
       <c r="C592" t="inlineStr">
         <is>
-          <t>Interrupção de aulas ou do trabalho</t>
+          <t>Impacto na saúde</t>
         </is>
       </c>
     </row>
@@ -23549,63 +23589,63 @@
       </c>
       <c r="B593" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>impacto_emocional</t>
         </is>
       </c>
       <c r="C593" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>Impacto emocional</t>
         </is>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="inlineStr">
         <is>
-          <t>afetou_com</t>
+          <t>impacto_risco_com</t>
         </is>
       </c>
       <c r="B594" t="inlineStr">
         <is>
-          <t>minha_familia_moradia</t>
+          <t>perda_de_renda_ou_plantacoes</t>
         </is>
       </c>
       <c r="C594" t="inlineStr">
         <is>
-          <t>Minha família / moradia</t>
+          <t>Perda de renda ou plantações</t>
         </is>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="inlineStr">
         <is>
-          <t>afetou_com</t>
+          <t>impacto_risco_com</t>
         </is>
       </c>
       <c r="B595" t="inlineStr">
         <is>
-          <t>a_comunidade_como_um_todo</t>
+          <t>interrupcao_de_aulas_ou_do_traba</t>
         </is>
       </c>
       <c r="C595" t="inlineStr">
         <is>
-          <t>A comunidade como um todo</t>
+          <t>Interrupção de aulas ou do trabalho</t>
         </is>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="inlineStr">
         <is>
-          <t>afetou_com</t>
+          <t>impacto_risco_com</t>
         </is>
       </c>
       <c r="B596" t="inlineStr">
         <is>
-          <t>ambos</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C596" t="inlineStr">
         <is>
-          <t>Ambos</t>
+          <t>Outro</t>
         </is>
       </c>
     </row>
@@ -23617,12 +23657,12 @@
       </c>
       <c r="B597" t="inlineStr">
         <is>
-          <t>nenhum</t>
+          <t>minha_familia_moradia</t>
         </is>
       </c>
       <c r="C597" t="inlineStr">
         <is>
-          <t>Nenhum</t>
+          <t>Minha família / moradia</t>
         </is>
       </c>
     </row>
@@ -23634,63 +23674,63 @@
       </c>
       <c r="B598" t="inlineStr">
         <is>
-          <t>nao_sabe</t>
+          <t>a_comunidade_como_um_todo</t>
         </is>
       </c>
       <c r="C598" t="inlineStr">
         <is>
-          <t>Não sabe</t>
+          <t>A comunidade como um todo</t>
         </is>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="inlineStr">
         <is>
-          <t>ativos_com</t>
+          <t>afetou_com</t>
         </is>
       </c>
       <c r="B599" t="inlineStr">
         <is>
-          <t>moradias</t>
+          <t>ambos</t>
         </is>
       </c>
       <c r="C599" t="inlineStr">
         <is>
-          <t>Moradias</t>
+          <t>Ambos</t>
         </is>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="inlineStr">
         <is>
-          <t>ativos_com</t>
+          <t>afetou_com</t>
         </is>
       </c>
       <c r="B600" t="inlineStr">
         <is>
-          <t>escola</t>
+          <t>nenhum</t>
         </is>
       </c>
       <c r="C600" t="inlineStr">
         <is>
-          <t>Escola(s)</t>
+          <t>Nenhum</t>
         </is>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="inlineStr">
         <is>
-          <t>ativos_com</t>
+          <t>afetou_com</t>
         </is>
       </c>
       <c r="B601" t="inlineStr">
         <is>
-          <t>posto_de_saude</t>
+          <t>nao_sabe</t>
         </is>
       </c>
       <c r="C601" t="inlineStr">
         <is>
-          <t>Posto de saúde</t>
+          <t>Não sabe</t>
         </is>
       </c>
     </row>
@@ -23702,12 +23742,12 @@
       </c>
       <c r="B602" t="inlineStr">
         <is>
-          <t>ruas_estradas_e_pontes</t>
+          <t>moradias</t>
         </is>
       </c>
       <c r="C602" t="inlineStr">
         <is>
-          <t>Ruas, estradas e pontes</t>
+          <t>Moradias</t>
         </is>
       </c>
     </row>
@@ -23719,12 +23759,12 @@
       </c>
       <c r="B603" t="inlineStr">
         <is>
-          <t>plantacoes_rocas_e_criacoes</t>
+          <t>escola</t>
         </is>
       </c>
       <c r="C603" t="inlineStr">
         <is>
-          <t>Plantações, roças e criações</t>
+          <t>Escola(s)</t>
         </is>
       </c>
     </row>
@@ -23736,12 +23776,12 @@
       </c>
       <c r="B604" t="inlineStr">
         <is>
-          <t>fontes_de_agua</t>
+          <t>posto_de_saude</t>
         </is>
       </c>
       <c r="C604" t="inlineStr">
         <is>
-          <t>Fontes de água</t>
+          <t>Posto de saúde</t>
         </is>
       </c>
     </row>
@@ -23753,12 +23793,12 @@
       </c>
       <c r="B605" t="inlineStr">
         <is>
-          <t>comercios_locais_de_trabalho</t>
+          <t>ruas_estradas_e_pontes</t>
         </is>
       </c>
       <c r="C605" t="inlineStr">
         <is>
-          <t>Comércios / locais de trabalho</t>
+          <t>Ruas, estradas e pontes</t>
         </is>
       </c>
     </row>
@@ -23770,12 +23810,12 @@
       </c>
       <c r="B606" t="inlineStr">
         <is>
-          <t>espacos_comunitarios</t>
+          <t>plantacoes_rocas_e_criacoes</t>
         </is>
       </c>
       <c r="C606" t="inlineStr">
         <is>
-          <t>Espaços comunitários</t>
+          <t>Plantações, roças e criações</t>
         </is>
       </c>
     </row>
@@ -23787,63 +23827,63 @@
       </c>
       <c r="B607" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>fontes_de_agua</t>
         </is>
       </c>
       <c r="C607" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>Fontes de água</t>
         </is>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="inlineStr">
         <is>
-          <t>grupos_exp_com</t>
+          <t>ativos_com</t>
         </is>
       </c>
       <c r="B608" t="inlineStr">
         <is>
-          <t>estudantes</t>
+          <t>comercios_locais_de_trabalho</t>
         </is>
       </c>
       <c r="C608" t="inlineStr">
         <is>
-          <t>Estudantes</t>
+          <t>Comércios / locais de trabalho</t>
         </is>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="inlineStr">
         <is>
-          <t>grupos_exp_com</t>
+          <t>ativos_com</t>
         </is>
       </c>
       <c r="B609" t="inlineStr">
         <is>
-          <t>familias</t>
+          <t>espacos_comunitarios</t>
         </is>
       </c>
       <c r="C609" t="inlineStr">
         <is>
-          <t>Famílias</t>
+          <t>Espaços comunitários</t>
         </is>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="inlineStr">
         <is>
-          <t>grupos_exp_com</t>
+          <t>ativos_com</t>
         </is>
       </c>
       <c r="B610" t="inlineStr">
         <is>
-          <t>pessoas_com_deficiencia</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C610" t="inlineStr">
         <is>
-          <t>Pessoas com deficiência</t>
+          <t>Outro</t>
         </is>
       </c>
     </row>
@@ -23855,12 +23895,12 @@
       </c>
       <c r="B611" t="inlineStr">
         <is>
-          <t>criancas_pequenas</t>
+          <t>estudantes</t>
         </is>
       </c>
       <c r="C611" t="inlineStr">
         <is>
-          <t>Crianças pequenas</t>
+          <t>Estudantes</t>
         </is>
       </c>
     </row>
@@ -23872,12 +23912,12 @@
       </c>
       <c r="B612" t="inlineStr">
         <is>
-          <t>idosos</t>
+          <t>familias</t>
         </is>
       </c>
       <c r="C612" t="inlineStr">
         <is>
-          <t>Idosos</t>
+          <t>Famílias</t>
         </is>
       </c>
     </row>
@@ -23889,12 +23929,12 @@
       </c>
       <c r="B613" t="inlineStr">
         <is>
-          <t>trabalhadores_rurais_pescadores</t>
+          <t>pessoas_com_deficiencia</t>
         </is>
       </c>
       <c r="C613" t="inlineStr">
         <is>
-          <t>Trabalhadores rurais / pescadores</t>
+          <t>Pessoas com deficiência</t>
         </is>
       </c>
     </row>
@@ -23906,12 +23946,12 @@
       </c>
       <c r="B614" t="inlineStr">
         <is>
-          <t>povos_e_comunidades_tradicionais</t>
+          <t>criancas_pequenas</t>
         </is>
       </c>
       <c r="C614" t="inlineStr">
         <is>
-          <t>Povos e comunidades tradicionais</t>
+          <t>Crianças pequenas</t>
         </is>
       </c>
     </row>
@@ -23923,63 +23963,63 @@
       </c>
       <c r="B615" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>idosos</t>
         </is>
       </c>
       <c r="C615" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>Idosos</t>
         </is>
       </c>
     </row>
     <row r="616">
       <c r="A616" t="inlineStr">
         <is>
-          <t>cartog_com</t>
+          <t>grupos_exp_com</t>
         </is>
       </c>
       <c r="B616" t="inlineStr">
         <is>
-          <t>estudantes</t>
+          <t>trabalhadores_rurais_pescadores</t>
         </is>
       </c>
       <c r="C616" t="inlineStr">
         <is>
-          <t>Estudantes</t>
+          <t>Trabalhadores rurais / pescadores</t>
         </is>
       </c>
     </row>
     <row r="617">
       <c r="A617" t="inlineStr">
         <is>
-          <t>cartog_com</t>
+          <t>grupos_exp_com</t>
         </is>
       </c>
       <c r="B617" t="inlineStr">
         <is>
-          <t>moradores</t>
+          <t>povos_e_comunidades_tradicionais</t>
         </is>
       </c>
       <c r="C617" t="inlineStr">
         <is>
-          <t>Moradores</t>
+          <t>Povos e comunidades tradicionais</t>
         </is>
       </c>
     </row>
     <row r="618">
       <c r="A618" t="inlineStr">
         <is>
-          <t>cartog_com</t>
+          <t>grupos_exp_com</t>
         </is>
       </c>
       <c r="B618" t="inlineStr">
         <is>
-          <t>liderancas</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C618" t="inlineStr">
         <is>
-          <t>Lideranças</t>
+          <t>Outro</t>
         </is>
       </c>
     </row>
@@ -23991,12 +24031,12 @@
       </c>
       <c r="B619" t="inlineStr">
         <is>
-          <t>pessoas_de_ongs</t>
+          <t>estudantes</t>
         </is>
       </c>
       <c r="C619" t="inlineStr">
         <is>
-          <t>Pessoas de ONGs</t>
+          <t>Estudantes</t>
         </is>
       </c>
     </row>
@@ -24008,63 +24048,63 @@
       </c>
       <c r="B620" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>moradores</t>
         </is>
       </c>
       <c r="C620" t="inlineStr">
         <is>
-          <t>Outros</t>
+          <t>Moradores</t>
         </is>
       </c>
     </row>
     <row r="621">
       <c r="A621" t="inlineStr">
         <is>
-          <t>abrangencia_com</t>
+          <t>cartog_com</t>
         </is>
       </c>
       <c r="B621" t="inlineStr">
         <is>
-          <t>individual</t>
+          <t>liderancas</t>
         </is>
       </c>
       <c r="C621" t="inlineStr">
         <is>
-          <t>Individual</t>
+          <t>Lideranças</t>
         </is>
       </c>
     </row>
     <row r="622">
       <c r="A622" t="inlineStr">
         <is>
-          <t>abrangencia_com</t>
+          <t>cartog_com</t>
         </is>
       </c>
       <c r="B622" t="inlineStr">
         <is>
-          <t>uma_familia</t>
+          <t>pessoas_de_ongs</t>
         </is>
       </c>
       <c r="C622" t="inlineStr">
         <is>
-          <t>Uma família</t>
+          <t>Pessoas de ONGs</t>
         </is>
       </c>
     </row>
     <row r="623">
       <c r="A623" t="inlineStr">
         <is>
-          <t>abrangencia_com</t>
+          <t>cartog_com</t>
         </is>
       </c>
       <c r="B623" t="inlineStr">
         <is>
-          <t>um_grupo_ou_organizacao</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C623" t="inlineStr">
         <is>
-          <t>Um grupo ou organização</t>
+          <t>Outros</t>
         </is>
       </c>
     </row>
@@ -24076,12 +24116,12 @@
       </c>
       <c r="B624" t="inlineStr">
         <is>
-          <t>toda_a_comunidade</t>
+          <t>individual</t>
         </is>
       </c>
       <c r="C624" t="inlineStr">
         <is>
-          <t>Toda a comunidade</t>
+          <t>Individual</t>
         </is>
       </c>
     </row>
@@ -24093,63 +24133,63 @@
       </c>
       <c r="B625" t="inlineStr">
         <is>
-          <t>mais_de_uma_comunidade_territori</t>
+          <t>uma_familia</t>
         </is>
       </c>
       <c r="C625" t="inlineStr">
         <is>
-          <t>Mais de uma comunidade / território</t>
+          <t>Uma família</t>
         </is>
       </c>
     </row>
     <row r="626">
       <c r="A626" t="inlineStr">
         <is>
-          <t>afetados_com</t>
+          <t>abrangencia_com</t>
         </is>
       </c>
       <c r="B626" t="inlineStr">
         <is>
-          <t>estudantes</t>
+          <t>um_grupo_ou_organizacao</t>
         </is>
       </c>
       <c r="C626" t="inlineStr">
         <is>
-          <t>Estudantes</t>
+          <t>Um grupo ou organização</t>
         </is>
       </c>
     </row>
     <row r="627">
       <c r="A627" t="inlineStr">
         <is>
-          <t>afetados_com</t>
+          <t>abrangencia_com</t>
         </is>
       </c>
       <c r="B627" t="inlineStr">
         <is>
-          <t>familias</t>
+          <t>toda_a_comunidade</t>
         </is>
       </c>
       <c r="C627" t="inlineStr">
         <is>
-          <t>Famílias</t>
+          <t>Toda a comunidade</t>
         </is>
       </c>
     </row>
     <row r="628">
       <c r="A628" t="inlineStr">
         <is>
-          <t>afetados_com</t>
+          <t>abrangencia_com</t>
         </is>
       </c>
       <c r="B628" t="inlineStr">
         <is>
-          <t>moradores</t>
+          <t>mais_de_uma_comunidade_territori</t>
         </is>
       </c>
       <c r="C628" t="inlineStr">
         <is>
-          <t>Moradores</t>
+          <t>Mais de uma comunidade / território</t>
         </is>
       </c>
     </row>
@@ -24161,12 +24201,12 @@
       </c>
       <c r="B629" t="inlineStr">
         <is>
-          <t>trabalhadores</t>
+          <t>estudantes</t>
         </is>
       </c>
       <c r="C629" t="inlineStr">
         <is>
-          <t>Trabalhadores</t>
+          <t>Estudantes</t>
         </is>
       </c>
     </row>
@@ -24178,12 +24218,12 @@
       </c>
       <c r="B630" t="inlineStr">
         <is>
-          <t>criancas_e_idosos</t>
+          <t>familias</t>
         </is>
       </c>
       <c r="C630" t="inlineStr">
         <is>
-          <t>Crianças e idosos</t>
+          <t>Famílias</t>
         </is>
       </c>
     </row>
@@ -24195,63 +24235,63 @@
       </c>
       <c r="B631" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>moradores</t>
         </is>
       </c>
       <c r="C631" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>Moradores</t>
         </is>
       </c>
     </row>
     <row r="632">
       <c r="A632" t="inlineStr">
         <is>
-          <t>decisao_part_com</t>
+          <t>afetados_com</t>
         </is>
       </c>
       <c r="B632" t="inlineStr">
         <is>
-          <t>estudantes</t>
+          <t>trabalhadores</t>
         </is>
       </c>
       <c r="C632" t="inlineStr">
         <is>
-          <t>Estudantes</t>
+          <t>Trabalhadores</t>
         </is>
       </c>
     </row>
     <row r="633">
       <c r="A633" t="inlineStr">
         <is>
-          <t>decisao_part_com</t>
+          <t>afetados_com</t>
         </is>
       </c>
       <c r="B633" t="inlineStr">
         <is>
-          <t>familias</t>
+          <t>criancas_e_idosos</t>
         </is>
       </c>
       <c r="C633" t="inlineStr">
         <is>
-          <t>Famílias</t>
+          <t>Crianças e idosos</t>
         </is>
       </c>
     </row>
     <row r="634">
       <c r="A634" t="inlineStr">
         <is>
-          <t>decisao_part_com</t>
+          <t>afetados_com</t>
         </is>
       </c>
       <c r="B634" t="inlineStr">
         <is>
-          <t>moradores</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C634" t="inlineStr">
         <is>
-          <t>Moradores</t>
+          <t>Outro</t>
         </is>
       </c>
     </row>
@@ -24263,12 +24303,12 @@
       </c>
       <c r="B635" t="inlineStr">
         <is>
-          <t>liderancas_comunitarias</t>
+          <t>estudantes</t>
         </is>
       </c>
       <c r="C635" t="inlineStr">
         <is>
-          <t>Lideranças comunitárias</t>
+          <t>Estudantes</t>
         </is>
       </c>
     </row>
@@ -24280,12 +24320,12 @@
       </c>
       <c r="B636" t="inlineStr">
         <is>
-          <t>associacoes_ongs</t>
+          <t>familias</t>
         </is>
       </c>
       <c r="C636" t="inlineStr">
         <is>
-          <t>Associações / ONGs</t>
+          <t>Famílias</t>
         </is>
       </c>
     </row>
@@ -24297,12 +24337,12 @@
       </c>
       <c r="B637" t="inlineStr">
         <is>
-          <t>poder_publico</t>
+          <t>moradores</t>
         </is>
       </c>
       <c r="C637" t="inlineStr">
         <is>
-          <t>Poder público</t>
+          <t>Moradores</t>
         </is>
       </c>
     </row>
@@ -24314,12 +24354,12 @@
       </c>
       <c r="B638" t="inlineStr">
         <is>
-          <t>escola_do_territorio</t>
+          <t>liderancas_comunitarias</t>
         </is>
       </c>
       <c r="C638" t="inlineStr">
         <is>
-          <t>Escola(s) do território</t>
+          <t>Lideranças comunitárias</t>
         </is>
       </c>
     </row>
@@ -24331,63 +24371,63 @@
       </c>
       <c r="B639" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>associacoes_ongs</t>
         </is>
       </c>
       <c r="C639" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>Associações / ONGs</t>
         </is>
       </c>
     </row>
     <row r="640">
       <c r="A640" t="inlineStr">
         <is>
-          <t>publicos_com</t>
+          <t>decisao_part_com</t>
         </is>
       </c>
       <c r="B640" t="inlineStr">
         <is>
-          <t>estudantes</t>
+          <t>poder_publico</t>
         </is>
       </c>
       <c r="C640" t="inlineStr">
         <is>
-          <t>Estudantes</t>
+          <t>Poder público</t>
         </is>
       </c>
     </row>
     <row r="641">
       <c r="A641" t="inlineStr">
         <is>
-          <t>publicos_com</t>
+          <t>decisao_part_com</t>
         </is>
       </c>
       <c r="B641" t="inlineStr">
         <is>
-          <t>professores</t>
+          <t>escola_do_territorio</t>
         </is>
       </c>
       <c r="C641" t="inlineStr">
         <is>
-          <t>Professores(as)</t>
+          <t>Escola(s) do território</t>
         </is>
       </c>
     </row>
     <row r="642">
       <c r="A642" t="inlineStr">
         <is>
-          <t>publicos_com</t>
+          <t>decisao_part_com</t>
         </is>
       </c>
       <c r="B642" t="inlineStr">
         <is>
-          <t>familias</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C642" t="inlineStr">
         <is>
-          <t>Famílias</t>
+          <t>Outro</t>
         </is>
       </c>
     </row>
@@ -24399,12 +24439,12 @@
       </c>
       <c r="B643" t="inlineStr">
         <is>
-          <t>moradores</t>
+          <t>estudantes</t>
         </is>
       </c>
       <c r="C643" t="inlineStr">
         <is>
-          <t>Moradores</t>
+          <t>Estudantes</t>
         </is>
       </c>
     </row>
@@ -24416,12 +24456,12 @@
       </c>
       <c r="B644" t="inlineStr">
         <is>
-          <t>associacoes_ongs</t>
+          <t>professores</t>
         </is>
       </c>
       <c r="C644" t="inlineStr">
         <is>
-          <t>Associações / ONGs</t>
+          <t>Professores(as)</t>
         </is>
       </c>
     </row>
@@ -24433,12 +24473,12 @@
       </c>
       <c r="B645" t="inlineStr">
         <is>
-          <t>poder_publico</t>
+          <t>familias</t>
         </is>
       </c>
       <c r="C645" t="inlineStr">
         <is>
-          <t>Poder público</t>
+          <t>Famílias</t>
         </is>
       </c>
     </row>
@@ -24450,63 +24490,63 @@
       </c>
       <c r="B646" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>moradores</t>
         </is>
       </c>
       <c r="C646" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>Moradores</t>
         </is>
       </c>
     </row>
     <row r="647">
       <c r="A647" t="inlineStr">
         <is>
-          <t>dependencias_com</t>
+          <t>publicos_com</t>
         </is>
       </c>
       <c r="B647" t="inlineStr">
         <is>
-          <t>aprovacao_de_liderancas_poder_pu</t>
+          <t>associacoes_ongs</t>
         </is>
       </c>
       <c r="C647" t="inlineStr">
         <is>
-          <t>Aprovação de lideranças / poder público</t>
+          <t>Associações / ONGs</t>
         </is>
       </c>
     </row>
     <row r="648">
       <c r="A648" t="inlineStr">
         <is>
-          <t>dependencias_com</t>
+          <t>publicos_com</t>
         </is>
       </c>
       <c r="B648" t="inlineStr">
         <is>
-          <t>recursos_financeiros</t>
+          <t>poder_publico</t>
         </is>
       </c>
       <c r="C648" t="inlineStr">
         <is>
-          <t>Recursos financeiros</t>
+          <t>Poder público</t>
         </is>
       </c>
     </row>
     <row r="649">
       <c r="A649" t="inlineStr">
         <is>
-          <t>dependencias_com</t>
+          <t>publicos_com</t>
         </is>
       </c>
       <c r="B649" t="inlineStr">
         <is>
-          <t>parceria_externa</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C649" t="inlineStr">
         <is>
-          <t>Parceria externa</t>
+          <t>Outro</t>
         </is>
       </c>
     </row>
@@ -24518,12 +24558,12 @@
       </c>
       <c r="B650" t="inlineStr">
         <is>
-          <t>formacao_previa</t>
+          <t>aprovacao_de_liderancas_poder_pu</t>
         </is>
       </c>
       <c r="C650" t="inlineStr">
         <is>
-          <t>Formação prévia</t>
+          <t>Aprovação de lideranças / poder público</t>
         </is>
       </c>
     </row>
@@ -24535,12 +24575,12 @@
       </c>
       <c r="B651" t="inlineStr">
         <is>
-          <t>nenhuma</t>
+          <t>recursos_financeiros</t>
         </is>
       </c>
       <c r="C651" t="inlineStr">
         <is>
-          <t>Nenhuma</t>
+          <t>Recursos financeiros</t>
         </is>
       </c>
     </row>
@@ -24552,63 +24592,63 @@
       </c>
       <c r="B652" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>parceria_externa</t>
         </is>
       </c>
       <c r="C652" t="inlineStr">
         <is>
-          <t>Outra</t>
+          <t>Parceria externa</t>
         </is>
       </c>
     </row>
     <row r="653">
       <c r="A653" t="inlineStr">
         <is>
-          <t>evid_exec_com</t>
+          <t>dependencias_com</t>
         </is>
       </c>
       <c r="B653" t="inlineStr">
         <is>
-          <t>fotos</t>
+          <t>formacao_previa</t>
         </is>
       </c>
       <c r="C653" t="inlineStr">
         <is>
-          <t>Fotos</t>
+          <t>Formação prévia</t>
         </is>
       </c>
     </row>
     <row r="654">
       <c r="A654" t="inlineStr">
         <is>
-          <t>evid_exec_com</t>
+          <t>dependencias_com</t>
         </is>
       </c>
       <c r="B654" t="inlineStr">
         <is>
-          <t>lista_de_presenca</t>
+          <t>nenhuma</t>
         </is>
       </c>
       <c r="C654" t="inlineStr">
         <is>
-          <t>Lista de presença</t>
+          <t>Nenhuma</t>
         </is>
       </c>
     </row>
     <row r="655">
       <c r="A655" t="inlineStr">
         <is>
-          <t>evid_exec_com</t>
+          <t>dependencias_com</t>
         </is>
       </c>
       <c r="B655" t="inlineStr">
         <is>
-          <t>producoes_da_comunidade</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C655" t="inlineStr">
         <is>
-          <t>Produções da comunidade</t>
+          <t>Outra</t>
         </is>
       </c>
     </row>
@@ -24620,12 +24660,12 @@
       </c>
       <c r="B656" t="inlineStr">
         <is>
-          <t>registro_em_ata</t>
+          <t>fotos</t>
         </is>
       </c>
       <c r="C656" t="inlineStr">
         <is>
-          <t>Registro em ata</t>
+          <t>Fotos</t>
         </is>
       </c>
     </row>
@@ -24637,12 +24677,12 @@
       </c>
       <c r="B657" t="inlineStr">
         <is>
-          <t>depoimentos</t>
+          <t>lista_de_presenca</t>
         </is>
       </c>
       <c r="C657" t="inlineStr">
         <is>
-          <t>Depoimentos</t>
+          <t>Lista de presença</t>
         </is>
       </c>
     </row>
@@ -24654,63 +24694,63 @@
       </c>
       <c r="B658" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>producoes_da_comunidade</t>
         </is>
       </c>
       <c r="C658" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>Produções da comunidade</t>
         </is>
       </c>
     </row>
     <row r="659">
       <c r="A659" t="inlineStr">
         <is>
-          <t>metodo_sel_com</t>
+          <t>evid_exec_com</t>
         </is>
       </c>
       <c r="B659" t="inlineStr">
         <is>
-          <t>votacao</t>
+          <t>registro_em_ata</t>
         </is>
       </c>
       <c r="C659" t="inlineStr">
         <is>
-          <t>Votação</t>
+          <t>Registro em ata</t>
         </is>
       </c>
     </row>
     <row r="660">
       <c r="A660" t="inlineStr">
         <is>
-          <t>metodo_sel_com</t>
+          <t>evid_exec_com</t>
         </is>
       </c>
       <c r="B660" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>depoimentos</t>
         </is>
       </c>
       <c r="C660" t="inlineStr">
         <is>
-          <t>Consenso</t>
+          <t>Depoimentos</t>
         </is>
       </c>
     </row>
     <row r="661">
       <c r="A661" t="inlineStr">
         <is>
-          <t>metodo_sel_com</t>
+          <t>evid_exec_com</t>
         </is>
       </c>
       <c r="B661" t="inlineStr">
         <is>
-          <t>decisao_de_liderancas_ou_da_coor</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C661" t="inlineStr">
         <is>
-          <t>Decisão de lideranças ou da coordenação</t>
+          <t>Outro</t>
         </is>
       </c>
     </row>
@@ -24722,12 +24762,12 @@
       </c>
       <c r="B662" t="inlineStr">
         <is>
-          <t>criterios_tecnicos</t>
+          <t>votacao</t>
         </is>
       </c>
       <c r="C662" t="inlineStr">
         <is>
-          <t>Critérios técnicos</t>
+          <t>Votação</t>
         </is>
       </c>
     </row>
@@ -24739,12 +24779,12 @@
       </c>
       <c r="B663" t="inlineStr">
         <is>
-          <t>discussao_coletiva</t>
+          <t>consenso</t>
         </is>
       </c>
       <c r="C663" t="inlineStr">
         <is>
-          <t>Discussão coletiva</t>
+          <t>Consenso</t>
         </is>
       </c>
     </row>
@@ -24756,63 +24796,63 @@
       </c>
       <c r="B664" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>decisao_de_liderancas_ou_da_coor</t>
         </is>
       </c>
       <c r="C664" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>Decisão de lideranças ou da coordenação</t>
         </is>
       </c>
     </row>
     <row r="665">
       <c r="A665" t="inlineStr">
         <is>
-          <t>com_produz_com</t>
+          <t>metodo_sel_com</t>
         </is>
       </c>
       <c r="B665" t="inlineStr">
         <is>
-          <t>estudantes</t>
+          <t>criterios_tecnicos</t>
         </is>
       </c>
       <c r="C665" t="inlineStr">
         <is>
-          <t>Estudantes</t>
+          <t>Critérios técnicos</t>
         </is>
       </c>
     </row>
     <row r="666">
       <c r="A666" t="inlineStr">
         <is>
-          <t>com_produz_com</t>
+          <t>metodo_sel_com</t>
         </is>
       </c>
       <c r="B666" t="inlineStr">
         <is>
-          <t>moradores</t>
+          <t>discussao_coletiva</t>
         </is>
       </c>
       <c r="C666" t="inlineStr">
         <is>
-          <t>Moradores</t>
+          <t>Discussão coletiva</t>
         </is>
       </c>
     </row>
     <row r="667">
       <c r="A667" t="inlineStr">
         <is>
-          <t>com_produz_com</t>
+          <t>metodo_sel_com</t>
         </is>
       </c>
       <c r="B667" t="inlineStr">
         <is>
-          <t>associacao_ong</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C667" t="inlineStr">
         <is>
-          <t>Associação / ONG</t>
+          <t>Outro</t>
         </is>
       </c>
     </row>
@@ -24824,12 +24864,12 @@
       </c>
       <c r="B668" t="inlineStr">
         <is>
-          <t>coletivos_de_jovens</t>
+          <t>estudantes</t>
         </is>
       </c>
       <c r="C668" t="inlineStr">
         <is>
-          <t>Coletivos de jovens</t>
+          <t>Estudantes</t>
         </is>
       </c>
     </row>
@@ -24841,12 +24881,12 @@
       </c>
       <c r="B669" t="inlineStr">
         <is>
-          <t>parceiros_externos</t>
+          <t>moradores</t>
         </is>
       </c>
       <c r="C669" t="inlineStr">
         <is>
-          <t>Parceiros externos</t>
+          <t>Moradores</t>
         </is>
       </c>
     </row>
@@ -24858,10 +24898,61 @@
       </c>
       <c r="B670" t="inlineStr">
         <is>
+          <t>associacao_ong</t>
+        </is>
+      </c>
+      <c r="C670" t="inlineStr">
+        <is>
+          <t>Associação / ONG</t>
+        </is>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" t="inlineStr">
+        <is>
+          <t>com_produz_com</t>
+        </is>
+      </c>
+      <c r="B671" t="inlineStr">
+        <is>
+          <t>coletivos_de_jovens</t>
+        </is>
+      </c>
+      <c r="C671" t="inlineStr">
+        <is>
+          <t>Coletivos de jovens</t>
+        </is>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" t="inlineStr">
+        <is>
+          <t>com_produz_com</t>
+        </is>
+      </c>
+      <c r="B672" t="inlineStr">
+        <is>
+          <t>parceiros_externos</t>
+        </is>
+      </c>
+      <c r="C672" t="inlineStr">
+        <is>
+          <t>Parceiros externos</t>
+        </is>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" t="inlineStr">
+        <is>
+          <t>com_produz_com</t>
+        </is>
+      </c>
+      <c r="B673" t="inlineStr">
+        <is>
           <t>outro</t>
         </is>
       </c>
-      <c r="C670" t="inlineStr">
+      <c r="C673" t="inlineStr">
         <is>
           <t>Outro</t>
         </is>
